--- a/cases/bcc-tmmin/model/TMMIN_Case_Model.xlsx
+++ b/cases/bcc-tmmin/model/TMMIN_Case_Model.xlsx
@@ -11,17 +11,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer_Guide" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ideation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulation" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exhibits" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Breakeven" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capability" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPIs" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA_Bank" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulation2" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulation1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulation" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exhibits" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Breakeven" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capability" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPIs" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA_Bank" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,6 +435,304 @@
           </spPr>
           <cat>
             <numRef>
+              <f>'Simulation2'!$A$42:$A$46</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Simulation2'!$B$42:$B$46</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>NPV across 10,000 runs (Rp B)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Simulation2'!$A$75:$A$90</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Simulation2'!$B$75:$B$90</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="10"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Scrap reduction falls as alerts are dismissed</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Simulation1'!$A$42:$A$46</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Simulation1'!$B$42:$B$46</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>NPV across 10,000 runs (Rp B)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Simulation1'!$A$75:$A$90</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Simulation1'!$B$75:$B$90</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="10"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Scrap reduction falls as alerts are dismissed</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
               <f>'Simulation'!$A$42:$A$46</f>
             </numRef>
           </cat>
@@ -476,7 +776,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -550,7 +850,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -624,7 +924,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -853,6 +1153,104 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>40</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="2160000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>73</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2520000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>40</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="2160000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>73</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2520000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1506,6 +1904,2591 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H86"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Savings, investment and NPV by scenario (Rp billion)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Program window 2026-2030 = 5-year economic life. No terminal value (conservative).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="35" t="inlineStr">
+        <is>
+          <t>Scenario: Conservative</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Adoption ramp-up</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C6" s="36">
+        <f>Assumptions!B$43</f>
+        <v/>
+      </c>
+      <c r="D6" s="36">
+        <f>Assumptions!C$43</f>
+        <v/>
+      </c>
+      <c r="E6" s="36">
+        <f>Assumptions!D$43</f>
+        <v/>
+      </c>
+      <c r="F6" s="36">
+        <f>Assumptions!E$43</f>
+        <v/>
+      </c>
+      <c r="G6" s="36">
+        <f>Assumptions!F$43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Escalation factor</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C7" s="37">
+        <f>(1+Assumptions!$B$10)^(Assumptions!B$45-1)</f>
+        <v/>
+      </c>
+      <c r="D7" s="37">
+        <f>(1+Assumptions!$B$10)^(Assumptions!C$45-1)</f>
+        <v/>
+      </c>
+      <c r="E7" s="37">
+        <f>(1+Assumptions!$B$10)^(Assumptions!D$45-1)</f>
+        <v/>
+      </c>
+      <c r="F7" s="37">
+        <f>(1+Assumptions!$B$10)^(Assumptions!E$45-1)</f>
+        <v/>
+      </c>
+      <c r="G7" s="37">
+        <f>(1+Assumptions!$B$10)^(Assumptions!F$45-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Saving: scrap</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C8" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$B$32*C6*C7</f>
+        <v/>
+      </c>
+      <c r="D8" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$B$32*D6*D7</f>
+        <v/>
+      </c>
+      <c r="E8" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$B$32*E6*E7</f>
+        <v/>
+      </c>
+      <c r="F8" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$B$32*F6*F7</f>
+        <v/>
+      </c>
+      <c r="G8" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$B$32*G6*G7</f>
+        <v/>
+      </c>
+      <c r="H8" s="76">
+        <f>SUM(C8:G8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Saving: maintenance / downtime</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C9" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$B$33*C6*C7</f>
+        <v/>
+      </c>
+      <c r="D9" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$B$33*D6*D7</f>
+        <v/>
+      </c>
+      <c r="E9" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$B$33*E6*E7</f>
+        <v/>
+      </c>
+      <c r="F9" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$B$33*F6*F7</f>
+        <v/>
+      </c>
+      <c r="G9" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$B$33*G6*G7</f>
+        <v/>
+      </c>
+      <c r="H9" s="76">
+        <f>SUM(C9:G9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Saving: operator NVA time</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C10" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$B$34*Assumptions!$B$28*C6*C7</f>
+        <v/>
+      </c>
+      <c r="D10" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$B$34*Assumptions!$B$28*D6*D7</f>
+        <v/>
+      </c>
+      <c r="E10" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$B$34*Assumptions!$B$28*E6*E7</f>
+        <v/>
+      </c>
+      <c r="F10" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$B$34*Assumptions!$B$28*F6*F7</f>
+        <v/>
+      </c>
+      <c r="G10" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$B$34*Assumptions!$B$28*G6*G7</f>
+        <v/>
+      </c>
+      <c r="H10" s="76">
+        <f>SUM(C10:G10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Saving: energy</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C11" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$B$35*C6*C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$B$35*D6*D7</f>
+        <v/>
+      </c>
+      <c r="E11" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$B$35*E6*E7</f>
+        <v/>
+      </c>
+      <c r="F11" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$B$35*F6*F7</f>
+        <v/>
+      </c>
+      <c r="G11" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$B$35*G6*G7</f>
+        <v/>
+      </c>
+      <c r="H11" s="76">
+        <f>SUM(C11:G11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Saving: variant modification</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C12" s="76">
+        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$36*C6*C7</f>
+        <v/>
+      </c>
+      <c r="D12" s="76">
+        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$36*D6*D7</f>
+        <v/>
+      </c>
+      <c r="E12" s="76">
+        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$36*E6*E7</f>
+        <v/>
+      </c>
+      <c r="F12" s="76">
+        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$36*F6*F7</f>
+        <v/>
+      </c>
+      <c r="G12" s="76">
+        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$36*G6*G7</f>
+        <v/>
+      </c>
+      <c r="H12" s="76">
+        <f>SUM(C12:G12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Total gross savings</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C13" s="79">
+        <f>SUM(C8:C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="79">
+        <f>SUM(D8:D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="79">
+        <f>SUM(E8:E12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="79">
+        <f>SUM(F8:F12)</f>
+        <v/>
+      </c>
+      <c r="G13" s="79">
+        <f>SUM(G8:G12)</f>
+        <v/>
+      </c>
+      <c r="H13" s="79">
+        <f>SUM(C13:G13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Investment (capex)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C14" s="76">
+        <f>Assumptions!$B$37*Assumptions!B$44</f>
+        <v/>
+      </c>
+      <c r="D14" s="76">
+        <f>Assumptions!$B$37*Assumptions!C$44</f>
+        <v/>
+      </c>
+      <c r="E14" s="76">
+        <f>Assumptions!$B$37*Assumptions!D$44</f>
+        <v/>
+      </c>
+      <c r="F14" s="76">
+        <f>Assumptions!$B$37*Assumptions!E$44</f>
+        <v/>
+      </c>
+      <c r="G14" s="76">
+        <f>Assumptions!$B$37*Assumptions!F$44</f>
+        <v/>
+      </c>
+      <c r="H14" s="76">
+        <f>SUM(C14:G14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Cumulative investment</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C15" s="76">
+        <f>SUM($C14:C14)</f>
+        <v/>
+      </c>
+      <c r="D15" s="76">
+        <f>SUM($C14:D14)</f>
+        <v/>
+      </c>
+      <c r="E15" s="76">
+        <f>SUM($C14:E14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="76">
+        <f>SUM($C14:F14)</f>
+        <v/>
+      </c>
+      <c r="G15" s="76">
+        <f>SUM($C14:G14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Running + training cost</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C16" s="76">
+        <f>C15*Assumptions!$B$38+Assumptions!$B$39</f>
+        <v/>
+      </c>
+      <c r="D16" s="76">
+        <f>D15*Assumptions!$B$38+Assumptions!$B$39</f>
+        <v/>
+      </c>
+      <c r="E16" s="76">
+        <f>E15*Assumptions!$B$38+Assumptions!$B$39</f>
+        <v/>
+      </c>
+      <c r="F16" s="76">
+        <f>F15*Assumptions!$B$38+Assumptions!$B$39</f>
+        <v/>
+      </c>
+      <c r="G16" s="76">
+        <f>G15*Assumptions!$B$38+Assumptions!$B$39</f>
+        <v/>
+      </c>
+      <c r="H16" s="76">
+        <f>SUM(C16:G16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Net cash flow</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C17" s="79">
+        <f>C13-C14-C16</f>
+        <v/>
+      </c>
+      <c r="D17" s="79">
+        <f>D13-D14-D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="79">
+        <f>E13-E14-E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="79">
+        <f>F13-F14-F16</f>
+        <v/>
+      </c>
+      <c r="G17" s="79">
+        <f>G13-G14-G16</f>
+        <v/>
+      </c>
+      <c r="H17" s="79">
+        <f>SUM(C17:G17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Discount factor</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C18" s="37">
+        <f>1/(1+Assumptions!$B$9)^Assumptions!B$45</f>
+        <v/>
+      </c>
+      <c r="D18" s="37">
+        <f>1/(1+Assumptions!$B$9)^Assumptions!C$45</f>
+        <v/>
+      </c>
+      <c r="E18" s="37">
+        <f>1/(1+Assumptions!$B$9)^Assumptions!D$45</f>
+        <v/>
+      </c>
+      <c r="F18" s="37">
+        <f>1/(1+Assumptions!$B$9)^Assumptions!E$45</f>
+        <v/>
+      </c>
+      <c r="G18" s="37">
+        <f>1/(1+Assumptions!$B$9)^Assumptions!F$45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Present value</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C19" s="79">
+        <f>C17*C18</f>
+        <v/>
+      </c>
+      <c r="D19" s="79">
+        <f>D17*D18</f>
+        <v/>
+      </c>
+      <c r="E19" s="79">
+        <f>E17*E18</f>
+        <v/>
+      </c>
+      <c r="F19" s="79">
+        <f>F17*F18</f>
+        <v/>
+      </c>
+      <c r="G19" s="79">
+        <f>G17*G18</f>
+        <v/>
+      </c>
+      <c r="H19" s="79">
+        <f>SUM(C19:G19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Cumulative net cash flow</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C20" s="76">
+        <f>SUM($C17:C17)</f>
+        <v/>
+      </c>
+      <c r="D20" s="76">
+        <f>SUM($C17:D17)</f>
+        <v/>
+      </c>
+      <c r="E20" s="76">
+        <f>SUM($C17:E17)</f>
+        <v/>
+      </c>
+      <c r="F20" s="76">
+        <f>SUM($C17:F17)</f>
+        <v/>
+      </c>
+      <c r="G20" s="76">
+        <f>SUM($C17:G17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>Outputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>NPV @ discount rate</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C23" s="79">
+        <f>SUM(C19:G19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>IRR</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C24" s="21">
+        <f>IFERROR(IRR(C17:G17),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Payback year (cumulative net turns positive)</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C25" s="3">
+        <f>IF(G20&lt;0,"Beyond 2030",2026+COUNTIF(C20:G20,"&lt;0"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Full run-rate savings (2025 prices)</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Rp B/yr</t>
+        </is>
+      </c>
+      <c r="C26" s="79">
+        <f>Assumptions!$B$8*(Assumptions!$B$22*Assumptions!B32+Assumptions!$B$20*Assumptions!B33+Assumptions!$B$18*Assumptions!$B$14*Assumptions!B34*Assumptions!$B$28+Assumptions!$B$19*Assumptions!B35)+Assumptions!$B$26*Assumptions!$B$27*Assumptions!B36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Run-rate savings as % of conversion cost</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C27" s="21">
+        <f>C26/Assumptions!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Implied conversion cost index</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="C28" s="53">
+        <f>Assumptions!$B$12*(1-C27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Share of gap to benchmark closed</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C29" s="21">
+        <f>(Assumptions!$B$12-C28)/(Assumptions!$B$12-Assumptions!$B$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>NPV incl. remaining equipment value at end-2030 (book)</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C30" s="79">
+        <f>C23+SUMPRODUCT(C14:G14,(Assumptions!$B$45:$F$45-0.5)/Assumptions!$B$11)/(1+Assumptions!$B$9)^Assumptions!$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="35" t="inlineStr">
+        <is>
+          <t>Scenario: Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Adoption ramp-up</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C34" s="36">
+        <f>Assumptions!B$43</f>
+        <v/>
+      </c>
+      <c r="D34" s="36">
+        <f>Assumptions!C$43</f>
+        <v/>
+      </c>
+      <c r="E34" s="36">
+        <f>Assumptions!D$43</f>
+        <v/>
+      </c>
+      <c r="F34" s="36">
+        <f>Assumptions!E$43</f>
+        <v/>
+      </c>
+      <c r="G34" s="36">
+        <f>Assumptions!F$43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Escalation factor</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C35" s="37">
+        <f>(1+Assumptions!$B$10)^(Assumptions!B$45-1)</f>
+        <v/>
+      </c>
+      <c r="D35" s="37">
+        <f>(1+Assumptions!$B$10)^(Assumptions!C$45-1)</f>
+        <v/>
+      </c>
+      <c r="E35" s="37">
+        <f>(1+Assumptions!$B$10)^(Assumptions!D$45-1)</f>
+        <v/>
+      </c>
+      <c r="F35" s="37">
+        <f>(1+Assumptions!$B$10)^(Assumptions!E$45-1)</f>
+        <v/>
+      </c>
+      <c r="G35" s="37">
+        <f>(1+Assumptions!$B$10)^(Assumptions!F$45-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Saving: scrap</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C36" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$C$32*C34*C35</f>
+        <v/>
+      </c>
+      <c r="D36" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$C$32*D34*D35</f>
+        <v/>
+      </c>
+      <c r="E36" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$C$32*E34*E35</f>
+        <v/>
+      </c>
+      <c r="F36" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$C$32*F34*F35</f>
+        <v/>
+      </c>
+      <c r="G36" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$C$32*G34*G35</f>
+        <v/>
+      </c>
+      <c r="H36" s="76">
+        <f>SUM(C36:G36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Saving: maintenance / downtime</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C37" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$C$33*C34*C35</f>
+        <v/>
+      </c>
+      <c r="D37" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$C$33*D34*D35</f>
+        <v/>
+      </c>
+      <c r="E37" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$C$33*E34*E35</f>
+        <v/>
+      </c>
+      <c r="F37" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$C$33*F34*F35</f>
+        <v/>
+      </c>
+      <c r="G37" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$C$33*G34*G35</f>
+        <v/>
+      </c>
+      <c r="H37" s="76">
+        <f>SUM(C37:G37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Saving: operator NVA time</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C38" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$C$34*Assumptions!$B$28*C34*C35</f>
+        <v/>
+      </c>
+      <c r="D38" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$C$34*Assumptions!$B$28*D34*D35</f>
+        <v/>
+      </c>
+      <c r="E38" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$C$34*Assumptions!$B$28*E34*E35</f>
+        <v/>
+      </c>
+      <c r="F38" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$C$34*Assumptions!$B$28*F34*F35</f>
+        <v/>
+      </c>
+      <c r="G38" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$C$34*Assumptions!$B$28*G34*G35</f>
+        <v/>
+      </c>
+      <c r="H38" s="76">
+        <f>SUM(C38:G38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Saving: energy</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C39" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$C$35*C34*C35</f>
+        <v/>
+      </c>
+      <c r="D39" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$C$35*D34*D35</f>
+        <v/>
+      </c>
+      <c r="E39" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$C$35*E34*E35</f>
+        <v/>
+      </c>
+      <c r="F39" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$C$35*F34*F35</f>
+        <v/>
+      </c>
+      <c r="G39" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$C$35*G34*G35</f>
+        <v/>
+      </c>
+      <c r="H39" s="76">
+        <f>SUM(C39:G39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Saving: variant modification</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C40" s="76">
+        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$C$36*C34*C35</f>
+        <v/>
+      </c>
+      <c r="D40" s="76">
+        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$C$36*D34*D35</f>
+        <v/>
+      </c>
+      <c r="E40" s="76">
+        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$C$36*E34*E35</f>
+        <v/>
+      </c>
+      <c r="F40" s="76">
+        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$C$36*F34*F35</f>
+        <v/>
+      </c>
+      <c r="G40" s="76">
+        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$C$36*G34*G35</f>
+        <v/>
+      </c>
+      <c r="H40" s="76">
+        <f>SUM(C40:G40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Total gross savings</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C41" s="79">
+        <f>SUM(C36:C40)</f>
+        <v/>
+      </c>
+      <c r="D41" s="79">
+        <f>SUM(D36:D40)</f>
+        <v/>
+      </c>
+      <c r="E41" s="79">
+        <f>SUM(E36:E40)</f>
+        <v/>
+      </c>
+      <c r="F41" s="79">
+        <f>SUM(F36:F40)</f>
+        <v/>
+      </c>
+      <c r="G41" s="79">
+        <f>SUM(G36:G40)</f>
+        <v/>
+      </c>
+      <c r="H41" s="79">
+        <f>SUM(C41:G41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Investment (capex)</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C42" s="76">
+        <f>Assumptions!$C$37*Assumptions!B$44</f>
+        <v/>
+      </c>
+      <c r="D42" s="76">
+        <f>Assumptions!$C$37*Assumptions!C$44</f>
+        <v/>
+      </c>
+      <c r="E42" s="76">
+        <f>Assumptions!$C$37*Assumptions!D$44</f>
+        <v/>
+      </c>
+      <c r="F42" s="76">
+        <f>Assumptions!$C$37*Assumptions!E$44</f>
+        <v/>
+      </c>
+      <c r="G42" s="76">
+        <f>Assumptions!$C$37*Assumptions!F$44</f>
+        <v/>
+      </c>
+      <c r="H42" s="76">
+        <f>SUM(C42:G42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Cumulative investment</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C43" s="76">
+        <f>SUM($C42:C42)</f>
+        <v/>
+      </c>
+      <c r="D43" s="76">
+        <f>SUM($C42:D42)</f>
+        <v/>
+      </c>
+      <c r="E43" s="76">
+        <f>SUM($C42:E42)</f>
+        <v/>
+      </c>
+      <c r="F43" s="76">
+        <f>SUM($C42:F42)</f>
+        <v/>
+      </c>
+      <c r="G43" s="76">
+        <f>SUM($C42:G42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Running + training cost</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C44" s="76">
+        <f>C43*Assumptions!$C$38+Assumptions!$C$39</f>
+        <v/>
+      </c>
+      <c r="D44" s="76">
+        <f>D43*Assumptions!$C$38+Assumptions!$C$39</f>
+        <v/>
+      </c>
+      <c r="E44" s="76">
+        <f>E43*Assumptions!$C$38+Assumptions!$C$39</f>
+        <v/>
+      </c>
+      <c r="F44" s="76">
+        <f>F43*Assumptions!$C$38+Assumptions!$C$39</f>
+        <v/>
+      </c>
+      <c r="G44" s="76">
+        <f>G43*Assumptions!$C$38+Assumptions!$C$39</f>
+        <v/>
+      </c>
+      <c r="H44" s="76">
+        <f>SUM(C44:G44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Net cash flow</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C45" s="79">
+        <f>C41-C42-C44</f>
+        <v/>
+      </c>
+      <c r="D45" s="79">
+        <f>D41-D42-D44</f>
+        <v/>
+      </c>
+      <c r="E45" s="79">
+        <f>E41-E42-E44</f>
+        <v/>
+      </c>
+      <c r="F45" s="79">
+        <f>F41-F42-F44</f>
+        <v/>
+      </c>
+      <c r="G45" s="79">
+        <f>G41-G42-G44</f>
+        <v/>
+      </c>
+      <c r="H45" s="79">
+        <f>SUM(C45:G45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Discount factor</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C46" s="37">
+        <f>1/(1+Assumptions!$B$9)^Assumptions!B$45</f>
+        <v/>
+      </c>
+      <c r="D46" s="37">
+        <f>1/(1+Assumptions!$B$9)^Assumptions!C$45</f>
+        <v/>
+      </c>
+      <c r="E46" s="37">
+        <f>1/(1+Assumptions!$B$9)^Assumptions!D$45</f>
+        <v/>
+      </c>
+      <c r="F46" s="37">
+        <f>1/(1+Assumptions!$B$9)^Assumptions!E$45</f>
+        <v/>
+      </c>
+      <c r="G46" s="37">
+        <f>1/(1+Assumptions!$B$9)^Assumptions!F$45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Present value</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C47" s="79">
+        <f>C45*C46</f>
+        <v/>
+      </c>
+      <c r="D47" s="79">
+        <f>D45*D46</f>
+        <v/>
+      </c>
+      <c r="E47" s="79">
+        <f>E45*E46</f>
+        <v/>
+      </c>
+      <c r="F47" s="79">
+        <f>F45*F46</f>
+        <v/>
+      </c>
+      <c r="G47" s="79">
+        <f>G45*G46</f>
+        <v/>
+      </c>
+      <c r="H47" s="79">
+        <f>SUM(C47:G47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Cumulative net cash flow</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C48" s="76">
+        <f>SUM($C45:C45)</f>
+        <v/>
+      </c>
+      <c r="D48" s="76">
+        <f>SUM($C45:D45)</f>
+        <v/>
+      </c>
+      <c r="E48" s="76">
+        <f>SUM($C45:E45)</f>
+        <v/>
+      </c>
+      <c r="F48" s="76">
+        <f>SUM($C45:F45)</f>
+        <v/>
+      </c>
+      <c r="G48" s="76">
+        <f>SUM($C45:G45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>Outputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>NPV @ discount rate</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C51" s="79">
+        <f>SUM(C47:G47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>IRR</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C52" s="21">
+        <f>IFERROR(IRR(C45:G45),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Payback year (cumulative net turns positive)</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C53" s="3">
+        <f>IF(G48&lt;0,"Beyond 2030",2026+COUNTIF(C48:G48,"&lt;0"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Full run-rate savings (2025 prices)</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Rp B/yr</t>
+        </is>
+      </c>
+      <c r="C54" s="79">
+        <f>Assumptions!$B$8*(Assumptions!$B$22*Assumptions!C32+Assumptions!$B$20*Assumptions!C33+Assumptions!$B$18*Assumptions!$B$14*Assumptions!C34*Assumptions!$B$28+Assumptions!$B$19*Assumptions!C35)+Assumptions!$B$26*Assumptions!$B$27*Assumptions!C36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Run-rate savings as % of conversion cost</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C55" s="21">
+        <f>C54/Assumptions!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Implied conversion cost index</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="C56" s="53">
+        <f>Assumptions!$B$12*(1-C55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Share of gap to benchmark closed</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C57" s="21">
+        <f>(Assumptions!$B$12-C56)/(Assumptions!$B$12-Assumptions!$B$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>NPV incl. remaining equipment value at end-2030 (book)</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C58" s="79">
+        <f>C51+SUMPRODUCT(C42:G42,(Assumptions!$B$45:$F$45-0.5)/Assumptions!$B$11)/(1+Assumptions!$B$9)^Assumptions!$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="35" t="inlineStr">
+        <is>
+          <t>Scenario: Optimistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Adoption ramp-up</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C62" s="36">
+        <f>Assumptions!B$43</f>
+        <v/>
+      </c>
+      <c r="D62" s="36">
+        <f>Assumptions!C$43</f>
+        <v/>
+      </c>
+      <c r="E62" s="36">
+        <f>Assumptions!D$43</f>
+        <v/>
+      </c>
+      <c r="F62" s="36">
+        <f>Assumptions!E$43</f>
+        <v/>
+      </c>
+      <c r="G62" s="36">
+        <f>Assumptions!F$43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Escalation factor</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C63" s="37">
+        <f>(1+Assumptions!$B$10)^(Assumptions!B$45-1)</f>
+        <v/>
+      </c>
+      <c r="D63" s="37">
+        <f>(1+Assumptions!$B$10)^(Assumptions!C$45-1)</f>
+        <v/>
+      </c>
+      <c r="E63" s="37">
+        <f>(1+Assumptions!$B$10)^(Assumptions!D$45-1)</f>
+        <v/>
+      </c>
+      <c r="F63" s="37">
+        <f>(1+Assumptions!$B$10)^(Assumptions!E$45-1)</f>
+        <v/>
+      </c>
+      <c r="G63" s="37">
+        <f>(1+Assumptions!$B$10)^(Assumptions!F$45-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Saving: scrap</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C64" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$D$32*C62*C63</f>
+        <v/>
+      </c>
+      <c r="D64" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$D$32*D62*D63</f>
+        <v/>
+      </c>
+      <c r="E64" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$D$32*E62*E63</f>
+        <v/>
+      </c>
+      <c r="F64" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$D$32*F62*F63</f>
+        <v/>
+      </c>
+      <c r="G64" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$D$32*G62*G63</f>
+        <v/>
+      </c>
+      <c r="H64" s="76">
+        <f>SUM(C64:G64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Saving: maintenance / downtime</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C65" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$D$33*C62*C63</f>
+        <v/>
+      </c>
+      <c r="D65" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$D$33*D62*D63</f>
+        <v/>
+      </c>
+      <c r="E65" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$D$33*E62*E63</f>
+        <v/>
+      </c>
+      <c r="F65" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$D$33*F62*F63</f>
+        <v/>
+      </c>
+      <c r="G65" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$D$33*G62*G63</f>
+        <v/>
+      </c>
+      <c r="H65" s="76">
+        <f>SUM(C65:G65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Saving: operator NVA time</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C66" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$D$34*Assumptions!$B$28*C62*C63</f>
+        <v/>
+      </c>
+      <c r="D66" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$D$34*Assumptions!$B$28*D62*D63</f>
+        <v/>
+      </c>
+      <c r="E66" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$D$34*Assumptions!$B$28*E62*E63</f>
+        <v/>
+      </c>
+      <c r="F66" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$D$34*Assumptions!$B$28*F62*F63</f>
+        <v/>
+      </c>
+      <c r="G66" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$D$34*Assumptions!$B$28*G62*G63</f>
+        <v/>
+      </c>
+      <c r="H66" s="76">
+        <f>SUM(C66:G66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Saving: energy</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C67" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$D$35*C62*C63</f>
+        <v/>
+      </c>
+      <c r="D67" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$D$35*D62*D63</f>
+        <v/>
+      </c>
+      <c r="E67" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$D$35*E62*E63</f>
+        <v/>
+      </c>
+      <c r="F67" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$D$35*F62*F63</f>
+        <v/>
+      </c>
+      <c r="G67" s="76">
+        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$D$35*G62*G63</f>
+        <v/>
+      </c>
+      <c r="H67" s="76">
+        <f>SUM(C67:G67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Saving: variant modification</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C68" s="76">
+        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$D$36*C62*C63</f>
+        <v/>
+      </c>
+      <c r="D68" s="76">
+        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$D$36*D62*D63</f>
+        <v/>
+      </c>
+      <c r="E68" s="76">
+        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$D$36*E62*E63</f>
+        <v/>
+      </c>
+      <c r="F68" s="76">
+        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$D$36*F62*F63</f>
+        <v/>
+      </c>
+      <c r="G68" s="76">
+        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$D$36*G62*G63</f>
+        <v/>
+      </c>
+      <c r="H68" s="76">
+        <f>SUM(C68:G68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Total gross savings</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C69" s="79">
+        <f>SUM(C64:C68)</f>
+        <v/>
+      </c>
+      <c r="D69" s="79">
+        <f>SUM(D64:D68)</f>
+        <v/>
+      </c>
+      <c r="E69" s="79">
+        <f>SUM(E64:E68)</f>
+        <v/>
+      </c>
+      <c r="F69" s="79">
+        <f>SUM(F64:F68)</f>
+        <v/>
+      </c>
+      <c r="G69" s="79">
+        <f>SUM(G64:G68)</f>
+        <v/>
+      </c>
+      <c r="H69" s="79">
+        <f>SUM(C69:G69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Investment (capex)</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C70" s="76">
+        <f>Assumptions!$D$37*Assumptions!B$44</f>
+        <v/>
+      </c>
+      <c r="D70" s="76">
+        <f>Assumptions!$D$37*Assumptions!C$44</f>
+        <v/>
+      </c>
+      <c r="E70" s="76">
+        <f>Assumptions!$D$37*Assumptions!D$44</f>
+        <v/>
+      </c>
+      <c r="F70" s="76">
+        <f>Assumptions!$D$37*Assumptions!E$44</f>
+        <v/>
+      </c>
+      <c r="G70" s="76">
+        <f>Assumptions!$D$37*Assumptions!F$44</f>
+        <v/>
+      </c>
+      <c r="H70" s="76">
+        <f>SUM(C70:G70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Cumulative investment</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C71" s="76">
+        <f>SUM($C70:C70)</f>
+        <v/>
+      </c>
+      <c r="D71" s="76">
+        <f>SUM($C70:D70)</f>
+        <v/>
+      </c>
+      <c r="E71" s="76">
+        <f>SUM($C70:E70)</f>
+        <v/>
+      </c>
+      <c r="F71" s="76">
+        <f>SUM($C70:F70)</f>
+        <v/>
+      </c>
+      <c r="G71" s="76">
+        <f>SUM($C70:G70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Running + training cost</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C72" s="76">
+        <f>C71*Assumptions!$D$38+Assumptions!$D$39</f>
+        <v/>
+      </c>
+      <c r="D72" s="76">
+        <f>D71*Assumptions!$D$38+Assumptions!$D$39</f>
+        <v/>
+      </c>
+      <c r="E72" s="76">
+        <f>E71*Assumptions!$D$38+Assumptions!$D$39</f>
+        <v/>
+      </c>
+      <c r="F72" s="76">
+        <f>F71*Assumptions!$D$38+Assumptions!$D$39</f>
+        <v/>
+      </c>
+      <c r="G72" s="76">
+        <f>G71*Assumptions!$D$38+Assumptions!$D$39</f>
+        <v/>
+      </c>
+      <c r="H72" s="76">
+        <f>SUM(C72:G72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Net cash flow</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C73" s="79">
+        <f>C69-C70-C72</f>
+        <v/>
+      </c>
+      <c r="D73" s="79">
+        <f>D69-D70-D72</f>
+        <v/>
+      </c>
+      <c r="E73" s="79">
+        <f>E69-E70-E72</f>
+        <v/>
+      </c>
+      <c r="F73" s="79">
+        <f>F69-F70-F72</f>
+        <v/>
+      </c>
+      <c r="G73" s="79">
+        <f>G69-G70-G72</f>
+        <v/>
+      </c>
+      <c r="H73" s="79">
+        <f>SUM(C73:G73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Discount factor</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C74" s="37">
+        <f>1/(1+Assumptions!$B$9)^Assumptions!B$45</f>
+        <v/>
+      </c>
+      <c r="D74" s="37">
+        <f>1/(1+Assumptions!$B$9)^Assumptions!C$45</f>
+        <v/>
+      </c>
+      <c r="E74" s="37">
+        <f>1/(1+Assumptions!$B$9)^Assumptions!D$45</f>
+        <v/>
+      </c>
+      <c r="F74" s="37">
+        <f>1/(1+Assumptions!$B$9)^Assumptions!E$45</f>
+        <v/>
+      </c>
+      <c r="G74" s="37">
+        <f>1/(1+Assumptions!$B$9)^Assumptions!F$45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Present value</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C75" s="79">
+        <f>C73*C74</f>
+        <v/>
+      </c>
+      <c r="D75" s="79">
+        <f>D73*D74</f>
+        <v/>
+      </c>
+      <c r="E75" s="79">
+        <f>E73*E74</f>
+        <v/>
+      </c>
+      <c r="F75" s="79">
+        <f>F73*F74</f>
+        <v/>
+      </c>
+      <c r="G75" s="79">
+        <f>G73*G74</f>
+        <v/>
+      </c>
+      <c r="H75" s="79">
+        <f>SUM(C75:G75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Cumulative net cash flow</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C76" s="76">
+        <f>SUM($C73:C73)</f>
+        <v/>
+      </c>
+      <c r="D76" s="76">
+        <f>SUM($C73:D73)</f>
+        <v/>
+      </c>
+      <c r="E76" s="76">
+        <f>SUM($C73:E73)</f>
+        <v/>
+      </c>
+      <c r="F76" s="76">
+        <f>SUM($C73:F73)</f>
+        <v/>
+      </c>
+      <c r="G76" s="76">
+        <f>SUM($C73:G73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="16" t="inlineStr">
+        <is>
+          <t>Outputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>NPV @ discount rate</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C79" s="79">
+        <f>SUM(C75:G75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>IRR</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C80" s="21">
+        <f>IFERROR(IRR(C73:G73),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Payback year (cumulative net turns positive)</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C81" s="3">
+        <f>IF(G76&lt;0,"Beyond 2030",2026+COUNTIF(C76:G76,"&lt;0"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Full run-rate savings (2025 prices)</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Rp B/yr</t>
+        </is>
+      </c>
+      <c r="C82" s="79">
+        <f>Assumptions!$B$8*(Assumptions!$B$22*Assumptions!D32+Assumptions!$B$20*Assumptions!D33+Assumptions!$B$18*Assumptions!$B$14*Assumptions!D34*Assumptions!$B$28+Assumptions!$B$19*Assumptions!D35)+Assumptions!$B$26*Assumptions!$B$27*Assumptions!D36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Run-rate savings as % of conversion cost</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C83" s="21">
+        <f>C82/Assumptions!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Implied conversion cost index</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="C84" s="53">
+        <f>Assumptions!$B$12*(1-C83)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Share of gap to benchmark closed</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C85" s="21">
+        <f>(Assumptions!$B$12-C84)/(Assumptions!$B$12-Assumptions!$B$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>NPV incl. remaining equipment value at end-2030 (book)</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Rp B</t>
+        </is>
+      </c>
+      <c r="C86" s="79">
+        <f>C79+SUMPRODUCT(C70:G70,(Assumptions!$B$45:$F$45-0.5)/Assumptions!$B$11)/(1+Assumptions!$B$9)^Assumptions!$B$11</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Financial summary for the deck (Rp billion)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Optimistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>NPV (10%)</t>
+        </is>
+      </c>
+      <c r="B4" s="80">
+        <f>Model!C23</f>
+        <v/>
+      </c>
+      <c r="C4" s="80">
+        <f>Model!C51</f>
+        <v/>
+      </c>
+      <c r="D4" s="80">
+        <f>Model!C79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>IRR</t>
+        </is>
+      </c>
+      <c r="B5" s="36">
+        <f>Model!C24</f>
+        <v/>
+      </c>
+      <c r="C5" s="36">
+        <f>Model!C52</f>
+        <v/>
+      </c>
+      <c r="D5" s="36">
+        <f>Model!C80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Payback year</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>Model!C25</f>
+        <v/>
+      </c>
+      <c r="C6" s="5">
+        <f>Model!C53</f>
+        <v/>
+      </c>
+      <c r="D6" s="5">
+        <f>Model!C81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Gross savings in 2030</t>
+        </is>
+      </c>
+      <c r="B7" s="80">
+        <f>Model!G13</f>
+        <v/>
+      </c>
+      <c r="C7" s="80">
+        <f>Model!G41</f>
+        <v/>
+      </c>
+      <c r="D7" s="80">
+        <f>Model!G69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Full run-rate savings / yr</t>
+        </is>
+      </c>
+      <c r="B8" s="80">
+        <f>Model!C26</f>
+        <v/>
+      </c>
+      <c r="C8" s="80">
+        <f>Model!C54</f>
+        <v/>
+      </c>
+      <c r="D8" s="80">
+        <f>Model!C82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Run-rate as % of conversion cost</t>
+        </is>
+      </c>
+      <c r="B9" s="36">
+        <f>Model!C27</f>
+        <v/>
+      </c>
+      <c r="C9" s="36">
+        <f>Model!C55</f>
+        <v/>
+      </c>
+      <c r="D9" s="36">
+        <f>Model!C83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Implied cost index (today 106)</t>
+        </is>
+      </c>
+      <c r="B10" s="81">
+        <f>Model!C28</f>
+        <v/>
+      </c>
+      <c r="C10" s="81">
+        <f>Model!C56</f>
+        <v/>
+      </c>
+      <c r="D10" s="81">
+        <f>Model!C84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Gap to new-player benchmark closed</t>
+        </is>
+      </c>
+      <c r="B11" s="36">
+        <f>Model!C29</f>
+        <v/>
+      </c>
+      <c r="C11" s="36">
+        <f>Model!C57</f>
+        <v/>
+      </c>
+      <c r="D11" s="36">
+        <f>Model!C85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>NPV incl. remaining equipment value</t>
+        </is>
+      </c>
+      <c r="B12" s="80">
+        <f>Model!C30</f>
+        <v/>
+      </c>
+      <c r="C12" s="80">
+        <f>Model!C58</f>
+        <v/>
+      </c>
+      <c r="D12" s="80">
+        <f>Model!C86</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Investment (Rp B)</t>
+        </is>
+      </c>
+      <c r="B13" s="80">
+        <f>Assumptions!B37</f>
+        <v/>
+      </c>
+      <c r="C13" s="80">
+        <f>Assumptions!C37</f>
+        <v/>
+      </c>
+      <c r="D13" s="80">
+        <f>Assumptions!D37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Variant modification time (months, today 9)</t>
+        </is>
+      </c>
+      <c r="B14" s="81">
+        <f>Assumptions!B40</f>
+        <v/>
+      </c>
+      <c r="C14" s="81">
+        <f>Assumptions!C40</f>
+        <v/>
+      </c>
+      <c r="D14" s="81">
+        <f>Assumptions!D40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Note: with pilot-light phasing the 2026 outflow is small, so IRR looks extreme. Lead with NPV and P(NPV&gt;0) from the Simulation tab, not IRR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Base case savings by lever</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Scrap</t>
+        </is>
+      </c>
+      <c r="B17" s="80">
+        <f>Model!C36</f>
+        <v/>
+      </c>
+      <c r="C17" s="80">
+        <f>Model!D36</f>
+        <v/>
+      </c>
+      <c r="D17" s="80">
+        <f>Model!E36</f>
+        <v/>
+      </c>
+      <c r="E17" s="80">
+        <f>Model!F36</f>
+        <v/>
+      </c>
+      <c r="F17" s="80">
+        <f>Model!G36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B18" s="80">
+        <f>Model!C37</f>
+        <v/>
+      </c>
+      <c r="C18" s="80">
+        <f>Model!D37</f>
+        <v/>
+      </c>
+      <c r="D18" s="80">
+        <f>Model!E37</f>
+        <v/>
+      </c>
+      <c r="E18" s="80">
+        <f>Model!F37</f>
+        <v/>
+      </c>
+      <c r="F18" s="80">
+        <f>Model!G37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Operator NVA</t>
+        </is>
+      </c>
+      <c r="B19" s="80">
+        <f>Model!C38</f>
+        <v/>
+      </c>
+      <c r="C19" s="80">
+        <f>Model!D38</f>
+        <v/>
+      </c>
+      <c r="D19" s="80">
+        <f>Model!E38</f>
+        <v/>
+      </c>
+      <c r="E19" s="80">
+        <f>Model!F38</f>
+        <v/>
+      </c>
+      <c r="F19" s="80">
+        <f>Model!G38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="B20" s="80">
+        <f>Model!C39</f>
+        <v/>
+      </c>
+      <c r="C20" s="80">
+        <f>Model!D39</f>
+        <v/>
+      </c>
+      <c r="D20" s="80">
+        <f>Model!E39</f>
+        <v/>
+      </c>
+      <c r="E20" s="80">
+        <f>Model!F39</f>
+        <v/>
+      </c>
+      <c r="F20" s="80">
+        <f>Model!G39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Variant modification</t>
+        </is>
+      </c>
+      <c r="B21" s="80">
+        <f>Model!C40</f>
+        <v/>
+      </c>
+      <c r="C21" s="80">
+        <f>Model!D40</f>
+        <v/>
+      </c>
+      <c r="D21" s="80">
+        <f>Model!E40</f>
+        <v/>
+      </c>
+      <c r="E21" s="80">
+        <f>Model!F40</f>
+        <v/>
+      </c>
+      <c r="F21" s="80">
+        <f>Model!G40</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1883,7 +4866,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2756,7 +5739,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3327,7 +6310,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3717,7 +6700,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4169,7 +7152,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11314,6 +14297,2736 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H104"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Idea tests: simulation results (values produced by run_tests.py, not formulas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="54" t="inlineStr">
+        <is>
+          <t>Re-run run_tests.py after changing assumptions. Process parameters below are illustrative assumptions, not TMMIN data: present them as a mechanism test, and show the sensitivity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>TEST 1. Does closing the quality loop beat adding technology alone? (sealer drift -&gt; inspection -&gt; feedback, 1 year, 175,000 units, 300 runs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="55" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>Defective units / yr</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>Scrapped units / yr</t>
+        </is>
+      </c>
+      <c r="D5" s="55" t="inlineStr">
+        <is>
+          <t>Escaped defects / yr</t>
+        </is>
+      </c>
+      <c r="E5" s="55" t="inlineStr">
+        <is>
+          <t>Units built while drifting</t>
+        </is>
+      </c>
+      <c r="F5" s="55" t="inlineStr">
+        <is>
+          <t>Scrap vs today</t>
+        </is>
+      </c>
+      <c r="G5" s="55" t="inlineStr">
+        <is>
+          <t>Escapes vs today</t>
+        </is>
+      </c>
+      <c r="H5" s="55" t="inlineStr">
+        <is>
+          <t>Scrap P5-P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="56" t="inlineStr">
+        <is>
+          <t>1. Today: visual at final inspection, manual feedback</t>
+        </is>
+      </c>
+      <c r="B6" s="57" t="n">
+        <v>4266.68</v>
+      </c>
+      <c r="C6" s="57" t="n">
+        <v>1088.524</v>
+      </c>
+      <c r="D6" s="57" t="n">
+        <v>638.2666666666667</v>
+      </c>
+      <c r="E6" s="57" t="n">
+        <v>15796.09333333333</v>
+      </c>
+      <c r="F6" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="57" t="inlineStr">
+        <is>
+          <t>835 - 1,365</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="56" t="inlineStr">
+        <is>
+          <t>2. Better camera at end-of-line only (tech, no loop)</t>
+        </is>
+      </c>
+      <c r="B7" s="57" t="n">
+        <v>4265.323333333334</v>
+      </c>
+      <c r="C7" s="57" t="n">
+        <v>1215.776</v>
+      </c>
+      <c r="D7" s="57" t="n">
+        <v>212.7366666666667</v>
+      </c>
+      <c r="E7" s="57" t="n">
+        <v>15793.25666666667</v>
+      </c>
+      <c r="F7" s="58" t="n">
+        <v>0.1169032561523677</v>
+      </c>
+      <c r="G7" s="58" t="n">
+        <v>-0.6666962607060789</v>
+      </c>
+      <c r="H7" s="57" t="inlineStr">
+        <is>
+          <t>910 - 1,492</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="56" t="inlineStr">
+        <is>
+          <t>3. Closed loop at sealer, 31% of alerts dismissed (as today)</t>
+        </is>
+      </c>
+      <c r="B8" s="57" t="n">
+        <v>1652.95</v>
+      </c>
+      <c r="C8" s="57" t="n">
+        <v>362.1536666666667</v>
+      </c>
+      <c r="D8" s="57" t="n">
+        <v>203.26</v>
+      </c>
+      <c r="E8" s="57" t="n">
+        <v>5247.72</v>
+      </c>
+      <c r="F8" s="58" t="n">
+        <v>-0.6672984089770491</v>
+      </c>
+      <c r="G8" s="58" t="n">
+        <v>-0.6815437643618132</v>
+      </c>
+      <c r="H8" s="57" t="inlineStr">
+        <is>
+          <t>216 - 543</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="59" t="inlineStr">
+        <is>
+          <t>4. Closed loop with people-centred design (10% dismissed)</t>
+        </is>
+      </c>
+      <c r="B9" s="60" t="n">
+        <v>908.3233333333334</v>
+      </c>
+      <c r="C9" s="60" t="n">
+        <v>166.8633333333333</v>
+      </c>
+      <c r="D9" s="60" t="n">
+        <v>88.00666666666666</v>
+      </c>
+      <c r="E9" s="60" t="n">
+        <v>2257.006666666667</v>
+      </c>
+      <c r="F9" s="61" t="n">
+        <v>-0.8467067943992661</v>
+      </c>
+      <c r="G9" s="61" t="n">
+        <v>-0.862116147900564</v>
+      </c>
+      <c r="H9" s="60" t="inlineStr">
+        <is>
+          <t>83 - 270</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>What this shows</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="62" t="inlineStr">
+        <is>
+          <t>- A better camera at end-of-line alone changes scrap by +12% while escapes fall 67%: it catches more bad units, but too late, so escapes turn into scrap. It does not prevent defects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="62" t="inlineStr">
+        <is>
+          <t>- Closing the loop right after the sealer cuts scrap 85% and escapes 86%, because a drift is stopped within a few units instead of hundreds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="62" t="inlineStr">
+        <is>
+          <t>- If operators dismiss alerts in 31% of drift episodes (today's override rate), scrap reduction falls to 67%. Trust, training and alert design are part of the value, not an add-on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="62" t="inlineStr">
+        <is>
+          <t>- Plant-wide: if the pilot scope causes 40% of plant scrap (team assumption), the plant-wide scrap cut is about 34%. Compare with the 20% / 35% / 50% lever in Assumptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="62" t="inlineStr">
+        <is>
+          <t>- Deck message: value comes from redesigning the system (where the check sits, how fast the signal travels, who acts on it), not from buying the device. That is exactly the case ask.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Process assumptions used (illustrative, change and re-run)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="54" t="inlineStr">
+        <is>
+          <t>Defect probability per unit, stable sealer</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="54" t="inlineStr">
+        <is>
+          <t>Average units between drift events</t>
+        </is>
+      </c>
+      <c r="B20" s="63" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="54" t="inlineStr">
+        <is>
+          <t>Defect probability per unit while drifting</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="54" t="inlineStr">
+        <is>
+          <t>Manual visual detection rate at final inspection</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="54" t="inlineStr">
+        <is>
+          <t>Share of sealer defect modes the in-line AI camera can see</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="54" t="inlineStr">
+        <is>
+          <t>Units between sealer and today's final inspection</t>
+        </is>
+      </c>
+      <c r="B24" s="63" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="54" t="inlineStr">
+        <is>
+          <t>Units built before manual feedback reaches the sealer</t>
+        </is>
+      </c>
+      <c r="B25" s="63" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="54" t="inlineStr">
+        <is>
+          <t>Share of late-found defects scrapped</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="54" t="inlineStr">
+        <is>
+          <t>Share of early-found defects scrapped</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="54" t="inlineStr">
+        <is>
+          <t>Share of plant scrap from the pilot scope (team assumption)</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="62" t="inlineStr">
+        <is>
+          <t>In-line check: 5 units after sealer, automatic feedback within 10 units, 90% detection on visible defect modes (case: AI camera in validation to Oct 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Robustness: closed-loop (scenario 4) scrap reduction vs today when each assumption changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="55" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="B32" s="55" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C32" s="55" t="inlineStr">
+        <is>
+          <t>Reduction</t>
+        </is>
+      </c>
+      <c r="D32" s="55" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E32" s="55" t="inlineStr">
+        <is>
+          <t>Reduction</t>
+        </is>
+      </c>
+      <c r="F32" s="55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G32" s="55" t="inlineStr">
+        <is>
+          <t>Reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>AI camera coverage of defect modes</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C33" s="64" t="n">
+        <v>0.8247043005741556</v>
+      </c>
+      <c r="D33" s="20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E33" s="64" t="n">
+        <v>0.8468422609923756</v>
+      </c>
+      <c r="F33" s="20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G33" s="64" t="n">
+        <v>0.8667088181512177</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Drift defect rate</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C34" s="64" t="n">
+        <v>0.8026017993273447</v>
+      </c>
+      <c r="D34" s="20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E34" s="64" t="n">
+        <v>0.8479906256107048</v>
+      </c>
+      <c r="F34" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G34" s="64" t="n">
+        <v>0.8649243431242232</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Units between drift events</t>
+        </is>
+      </c>
+      <c r="B35" s="63" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C35" s="64" t="n">
+        <v>0.8634074536698797</v>
+      </c>
+      <c r="D35" s="63" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E35" s="64" t="n">
+        <v>0.8582510378017658</v>
+      </c>
+      <c r="F35" s="63" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G35" s="64" t="n">
+        <v>0.8336816505910225</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Late-found scrap share</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C36" s="64" t="n">
+        <v>0.8314626883200975</v>
+      </c>
+      <c r="D36" s="20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E36" s="64" t="n">
+        <v>0.8538779573335564</v>
+      </c>
+      <c r="F36" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G36" s="64" t="n">
+        <v>0.8501771115300518</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Units from sealer to today's inspection</t>
+        </is>
+      </c>
+      <c r="B37" s="63" t="n">
+        <v>100</v>
+      </c>
+      <c r="C37" s="64" t="n">
+        <v>0.8111230466252334</v>
+      </c>
+      <c r="D37" s="63" t="n">
+        <v>300</v>
+      </c>
+      <c r="E37" s="64" t="n">
+        <v>0.8492533988756621</v>
+      </c>
+      <c r="F37" s="63" t="n">
+        <v>600</v>
+      </c>
+      <c r="G37" s="64" t="n">
+        <v>0.8737976071910339</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Lowest scrap reduction across all tested cases: 80%. The mechanism holds even with pessimistic process assumptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>People test: how much value is lost when operators dismiss alerts?</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="55" t="inlineStr">
+        <is>
+          <t>Share of drift episodes where alerts are dismissed</t>
+        </is>
+      </c>
+      <c r="B41" s="55" t="inlineStr">
+        <is>
+          <t>Scrap reduction vs today</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="B42" s="64" t="n">
+        <v>0.9392930243154951</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B43" s="64" t="n">
+        <v>0.8445760803926541</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B44" s="64" t="n">
+        <v>0.7497194978398884</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="B45" s="64" t="n">
+        <v>0.6431060163426193</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B46" s="64" t="n">
+        <v>0.4964125733562145</v>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="62" t="inlineStr">
+        <is>
+          <t>Exhibit 6B says 31% of operators frequently override alerts today. This chart is the quantified case for the people part of the idea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>TEST 2. Is the business case robust? Financial Monte Carlo (10,000 runs, mirrors the Model tab incl. pilot-light phasing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="55" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B50" s="55" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C50" s="55" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Deterministic base NPV (check vs Model tab)</t>
+        </is>
+      </c>
+      <c r="B51" s="65" t="n">
+        <v>27.01403870465879</v>
+      </c>
+      <c r="C51" s="54" t="inlineStr">
+        <is>
+          <t>Should match Dashboard base NPV</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Mean NPV</t>
+        </is>
+      </c>
+      <c r="B52" s="65" t="n">
+        <v>11.82360761131173</v>
+      </c>
+      <c r="C52" s="54" t="inlineStr">
+        <is>
+          <t>Rp billion</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>P5 NPV (bad case)</t>
+        </is>
+      </c>
+      <c r="B53" s="65" t="n">
+        <v>-19.41291040060244</v>
+      </c>
+      <c r="C53" s="54" t="inlineStr">
+        <is>
+          <t>1-in-20 downside</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Median NPV</t>
+        </is>
+      </c>
+      <c r="B54" s="65" t="n">
+        <v>11.7084469092985</v>
+      </c>
+      <c r="C54" s="54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>P95 NPV (good case)</t>
+        </is>
+      </c>
+      <c r="B55" s="65" t="n">
+        <v>43.10332192077205</v>
+      </c>
+      <c r="C55" s="54" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Probability NPV &gt; 0</t>
+        </is>
+      </c>
+      <c r="B56" s="64" t="n">
+        <v>0.7311</v>
+      </c>
+      <c r="C56" s="54" t="inlineStr">
+        <is>
+          <t>Headline for the financial slide</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Median full run-rate savings (Rp B/yr)</t>
+        </is>
+      </c>
+      <c r="B57" s="65" t="n">
+        <v>49.0844126012166</v>
+      </c>
+      <c r="C57" s="54" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Median run-rate as % of conversion cost</t>
+        </is>
+      </c>
+      <c r="B58" s="64" t="n">
+        <v>0.08765073678788678</v>
+      </c>
+      <c r="C58" s="54" t="inlineStr">
+        <is>
+          <t>vs 16% gap to benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>TEST 2b. How should the roadmap spend the money? Same 10,000 runs, five strategies (gate = stop scaling if 2027 pilot adoption &lt; 80%; happens in 25% of runs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="55" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="B61" s="55" t="inlineStr">
+        <is>
+          <t>Mean NPV</t>
+        </is>
+      </c>
+      <c r="C61" s="55" t="inlineStr">
+        <is>
+          <t>P5 NPV</t>
+        </is>
+      </c>
+      <c r="D61" s="55" t="inlineStr">
+        <is>
+          <t>Median NPV</t>
+        </is>
+      </c>
+      <c r="E61" s="55" t="inlineStr">
+        <is>
+          <t>P95 NPV</t>
+        </is>
+      </c>
+      <c r="F61" s="55" t="inlineStr">
+        <is>
+          <t>P(NPV &gt; 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="66" t="inlineStr">
+        <is>
+          <t>A. Front-loaded phasing, no gate</t>
+        </is>
+      </c>
+      <c r="B62" s="67" t="n">
+        <v>-0.191332294676973</v>
+      </c>
+      <c r="C62" s="67" t="n">
+        <v>-32.83255089311962</v>
+      </c>
+      <c r="D62" s="67" t="n">
+        <v>-0.3737217276611755</v>
+      </c>
+      <c r="E62" s="67" t="n">
+        <v>32.5044161216826</v>
+      </c>
+      <c r="F62" s="58" t="n">
+        <v>0.4925</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="66" t="inlineStr">
+        <is>
+          <t>B. Front-loaded phasing + gate (65% already spent)</t>
+        </is>
+      </c>
+      <c r="B63" s="67" t="n">
+        <v>-3.79967892697686</v>
+      </c>
+      <c r="C63" s="67" t="n">
+        <v>-39.74590657971964</v>
+      </c>
+      <c r="D63" s="67" t="n">
+        <v>-2.962350007986172</v>
+      </c>
+      <c r="E63" s="67" t="n">
+        <v>32.40194504032392</v>
+      </c>
+      <c r="F63" s="58" t="n">
+        <v>0.4518</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="66" t="inlineStr">
+        <is>
+          <t>C. Pilot-light phasing, no gate (as in Model tab)</t>
+        </is>
+      </c>
+      <c r="B64" s="67" t="n">
+        <v>11.82360761131173</v>
+      </c>
+      <c r="C64" s="67" t="n">
+        <v>-19.41291040060244</v>
+      </c>
+      <c r="D64" s="67" t="n">
+        <v>11.7084469092985</v>
+      </c>
+      <c r="E64" s="67" t="n">
+        <v>43.10332192077205</v>
+      </c>
+      <c r="F64" s="58" t="n">
+        <v>0.7311</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="68" t="inlineStr">
+        <is>
+          <t>D. Pilot-light phasing + gate</t>
+        </is>
+      </c>
+      <c r="B65" s="69" t="n">
+        <v>15.05090030021514</v>
+      </c>
+      <c r="C65" s="69" t="n">
+        <v>-8.411626796801812</v>
+      </c>
+      <c r="D65" s="69" t="n">
+        <v>13.32040175184729</v>
+      </c>
+      <c r="E65" s="69" t="n">
+        <v>43.06772269056702</v>
+      </c>
+      <c r="F65" s="61" t="n">
+        <v>0.8595</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="66" t="inlineStr">
+        <is>
+          <t>E. D + remaining equipment life valued at book</t>
+        </is>
+      </c>
+      <c r="B66" s="67" t="n">
+        <v>36.01053481960803</v>
+      </c>
+      <c r="C66" s="67" t="n">
+        <v>6.476777490438207</v>
+      </c>
+      <c r="D66" s="67" t="n">
+        <v>36.96085240343595</v>
+      </c>
+      <c r="E66" s="67" t="n">
+        <v>67.48368978517901</v>
+      </c>
+      <c r="F66" s="58" t="n">
+        <v>0.9938</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="66" t="inlineStr">
+        <is>
+          <t>F. D but savings ramp one year slower (stress test)</t>
+        </is>
+      </c>
+      <c r="B67" s="67" t="n">
+        <v>-7.534233621168762</v>
+      </c>
+      <c r="C67" s="67" t="n">
+        <v>-31.89940806088983</v>
+      </c>
+      <c r="D67" s="67" t="n">
+        <v>-5.542507323532465</v>
+      </c>
+      <c r="E67" s="67" t="n">
+        <v>12.32550108470081</v>
+      </c>
+      <c r="F67" s="58" t="n">
+        <v>0.3242</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="66" t="inlineStr">
+        <is>
+          <t>G. F + remaining equipment life valued at book</t>
+        </is>
+      </c>
+      <c r="B68" s="67" t="n">
+        <v>13.42540089822414</v>
+      </c>
+      <c r="C68" s="67" t="n">
+        <v>-3.778779125254701</v>
+      </c>
+      <c r="D68" s="67" t="n">
+        <v>11.92716410770895</v>
+      </c>
+      <c r="E68" s="67" t="n">
+        <v>35.1241416528562</v>
+      </c>
+      <c r="F68" s="58" t="n">
+        <v>0.879</v>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="62" t="inlineStr">
+        <is>
+          <t>Pilot-light phasing: 10% / 15% / 40% / 25% / 10% of capex in 2026-2030. Ramp-up kept the same to isolate the effect of phasing; if scaling later also delays savings, the gain is smaller.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="58" customHeight="1">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>Reading: a gate only protects value if little money is spent before it. Gate after heavy spending (B) destroys value; pilot-light + gate (D) is the design to defend in SQ3. Valuing equipment life beyond 2030 (E) is legitimate but state it openly. Stress test (F): if savings arrive a year late, P(NPV&gt;0) falls to 32% (88% if remaining equipment life is valued, G). Speed of the pilot is the make-or-break factor: quick wins in 2026-27 belong in the roadmap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="45" customHeight="1">
+      <c r="A71" s="62" t="inlineStr">
+        <is>
+          <t>Ranges used (triangular low / mode / high): scrap 20/35/50%, maintenance 5/10/15%, NVA 15/30/45%, energy 2/5/8%, variant cost 20/35/50%, investment 60/80/110, running 8/9/12%, training 2/2.5/3, variant projects 2/3/5, cost per project 5/10/15, cash realization 30/50/70%, adoption 60/100/100%, labor share 35/40/45%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>NPV distribution (histogram)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="55" t="inlineStr">
+        <is>
+          <t>NPV bin from (Rp B)</t>
+        </is>
+      </c>
+      <c r="B74" s="55" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="65" t="n">
+        <v>-51.6</v>
+      </c>
+      <c r="B75" s="70" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="65" t="n">
+        <v>-41.6</v>
+      </c>
+      <c r="B76" s="70" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="65" t="n">
+        <v>-31.5</v>
+      </c>
+      <c r="B77" s="70" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="65" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="B78" s="70" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="65" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="B79" s="70" t="n">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="65" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="B80" s="70" t="n">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="65" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="B81" s="70" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="65" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="B82" s="70" t="n">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="65" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="B83" s="70" t="n">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="65" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="B84" s="70" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="65" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="B85" s="70" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="65" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="B86" s="70" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="65" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="B87" s="70" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="65" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="B88" s="70" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="65" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="B89" s="70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="65" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="B90" s="70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>TEST 3. Which assumption matters most? Tornado (base case, one at a time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="55" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="B93" s="55" t="inlineStr">
+        <is>
+          <t>Low input</t>
+        </is>
+      </c>
+      <c r="C93" s="55" t="inlineStr">
+        <is>
+          <t>High input</t>
+        </is>
+      </c>
+      <c r="D93" s="55" t="inlineStr">
+        <is>
+          <t>NPV at low</t>
+        </is>
+      </c>
+      <c r="E93" s="55" t="inlineStr">
+        <is>
+          <t>NPV at high</t>
+        </is>
+      </c>
+      <c r="F93" s="55" t="inlineStr">
+        <is>
+          <t>Swing</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="71" t="inlineStr">
+        <is>
+          <t>Investment (Rp B)</t>
+        </is>
+      </c>
+      <c r="B94" s="72" t="n">
+        <v>110</v>
+      </c>
+      <c r="C94" s="72" t="n">
+        <v>60</v>
+      </c>
+      <c r="D94" s="67" t="n">
+        <v>-1.497910926203485</v>
+      </c>
+      <c r="E94" s="67" t="n">
+        <v>46.02200512523363</v>
+      </c>
+      <c r="F94" s="67" t="n">
+        <v>47.51991605143711</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="71" t="inlineStr">
+        <is>
+          <t>Adoption achieved</t>
+        </is>
+      </c>
+      <c r="B95" s="58" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C95" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" s="67" t="n">
+        <v>-17.99510981953292</v>
+      </c>
+      <c r="E95" s="67" t="n">
+        <v>27.01403870465879</v>
+      </c>
+      <c r="F95" s="67" t="n">
+        <v>45.00914852419172</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="71" t="inlineStr">
+        <is>
+          <t>Scrap reduction</t>
+        </is>
+      </c>
+      <c r="B96" s="58" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C96" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D96" s="67" t="n">
+        <v>7.376539348554191</v>
+      </c>
+      <c r="E96" s="67" t="n">
+        <v>46.65153806076337</v>
+      </c>
+      <c r="F96" s="67" t="n">
+        <v>39.27499871220918</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="71" t="inlineStr">
+        <is>
+          <t>Variant projects / yr</t>
+        </is>
+      </c>
+      <c r="B97" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="C97" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="D97" s="67" t="n">
+        <v>18.83174730628188</v>
+      </c>
+      <c r="E97" s="67" t="n">
+        <v>43.37862150141261</v>
+      </c>
+      <c r="F97" s="67" t="n">
+        <v>24.54687419513073</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="71" t="inlineStr">
+        <is>
+          <t>Cost per variant project</t>
+        </is>
+      </c>
+      <c r="B98" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="C98" s="72" t="n">
+        <v>15</v>
+      </c>
+      <c r="D98" s="67" t="n">
+        <v>14.74060160709343</v>
+      </c>
+      <c r="E98" s="67" t="n">
+        <v>39.28747580222415</v>
+      </c>
+      <c r="F98" s="67" t="n">
+        <v>24.54687419513073</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="71" t="inlineStr">
+        <is>
+          <t>Variant cost reduction</t>
+        </is>
+      </c>
+      <c r="B99" s="58" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C99" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D99" s="67" t="n">
+        <v>16.49394976388848</v>
+      </c>
+      <c r="E99" s="67" t="n">
+        <v>37.5341276454291</v>
+      </c>
+      <c r="F99" s="67" t="n">
+        <v>21.04017788154063</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="71" t="inlineStr">
+        <is>
+          <t>Operator NVA eliminated</t>
+        </is>
+      </c>
+      <c r="B100" s="58" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C100" s="58" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D100" s="67" t="n">
+        <v>18.37353898797276</v>
+      </c>
+      <c r="E100" s="67" t="n">
+        <v>35.6545384213448</v>
+      </c>
+      <c r="F100" s="67" t="n">
+        <v>17.28099943337204</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="71" t="inlineStr">
+        <is>
+          <t>Maintenance reduction</t>
+        </is>
+      </c>
+      <c r="B101" s="58" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C101" s="58" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D101" s="67" t="n">
+        <v>18.50445565034678</v>
+      </c>
+      <c r="E101" s="67" t="n">
+        <v>35.52362175897076</v>
+      </c>
+      <c r="F101" s="67" t="n">
+        <v>17.01916610862397</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="71" t="inlineStr">
+        <is>
+          <t>Energy reduction</t>
+        </is>
+      </c>
+      <c r="B102" s="58" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C102" s="58" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D102" s="67" t="n">
+        <v>22.30103885919367</v>
+      </c>
+      <c r="E102" s="67" t="n">
+        <v>31.72703855012389</v>
+      </c>
+      <c r="F102" s="67" t="n">
+        <v>9.425999690930212</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="71" t="inlineStr">
+        <is>
+          <t>Running cost %</t>
+        </is>
+      </c>
+      <c r="B103" s="58" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C103" s="58" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D103" s="67" t="n">
+        <v>23.77962476124955</v>
+      </c>
+      <c r="E103" s="67" t="n">
+        <v>30.24845264806801</v>
+      </c>
+      <c r="F103" s="67" t="n">
+        <v>6.468827886818463</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>Use the top 2-3 drivers as the assumptions you defend hardest in Q&amp;A, and as the KPIs you track first in the pilot.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H104"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Idea tests: simulation results (values produced by run_tests.py, not formulas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="54" t="inlineStr">
+        <is>
+          <t>Re-run run_tests.py after changing assumptions. Process parameters below are illustrative assumptions, not TMMIN data: present them as a mechanism test, and show the sensitivity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>TEST 1. Does closing the quality loop beat adding technology alone? (sealer drift -&gt; inspection -&gt; feedback, 1 year, 175,000 units, 300 runs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="55" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>Defective units / yr</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>Scrapped units / yr</t>
+        </is>
+      </c>
+      <c r="D5" s="55" t="inlineStr">
+        <is>
+          <t>Escaped defects / yr</t>
+        </is>
+      </c>
+      <c r="E5" s="55" t="inlineStr">
+        <is>
+          <t>Units built while drifting</t>
+        </is>
+      </c>
+      <c r="F5" s="55" t="inlineStr">
+        <is>
+          <t>Scrap vs today</t>
+        </is>
+      </c>
+      <c r="G5" s="55" t="inlineStr">
+        <is>
+          <t>Escapes vs today</t>
+        </is>
+      </c>
+      <c r="H5" s="55" t="inlineStr">
+        <is>
+          <t>Scrap P5-P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="56" t="inlineStr">
+        <is>
+          <t>1. Today: visual at final inspection, manual feedback</t>
+        </is>
+      </c>
+      <c r="B6" s="57" t="n">
+        <v>4266.68</v>
+      </c>
+      <c r="C6" s="57" t="n">
+        <v>1088.524</v>
+      </c>
+      <c r="D6" s="57" t="n">
+        <v>638.2666666666667</v>
+      </c>
+      <c r="E6" s="57" t="n">
+        <v>15796.09333333333</v>
+      </c>
+      <c r="F6" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="57" t="inlineStr">
+        <is>
+          <t>835 - 1,365</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="56" t="inlineStr">
+        <is>
+          <t>2. Better camera at end-of-line only (tech, no loop)</t>
+        </is>
+      </c>
+      <c r="B7" s="57" t="n">
+        <v>4265.323333333334</v>
+      </c>
+      <c r="C7" s="57" t="n">
+        <v>1215.776</v>
+      </c>
+      <c r="D7" s="57" t="n">
+        <v>212.7366666666667</v>
+      </c>
+      <c r="E7" s="57" t="n">
+        <v>15793.25666666667</v>
+      </c>
+      <c r="F7" s="58" t="n">
+        <v>0.1169032561523677</v>
+      </c>
+      <c r="G7" s="58" t="n">
+        <v>-0.6666962607060789</v>
+      </c>
+      <c r="H7" s="57" t="inlineStr">
+        <is>
+          <t>910 - 1,492</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="56" t="inlineStr">
+        <is>
+          <t>3. Closed loop at sealer, 31% of alerts dismissed (as today)</t>
+        </is>
+      </c>
+      <c r="B8" s="57" t="n">
+        <v>1652.95</v>
+      </c>
+      <c r="C8" s="57" t="n">
+        <v>362.1536666666667</v>
+      </c>
+      <c r="D8" s="57" t="n">
+        <v>203.26</v>
+      </c>
+      <c r="E8" s="57" t="n">
+        <v>5247.72</v>
+      </c>
+      <c r="F8" s="58" t="n">
+        <v>-0.6672984089770491</v>
+      </c>
+      <c r="G8" s="58" t="n">
+        <v>-0.6815437643618132</v>
+      </c>
+      <c r="H8" s="57" t="inlineStr">
+        <is>
+          <t>216 - 543</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="59" t="inlineStr">
+        <is>
+          <t>4. Closed loop with people-centred design (10% dismissed)</t>
+        </is>
+      </c>
+      <c r="B9" s="60" t="n">
+        <v>908.3233333333334</v>
+      </c>
+      <c r="C9" s="60" t="n">
+        <v>166.8633333333333</v>
+      </c>
+      <c r="D9" s="60" t="n">
+        <v>88.00666666666666</v>
+      </c>
+      <c r="E9" s="60" t="n">
+        <v>2257.006666666667</v>
+      </c>
+      <c r="F9" s="61" t="n">
+        <v>-0.8467067943992661</v>
+      </c>
+      <c r="G9" s="61" t="n">
+        <v>-0.862116147900564</v>
+      </c>
+      <c r="H9" s="60" t="inlineStr">
+        <is>
+          <t>83 - 270</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>What this shows</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="62" t="inlineStr">
+        <is>
+          <t>- A better camera at end-of-line alone changes scrap by +12% while escapes fall 67%: it catches more bad units, but too late, so escapes turn into scrap. It does not prevent defects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="62" t="inlineStr">
+        <is>
+          <t>- Closing the loop right after the sealer cuts scrap 85% and escapes 86%, because a drift is stopped within a few units instead of hundreds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="62" t="inlineStr">
+        <is>
+          <t>- If operators dismiss alerts in 31% of drift episodes (today's override rate), scrap reduction falls to 67%. Trust, training and alert design are part of the value, not an add-on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="62" t="inlineStr">
+        <is>
+          <t>- Plant-wide: if the pilot scope causes 40% of plant scrap (team assumption), the plant-wide scrap cut is about 34%. Compare with the 20% / 35% / 50% lever in Assumptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="62" t="inlineStr">
+        <is>
+          <t>- Deck message: value comes from redesigning the system (where the check sits, how fast the signal travels, who acts on it), not from buying the device. That is exactly the case ask.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Process assumptions used (illustrative, change and re-run)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="54" t="inlineStr">
+        <is>
+          <t>Defect probability per unit, stable sealer</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="54" t="inlineStr">
+        <is>
+          <t>Average units between drift events</t>
+        </is>
+      </c>
+      <c r="B20" s="63" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="54" t="inlineStr">
+        <is>
+          <t>Defect probability per unit while drifting</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="54" t="inlineStr">
+        <is>
+          <t>Manual visual detection rate at final inspection</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="54" t="inlineStr">
+        <is>
+          <t>Share of sealer defect modes the in-line AI camera can see</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="54" t="inlineStr">
+        <is>
+          <t>Units between sealer and today's final inspection</t>
+        </is>
+      </c>
+      <c r="B24" s="63" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="54" t="inlineStr">
+        <is>
+          <t>Units built before manual feedback reaches the sealer</t>
+        </is>
+      </c>
+      <c r="B25" s="63" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="54" t="inlineStr">
+        <is>
+          <t>Share of late-found defects scrapped</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="54" t="inlineStr">
+        <is>
+          <t>Share of early-found defects scrapped</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="54" t="inlineStr">
+        <is>
+          <t>Share of plant scrap from the pilot scope (team assumption)</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="62" t="inlineStr">
+        <is>
+          <t>In-line check: 5 units after sealer, automatic feedback within 10 units, 90% detection on visible defect modes (case: AI camera in validation to Oct 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Robustness: closed-loop (scenario 4) scrap reduction vs today when each assumption changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="55" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="B32" s="55" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C32" s="55" t="inlineStr">
+        <is>
+          <t>Reduction</t>
+        </is>
+      </c>
+      <c r="D32" s="55" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E32" s="55" t="inlineStr">
+        <is>
+          <t>Reduction</t>
+        </is>
+      </c>
+      <c r="F32" s="55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G32" s="55" t="inlineStr">
+        <is>
+          <t>Reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>AI camera coverage of defect modes</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C33" s="64" t="n">
+        <v>0.8247043005741556</v>
+      </c>
+      <c r="D33" s="20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E33" s="64" t="n">
+        <v>0.8468422609923756</v>
+      </c>
+      <c r="F33" s="20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G33" s="64" t="n">
+        <v>0.8667088181512177</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Drift defect rate</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C34" s="64" t="n">
+        <v>0.8026017993273447</v>
+      </c>
+      <c r="D34" s="20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E34" s="64" t="n">
+        <v>0.8479906256107048</v>
+      </c>
+      <c r="F34" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G34" s="64" t="n">
+        <v>0.8649243431242232</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Units between drift events</t>
+        </is>
+      </c>
+      <c r="B35" s="63" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C35" s="64" t="n">
+        <v>0.8634074536698797</v>
+      </c>
+      <c r="D35" s="63" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E35" s="64" t="n">
+        <v>0.8582510378017658</v>
+      </c>
+      <c r="F35" s="63" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G35" s="64" t="n">
+        <v>0.8336816505910225</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Late-found scrap share</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C36" s="64" t="n">
+        <v>0.8314626883200975</v>
+      </c>
+      <c r="D36" s="20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E36" s="64" t="n">
+        <v>0.8538779573335564</v>
+      </c>
+      <c r="F36" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G36" s="64" t="n">
+        <v>0.8501771115300518</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Units from sealer to today's inspection</t>
+        </is>
+      </c>
+      <c r="B37" s="63" t="n">
+        <v>100</v>
+      </c>
+      <c r="C37" s="64" t="n">
+        <v>0.8111230466252334</v>
+      </c>
+      <c r="D37" s="63" t="n">
+        <v>300</v>
+      </c>
+      <c r="E37" s="64" t="n">
+        <v>0.8492533988756621</v>
+      </c>
+      <c r="F37" s="63" t="n">
+        <v>600</v>
+      </c>
+      <c r="G37" s="64" t="n">
+        <v>0.8737976071910339</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Lowest scrap reduction across all tested cases: 80%. The mechanism holds even with pessimistic process assumptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>People test: how much value is lost when operators dismiss alerts?</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="55" t="inlineStr">
+        <is>
+          <t>Share of drift episodes where alerts are dismissed</t>
+        </is>
+      </c>
+      <c r="B41" s="55" t="inlineStr">
+        <is>
+          <t>Scrap reduction vs today</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="B42" s="64" t="n">
+        <v>0.9392930243154951</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B43" s="64" t="n">
+        <v>0.8445760803926541</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B44" s="64" t="n">
+        <v>0.7497194978398884</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="B45" s="64" t="n">
+        <v>0.6431060163426193</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B46" s="64" t="n">
+        <v>0.4964125733562145</v>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="62" t="inlineStr">
+        <is>
+          <t>Exhibit 6B says 31% of operators frequently override alerts today. This chart is the quantified case for the people part of the idea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>TEST 2. Is the business case robust? Financial Monte Carlo (10,000 runs, mirrors the Model tab incl. pilot-light phasing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="55" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B50" s="55" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C50" s="55" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Deterministic base NPV (check vs Model tab)</t>
+        </is>
+      </c>
+      <c r="B51" s="65" t="n">
+        <v>27.01403870465879</v>
+      </c>
+      <c r="C51" s="54" t="inlineStr">
+        <is>
+          <t>Should match Dashboard base NPV</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Mean NPV</t>
+        </is>
+      </c>
+      <c r="B52" s="65" t="n">
+        <v>11.82360761131173</v>
+      </c>
+      <c r="C52" s="54" t="inlineStr">
+        <is>
+          <t>Rp billion</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>P5 NPV (bad case)</t>
+        </is>
+      </c>
+      <c r="B53" s="65" t="n">
+        <v>-19.41291040060244</v>
+      </c>
+      <c r="C53" s="54" t="inlineStr">
+        <is>
+          <t>1-in-20 downside</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Median NPV</t>
+        </is>
+      </c>
+      <c r="B54" s="65" t="n">
+        <v>11.7084469092985</v>
+      </c>
+      <c r="C54" s="54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>P95 NPV (good case)</t>
+        </is>
+      </c>
+      <c r="B55" s="65" t="n">
+        <v>43.10332192077205</v>
+      </c>
+      <c r="C55" s="54" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Probability NPV &gt; 0</t>
+        </is>
+      </c>
+      <c r="B56" s="64" t="n">
+        <v>0.7311</v>
+      </c>
+      <c r="C56" s="54" t="inlineStr">
+        <is>
+          <t>Headline for the financial slide</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Median full run-rate savings (Rp B/yr)</t>
+        </is>
+      </c>
+      <c r="B57" s="65" t="n">
+        <v>49.0844126012166</v>
+      </c>
+      <c r="C57" s="54" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Median run-rate as % of conversion cost</t>
+        </is>
+      </c>
+      <c r="B58" s="64" t="n">
+        <v>0.08765073678788678</v>
+      </c>
+      <c r="C58" s="54" t="inlineStr">
+        <is>
+          <t>vs 16% gap to benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>TEST 2b. How should the roadmap spend the money? Same 10,000 runs, five strategies (gate = stop scaling if 2027 pilot adoption &lt; 80%; happens in 25% of runs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="55" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="B61" s="55" t="inlineStr">
+        <is>
+          <t>Mean NPV</t>
+        </is>
+      </c>
+      <c r="C61" s="55" t="inlineStr">
+        <is>
+          <t>P5 NPV</t>
+        </is>
+      </c>
+      <c r="D61" s="55" t="inlineStr">
+        <is>
+          <t>Median NPV</t>
+        </is>
+      </c>
+      <c r="E61" s="55" t="inlineStr">
+        <is>
+          <t>P95 NPV</t>
+        </is>
+      </c>
+      <c r="F61" s="55" t="inlineStr">
+        <is>
+          <t>P(NPV &gt; 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="66" t="inlineStr">
+        <is>
+          <t>A. Front-loaded phasing, no gate</t>
+        </is>
+      </c>
+      <c r="B62" s="67" t="n">
+        <v>-0.191332294676973</v>
+      </c>
+      <c r="C62" s="67" t="n">
+        <v>-32.83255089311962</v>
+      </c>
+      <c r="D62" s="67" t="n">
+        <v>-0.3737217276611755</v>
+      </c>
+      <c r="E62" s="67" t="n">
+        <v>32.5044161216826</v>
+      </c>
+      <c r="F62" s="58" t="n">
+        <v>0.4925</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="66" t="inlineStr">
+        <is>
+          <t>B. Front-loaded phasing + gate (65% already spent)</t>
+        </is>
+      </c>
+      <c r="B63" s="67" t="n">
+        <v>-3.79967892697686</v>
+      </c>
+      <c r="C63" s="67" t="n">
+        <v>-39.74590657971964</v>
+      </c>
+      <c r="D63" s="67" t="n">
+        <v>-2.962350007986172</v>
+      </c>
+      <c r="E63" s="67" t="n">
+        <v>32.40194504032392</v>
+      </c>
+      <c r="F63" s="58" t="n">
+        <v>0.4518</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="66" t="inlineStr">
+        <is>
+          <t>C. Pilot-light phasing, no gate (as in Model tab)</t>
+        </is>
+      </c>
+      <c r="B64" s="67" t="n">
+        <v>11.82360761131173</v>
+      </c>
+      <c r="C64" s="67" t="n">
+        <v>-19.41291040060244</v>
+      </c>
+      <c r="D64" s="67" t="n">
+        <v>11.7084469092985</v>
+      </c>
+      <c r="E64" s="67" t="n">
+        <v>43.10332192077205</v>
+      </c>
+      <c r="F64" s="58" t="n">
+        <v>0.7311</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="68" t="inlineStr">
+        <is>
+          <t>D. Pilot-light phasing + gate</t>
+        </is>
+      </c>
+      <c r="B65" s="69" t="n">
+        <v>15.05090030021514</v>
+      </c>
+      <c r="C65" s="69" t="n">
+        <v>-8.411626796801812</v>
+      </c>
+      <c r="D65" s="69" t="n">
+        <v>13.32040175184729</v>
+      </c>
+      <c r="E65" s="69" t="n">
+        <v>43.06772269056702</v>
+      </c>
+      <c r="F65" s="61" t="n">
+        <v>0.8595</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="66" t="inlineStr">
+        <is>
+          <t>E. D + remaining equipment life valued at book</t>
+        </is>
+      </c>
+      <c r="B66" s="67" t="n">
+        <v>36.01053481960803</v>
+      </c>
+      <c r="C66" s="67" t="n">
+        <v>6.476777490438207</v>
+      </c>
+      <c r="D66" s="67" t="n">
+        <v>36.96085240343595</v>
+      </c>
+      <c r="E66" s="67" t="n">
+        <v>67.48368978517901</v>
+      </c>
+      <c r="F66" s="58" t="n">
+        <v>0.9938</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="66" t="inlineStr">
+        <is>
+          <t>F. D but savings ramp one year slower (stress test)</t>
+        </is>
+      </c>
+      <c r="B67" s="67" t="n">
+        <v>-7.534233621168762</v>
+      </c>
+      <c r="C67" s="67" t="n">
+        <v>-31.89940806088983</v>
+      </c>
+      <c r="D67" s="67" t="n">
+        <v>-5.542507323532465</v>
+      </c>
+      <c r="E67" s="67" t="n">
+        <v>12.32550108470081</v>
+      </c>
+      <c r="F67" s="58" t="n">
+        <v>0.3242</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="66" t="inlineStr">
+        <is>
+          <t>G. F + remaining equipment life valued at book</t>
+        </is>
+      </c>
+      <c r="B68" s="67" t="n">
+        <v>13.42540089822414</v>
+      </c>
+      <c r="C68" s="67" t="n">
+        <v>-3.778779125254701</v>
+      </c>
+      <c r="D68" s="67" t="n">
+        <v>11.92716410770895</v>
+      </c>
+      <c r="E68" s="67" t="n">
+        <v>35.1241416528562</v>
+      </c>
+      <c r="F68" s="58" t="n">
+        <v>0.879</v>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="62" t="inlineStr">
+        <is>
+          <t>Pilot-light phasing: 10% / 15% / 40% / 25% / 10% of capex in 2026-2030. Ramp-up kept the same to isolate the effect of phasing; if scaling later also delays savings, the gain is smaller.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="58" customHeight="1">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>Reading: a gate only protects value if little money is spent before it. Gate after heavy spending (B) destroys value; pilot-light + gate (D) is the design to defend in SQ3. Valuing equipment life beyond 2030 (E) is legitimate but state it openly. Stress test (F): if savings arrive a year late, P(NPV&gt;0) falls to 32% (88% if remaining equipment life is valued, G). Speed of the pilot is the make-or-break factor: quick wins in 2026-27 belong in the roadmap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="45" customHeight="1">
+      <c r="A71" s="62" t="inlineStr">
+        <is>
+          <t>Ranges used (triangular low / mode / high): scrap 20/35/50%, maintenance 5/10/15%, NVA 15/30/45%, energy 2/5/8%, variant cost 20/35/50%, investment 60/80/110, running 8/9/12%, training 2/2.5/3, variant projects 2/3/5, cost per project 5/10/15, cash realization 30/50/70%, adoption 60/100/100%, labor share 35/40/45%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>NPV distribution (histogram)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="55" t="inlineStr">
+        <is>
+          <t>NPV bin from (Rp B)</t>
+        </is>
+      </c>
+      <c r="B74" s="55" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="65" t="n">
+        <v>-51.6</v>
+      </c>
+      <c r="B75" s="70" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="65" t="n">
+        <v>-41.6</v>
+      </c>
+      <c r="B76" s="70" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="65" t="n">
+        <v>-31.5</v>
+      </c>
+      <c r="B77" s="70" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="65" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="B78" s="70" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="65" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="B79" s="70" t="n">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="65" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="B80" s="70" t="n">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="65" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="B81" s="70" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="65" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="B82" s="70" t="n">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="65" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="B83" s="70" t="n">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="65" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="B84" s="70" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="65" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="B85" s="70" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="65" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="B86" s="70" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="65" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="B87" s="70" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="65" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="B88" s="70" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="65" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="B89" s="70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="65" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="B90" s="70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>TEST 3. Which assumption matters most? Tornado (base case, one at a time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="55" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="B93" s="55" t="inlineStr">
+        <is>
+          <t>Low input</t>
+        </is>
+      </c>
+      <c r="C93" s="55" t="inlineStr">
+        <is>
+          <t>High input</t>
+        </is>
+      </c>
+      <c r="D93" s="55" t="inlineStr">
+        <is>
+          <t>NPV at low</t>
+        </is>
+      </c>
+      <c r="E93" s="55" t="inlineStr">
+        <is>
+          <t>NPV at high</t>
+        </is>
+      </c>
+      <c r="F93" s="55" t="inlineStr">
+        <is>
+          <t>Swing</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="71" t="inlineStr">
+        <is>
+          <t>Investment (Rp B)</t>
+        </is>
+      </c>
+      <c r="B94" s="72" t="n">
+        <v>110</v>
+      </c>
+      <c r="C94" s="72" t="n">
+        <v>60</v>
+      </c>
+      <c r="D94" s="67" t="n">
+        <v>-1.497910926203485</v>
+      </c>
+      <c r="E94" s="67" t="n">
+        <v>46.02200512523363</v>
+      </c>
+      <c r="F94" s="67" t="n">
+        <v>47.51991605143711</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="71" t="inlineStr">
+        <is>
+          <t>Adoption achieved</t>
+        </is>
+      </c>
+      <c r="B95" s="58" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C95" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" s="67" t="n">
+        <v>-17.99510981953292</v>
+      </c>
+      <c r="E95" s="67" t="n">
+        <v>27.01403870465879</v>
+      </c>
+      <c r="F95" s="67" t="n">
+        <v>45.00914852419172</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="71" t="inlineStr">
+        <is>
+          <t>Scrap reduction</t>
+        </is>
+      </c>
+      <c r="B96" s="58" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C96" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D96" s="67" t="n">
+        <v>7.376539348554191</v>
+      </c>
+      <c r="E96" s="67" t="n">
+        <v>46.65153806076337</v>
+      </c>
+      <c r="F96" s="67" t="n">
+        <v>39.27499871220918</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="71" t="inlineStr">
+        <is>
+          <t>Variant projects / yr</t>
+        </is>
+      </c>
+      <c r="B97" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="C97" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="D97" s="67" t="n">
+        <v>18.83174730628188</v>
+      </c>
+      <c r="E97" s="67" t="n">
+        <v>43.37862150141261</v>
+      </c>
+      <c r="F97" s="67" t="n">
+        <v>24.54687419513073</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="71" t="inlineStr">
+        <is>
+          <t>Cost per variant project</t>
+        </is>
+      </c>
+      <c r="B98" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="C98" s="72" t="n">
+        <v>15</v>
+      </c>
+      <c r="D98" s="67" t="n">
+        <v>14.74060160709343</v>
+      </c>
+      <c r="E98" s="67" t="n">
+        <v>39.28747580222415</v>
+      </c>
+      <c r="F98" s="67" t="n">
+        <v>24.54687419513073</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="71" t="inlineStr">
+        <is>
+          <t>Variant cost reduction</t>
+        </is>
+      </c>
+      <c r="B99" s="58" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C99" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D99" s="67" t="n">
+        <v>16.49394976388848</v>
+      </c>
+      <c r="E99" s="67" t="n">
+        <v>37.5341276454291</v>
+      </c>
+      <c r="F99" s="67" t="n">
+        <v>21.04017788154063</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="71" t="inlineStr">
+        <is>
+          <t>Operator NVA eliminated</t>
+        </is>
+      </c>
+      <c r="B100" s="58" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C100" s="58" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D100" s="67" t="n">
+        <v>18.37353898797276</v>
+      </c>
+      <c r="E100" s="67" t="n">
+        <v>35.6545384213448</v>
+      </c>
+      <c r="F100" s="67" t="n">
+        <v>17.28099943337204</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="71" t="inlineStr">
+        <is>
+          <t>Maintenance reduction</t>
+        </is>
+      </c>
+      <c r="B101" s="58" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C101" s="58" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D101" s="67" t="n">
+        <v>18.50445565034678</v>
+      </c>
+      <c r="E101" s="67" t="n">
+        <v>35.52362175897076</v>
+      </c>
+      <c r="F101" s="67" t="n">
+        <v>17.01916610862397</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="71" t="inlineStr">
+        <is>
+          <t>Energy reduction</t>
+        </is>
+      </c>
+      <c r="B102" s="58" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C102" s="58" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D102" s="67" t="n">
+        <v>22.30103885919367</v>
+      </c>
+      <c r="E102" s="67" t="n">
+        <v>31.72703855012389</v>
+      </c>
+      <c r="F102" s="67" t="n">
+        <v>9.425999690930212</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="71" t="inlineStr">
+        <is>
+          <t>Running cost %</t>
+        </is>
+      </c>
+      <c r="B103" s="58" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C103" s="58" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D103" s="67" t="n">
+        <v>23.77962476124955</v>
+      </c>
+      <c r="E103" s="67" t="n">
+        <v>30.24845264806801</v>
+      </c>
+      <c r="F103" s="67" t="n">
+        <v>6.468827886818463</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>Use the top 2-3 drivers as the assumptions you defend hardest in Q&amp;A, and as the KPIs you track first in the pilot.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -12393,7 +18106,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13310,2589 +19023,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H86"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Savings, investment and NPV by scenario (Rp billion)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Program window 2026-2030 = 5-year economic life. No terminal value (conservative).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="35" t="inlineStr">
-        <is>
-          <t>Scenario: Conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Adoption ramp-up</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C6" s="36">
-        <f>Assumptions!B$43</f>
-        <v/>
-      </c>
-      <c r="D6" s="36">
-        <f>Assumptions!C$43</f>
-        <v/>
-      </c>
-      <c r="E6" s="36">
-        <f>Assumptions!D$43</f>
-        <v/>
-      </c>
-      <c r="F6" s="36">
-        <f>Assumptions!E$43</f>
-        <v/>
-      </c>
-      <c r="G6" s="36">
-        <f>Assumptions!F$43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Escalation factor</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C7" s="37">
-        <f>(1+Assumptions!$B$10)^(Assumptions!B$45-1)</f>
-        <v/>
-      </c>
-      <c r="D7" s="37">
-        <f>(1+Assumptions!$B$10)^(Assumptions!C$45-1)</f>
-        <v/>
-      </c>
-      <c r="E7" s="37">
-        <f>(1+Assumptions!$B$10)^(Assumptions!D$45-1)</f>
-        <v/>
-      </c>
-      <c r="F7" s="37">
-        <f>(1+Assumptions!$B$10)^(Assumptions!E$45-1)</f>
-        <v/>
-      </c>
-      <c r="G7" s="37">
-        <f>(1+Assumptions!$B$10)^(Assumptions!F$45-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Saving: scrap</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C8" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$B$32*C6*C7</f>
-        <v/>
-      </c>
-      <c r="D8" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$B$32*D6*D7</f>
-        <v/>
-      </c>
-      <c r="E8" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$B$32*E6*E7</f>
-        <v/>
-      </c>
-      <c r="F8" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$B$32*F6*F7</f>
-        <v/>
-      </c>
-      <c r="G8" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$B$32*G6*G7</f>
-        <v/>
-      </c>
-      <c r="H8" s="76">
-        <f>SUM(C8:G8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Saving: maintenance / downtime</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C9" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$B$33*C6*C7</f>
-        <v/>
-      </c>
-      <c r="D9" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$B$33*D6*D7</f>
-        <v/>
-      </c>
-      <c r="E9" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$B$33*E6*E7</f>
-        <v/>
-      </c>
-      <c r="F9" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$B$33*F6*F7</f>
-        <v/>
-      </c>
-      <c r="G9" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$B$33*G6*G7</f>
-        <v/>
-      </c>
-      <c r="H9" s="76">
-        <f>SUM(C9:G9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Saving: operator NVA time</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C10" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$B$34*Assumptions!$B$28*C6*C7</f>
-        <v/>
-      </c>
-      <c r="D10" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$B$34*Assumptions!$B$28*D6*D7</f>
-        <v/>
-      </c>
-      <c r="E10" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$B$34*Assumptions!$B$28*E6*E7</f>
-        <v/>
-      </c>
-      <c r="F10" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$B$34*Assumptions!$B$28*F6*F7</f>
-        <v/>
-      </c>
-      <c r="G10" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$B$34*Assumptions!$B$28*G6*G7</f>
-        <v/>
-      </c>
-      <c r="H10" s="76">
-        <f>SUM(C10:G10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Saving: energy</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C11" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$B$35*C6*C7</f>
-        <v/>
-      </c>
-      <c r="D11" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$B$35*D6*D7</f>
-        <v/>
-      </c>
-      <c r="E11" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$B$35*E6*E7</f>
-        <v/>
-      </c>
-      <c r="F11" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$B$35*F6*F7</f>
-        <v/>
-      </c>
-      <c r="G11" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$B$35*G6*G7</f>
-        <v/>
-      </c>
-      <c r="H11" s="76">
-        <f>SUM(C11:G11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Saving: variant modification</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C12" s="76">
-        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$36*C6*C7</f>
-        <v/>
-      </c>
-      <c r="D12" s="76">
-        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$36*D6*D7</f>
-        <v/>
-      </c>
-      <c r="E12" s="76">
-        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$36*E6*E7</f>
-        <v/>
-      </c>
-      <c r="F12" s="76">
-        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$36*F6*F7</f>
-        <v/>
-      </c>
-      <c r="G12" s="76">
-        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$36*G6*G7</f>
-        <v/>
-      </c>
-      <c r="H12" s="76">
-        <f>SUM(C12:G12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Total gross savings</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C13" s="79">
-        <f>SUM(C8:C12)</f>
-        <v/>
-      </c>
-      <c r="D13" s="79">
-        <f>SUM(D8:D12)</f>
-        <v/>
-      </c>
-      <c r="E13" s="79">
-        <f>SUM(E8:E12)</f>
-        <v/>
-      </c>
-      <c r="F13" s="79">
-        <f>SUM(F8:F12)</f>
-        <v/>
-      </c>
-      <c r="G13" s="79">
-        <f>SUM(G8:G12)</f>
-        <v/>
-      </c>
-      <c r="H13" s="79">
-        <f>SUM(C13:G13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Investment (capex)</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C14" s="76">
-        <f>Assumptions!$B$37*Assumptions!B$44</f>
-        <v/>
-      </c>
-      <c r="D14" s="76">
-        <f>Assumptions!$B$37*Assumptions!C$44</f>
-        <v/>
-      </c>
-      <c r="E14" s="76">
-        <f>Assumptions!$B$37*Assumptions!D$44</f>
-        <v/>
-      </c>
-      <c r="F14" s="76">
-        <f>Assumptions!$B$37*Assumptions!E$44</f>
-        <v/>
-      </c>
-      <c r="G14" s="76">
-        <f>Assumptions!$B$37*Assumptions!F$44</f>
-        <v/>
-      </c>
-      <c r="H14" s="76">
-        <f>SUM(C14:G14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Cumulative investment</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C15" s="76">
-        <f>SUM($C14:C14)</f>
-        <v/>
-      </c>
-      <c r="D15" s="76">
-        <f>SUM($C14:D14)</f>
-        <v/>
-      </c>
-      <c r="E15" s="76">
-        <f>SUM($C14:E14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="76">
-        <f>SUM($C14:F14)</f>
-        <v/>
-      </c>
-      <c r="G15" s="76">
-        <f>SUM($C14:G14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Running + training cost</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C16" s="76">
-        <f>C15*Assumptions!$B$38+Assumptions!$B$39</f>
-        <v/>
-      </c>
-      <c r="D16" s="76">
-        <f>D15*Assumptions!$B$38+Assumptions!$B$39</f>
-        <v/>
-      </c>
-      <c r="E16" s="76">
-        <f>E15*Assumptions!$B$38+Assumptions!$B$39</f>
-        <v/>
-      </c>
-      <c r="F16" s="76">
-        <f>F15*Assumptions!$B$38+Assumptions!$B$39</f>
-        <v/>
-      </c>
-      <c r="G16" s="76">
-        <f>G15*Assumptions!$B$38+Assumptions!$B$39</f>
-        <v/>
-      </c>
-      <c r="H16" s="76">
-        <f>SUM(C16:G16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Net cash flow</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C17" s="79">
-        <f>C13-C14-C16</f>
-        <v/>
-      </c>
-      <c r="D17" s="79">
-        <f>D13-D14-D16</f>
-        <v/>
-      </c>
-      <c r="E17" s="79">
-        <f>E13-E14-E16</f>
-        <v/>
-      </c>
-      <c r="F17" s="79">
-        <f>F13-F14-F16</f>
-        <v/>
-      </c>
-      <c r="G17" s="79">
-        <f>G13-G14-G16</f>
-        <v/>
-      </c>
-      <c r="H17" s="79">
-        <f>SUM(C17:G17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Discount factor</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C18" s="37">
-        <f>1/(1+Assumptions!$B$9)^Assumptions!B$45</f>
-        <v/>
-      </c>
-      <c r="D18" s="37">
-        <f>1/(1+Assumptions!$B$9)^Assumptions!C$45</f>
-        <v/>
-      </c>
-      <c r="E18" s="37">
-        <f>1/(1+Assumptions!$B$9)^Assumptions!D$45</f>
-        <v/>
-      </c>
-      <c r="F18" s="37">
-        <f>1/(1+Assumptions!$B$9)^Assumptions!E$45</f>
-        <v/>
-      </c>
-      <c r="G18" s="37">
-        <f>1/(1+Assumptions!$B$9)^Assumptions!F$45</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Present value</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C19" s="79">
-        <f>C17*C18</f>
-        <v/>
-      </c>
-      <c r="D19" s="79">
-        <f>D17*D18</f>
-        <v/>
-      </c>
-      <c r="E19" s="79">
-        <f>E17*E18</f>
-        <v/>
-      </c>
-      <c r="F19" s="79">
-        <f>F17*F18</f>
-        <v/>
-      </c>
-      <c r="G19" s="79">
-        <f>G17*G18</f>
-        <v/>
-      </c>
-      <c r="H19" s="79">
-        <f>SUM(C19:G19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Cumulative net cash flow</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C20" s="76">
-        <f>SUM($C17:C17)</f>
-        <v/>
-      </c>
-      <c r="D20" s="76">
-        <f>SUM($C17:D17)</f>
-        <v/>
-      </c>
-      <c r="E20" s="76">
-        <f>SUM($C17:E17)</f>
-        <v/>
-      </c>
-      <c r="F20" s="76">
-        <f>SUM($C17:F17)</f>
-        <v/>
-      </c>
-      <c r="G20" s="76">
-        <f>SUM($C17:G17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>Outputs</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>NPV @ discount rate</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C23" s="79">
-        <f>SUM(C19:G19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>IRR</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C24" s="21">
-        <f>IFERROR(IRR(C17:G17),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Payback year (cumulative net turns positive)</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="C25" s="3">
-        <f>IF(G20&lt;0,"Beyond 2030",2026+COUNTIF(C20:G20,"&lt;0"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Full run-rate savings (2025 prices)</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Rp B/yr</t>
-        </is>
-      </c>
-      <c r="C26" s="79">
-        <f>Assumptions!$B$8*(Assumptions!$B$22*Assumptions!B32+Assumptions!$B$20*Assumptions!B33+Assumptions!$B$18*Assumptions!$B$14*Assumptions!B34*Assumptions!$B$28+Assumptions!$B$19*Assumptions!B35)+Assumptions!$B$26*Assumptions!$B$27*Assumptions!B36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Run-rate savings as % of conversion cost</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C27" s="21">
-        <f>C26/Assumptions!$B$8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Implied conversion cost index</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>index</t>
-        </is>
-      </c>
-      <c r="C28" s="53">
-        <f>Assumptions!$B$12*(1-C27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Share of gap to benchmark closed</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C29" s="21">
-        <f>(Assumptions!$B$12-C28)/(Assumptions!$B$12-Assumptions!$B$13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>NPV incl. remaining equipment value at end-2030 (book)</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C30" s="79">
-        <f>C23+SUMPRODUCT(C14:G14,(Assumptions!$B$45:$F$45-0.5)/Assumptions!$B$11)/(1+Assumptions!$B$9)^Assumptions!$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="35" t="inlineStr">
-        <is>
-          <t>Scenario: Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Adoption ramp-up</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C34" s="36">
-        <f>Assumptions!B$43</f>
-        <v/>
-      </c>
-      <c r="D34" s="36">
-        <f>Assumptions!C$43</f>
-        <v/>
-      </c>
-      <c r="E34" s="36">
-        <f>Assumptions!D$43</f>
-        <v/>
-      </c>
-      <c r="F34" s="36">
-        <f>Assumptions!E$43</f>
-        <v/>
-      </c>
-      <c r="G34" s="36">
-        <f>Assumptions!F$43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Escalation factor</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C35" s="37">
-        <f>(1+Assumptions!$B$10)^(Assumptions!B$45-1)</f>
-        <v/>
-      </c>
-      <c r="D35" s="37">
-        <f>(1+Assumptions!$B$10)^(Assumptions!C$45-1)</f>
-        <v/>
-      </c>
-      <c r="E35" s="37">
-        <f>(1+Assumptions!$B$10)^(Assumptions!D$45-1)</f>
-        <v/>
-      </c>
-      <c r="F35" s="37">
-        <f>(1+Assumptions!$B$10)^(Assumptions!E$45-1)</f>
-        <v/>
-      </c>
-      <c r="G35" s="37">
-        <f>(1+Assumptions!$B$10)^(Assumptions!F$45-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Saving: scrap</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C36" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$C$32*C34*C35</f>
-        <v/>
-      </c>
-      <c r="D36" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$C$32*D34*D35</f>
-        <v/>
-      </c>
-      <c r="E36" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$C$32*E34*E35</f>
-        <v/>
-      </c>
-      <c r="F36" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$C$32*F34*F35</f>
-        <v/>
-      </c>
-      <c r="G36" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$C$32*G34*G35</f>
-        <v/>
-      </c>
-      <c r="H36" s="76">
-        <f>SUM(C36:G36)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Saving: maintenance / downtime</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C37" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$C$33*C34*C35</f>
-        <v/>
-      </c>
-      <c r="D37" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$C$33*D34*D35</f>
-        <v/>
-      </c>
-      <c r="E37" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$C$33*E34*E35</f>
-        <v/>
-      </c>
-      <c r="F37" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$C$33*F34*F35</f>
-        <v/>
-      </c>
-      <c r="G37" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$C$33*G34*G35</f>
-        <v/>
-      </c>
-      <c r="H37" s="76">
-        <f>SUM(C37:G37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Saving: operator NVA time</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C38" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$C$34*Assumptions!$B$28*C34*C35</f>
-        <v/>
-      </c>
-      <c r="D38" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$C$34*Assumptions!$B$28*D34*D35</f>
-        <v/>
-      </c>
-      <c r="E38" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$C$34*Assumptions!$B$28*E34*E35</f>
-        <v/>
-      </c>
-      <c r="F38" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$C$34*Assumptions!$B$28*F34*F35</f>
-        <v/>
-      </c>
-      <c r="G38" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$C$34*Assumptions!$B$28*G34*G35</f>
-        <v/>
-      </c>
-      <c r="H38" s="76">
-        <f>SUM(C38:G38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Saving: energy</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C39" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$C$35*C34*C35</f>
-        <v/>
-      </c>
-      <c r="D39" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$C$35*D34*D35</f>
-        <v/>
-      </c>
-      <c r="E39" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$C$35*E34*E35</f>
-        <v/>
-      </c>
-      <c r="F39" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$C$35*F34*F35</f>
-        <v/>
-      </c>
-      <c r="G39" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$C$35*G34*G35</f>
-        <v/>
-      </c>
-      <c r="H39" s="76">
-        <f>SUM(C39:G39)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Saving: variant modification</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C40" s="76">
-        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$C$36*C34*C35</f>
-        <v/>
-      </c>
-      <c r="D40" s="76">
-        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$C$36*D34*D35</f>
-        <v/>
-      </c>
-      <c r="E40" s="76">
-        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$C$36*E34*E35</f>
-        <v/>
-      </c>
-      <c r="F40" s="76">
-        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$C$36*F34*F35</f>
-        <v/>
-      </c>
-      <c r="G40" s="76">
-        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$C$36*G34*G35</f>
-        <v/>
-      </c>
-      <c r="H40" s="76">
-        <f>SUM(C40:G40)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Total gross savings</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C41" s="79">
-        <f>SUM(C36:C40)</f>
-        <v/>
-      </c>
-      <c r="D41" s="79">
-        <f>SUM(D36:D40)</f>
-        <v/>
-      </c>
-      <c r="E41" s="79">
-        <f>SUM(E36:E40)</f>
-        <v/>
-      </c>
-      <c r="F41" s="79">
-        <f>SUM(F36:F40)</f>
-        <v/>
-      </c>
-      <c r="G41" s="79">
-        <f>SUM(G36:G40)</f>
-        <v/>
-      </c>
-      <c r="H41" s="79">
-        <f>SUM(C41:G41)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Investment (capex)</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C42" s="76">
-        <f>Assumptions!$C$37*Assumptions!B$44</f>
-        <v/>
-      </c>
-      <c r="D42" s="76">
-        <f>Assumptions!$C$37*Assumptions!C$44</f>
-        <v/>
-      </c>
-      <c r="E42" s="76">
-        <f>Assumptions!$C$37*Assumptions!D$44</f>
-        <v/>
-      </c>
-      <c r="F42" s="76">
-        <f>Assumptions!$C$37*Assumptions!E$44</f>
-        <v/>
-      </c>
-      <c r="G42" s="76">
-        <f>Assumptions!$C$37*Assumptions!F$44</f>
-        <v/>
-      </c>
-      <c r="H42" s="76">
-        <f>SUM(C42:G42)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Cumulative investment</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C43" s="76">
-        <f>SUM($C42:C42)</f>
-        <v/>
-      </c>
-      <c r="D43" s="76">
-        <f>SUM($C42:D42)</f>
-        <v/>
-      </c>
-      <c r="E43" s="76">
-        <f>SUM($C42:E42)</f>
-        <v/>
-      </c>
-      <c r="F43" s="76">
-        <f>SUM($C42:F42)</f>
-        <v/>
-      </c>
-      <c r="G43" s="76">
-        <f>SUM($C42:G42)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Running + training cost</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C44" s="76">
-        <f>C43*Assumptions!$C$38+Assumptions!$C$39</f>
-        <v/>
-      </c>
-      <c r="D44" s="76">
-        <f>D43*Assumptions!$C$38+Assumptions!$C$39</f>
-        <v/>
-      </c>
-      <c r="E44" s="76">
-        <f>E43*Assumptions!$C$38+Assumptions!$C$39</f>
-        <v/>
-      </c>
-      <c r="F44" s="76">
-        <f>F43*Assumptions!$C$38+Assumptions!$C$39</f>
-        <v/>
-      </c>
-      <c r="G44" s="76">
-        <f>G43*Assumptions!$C$38+Assumptions!$C$39</f>
-        <v/>
-      </c>
-      <c r="H44" s="76">
-        <f>SUM(C44:G44)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Net cash flow</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C45" s="79">
-        <f>C41-C42-C44</f>
-        <v/>
-      </c>
-      <c r="D45" s="79">
-        <f>D41-D42-D44</f>
-        <v/>
-      </c>
-      <c r="E45" s="79">
-        <f>E41-E42-E44</f>
-        <v/>
-      </c>
-      <c r="F45" s="79">
-        <f>F41-F42-F44</f>
-        <v/>
-      </c>
-      <c r="G45" s="79">
-        <f>G41-G42-G44</f>
-        <v/>
-      </c>
-      <c r="H45" s="79">
-        <f>SUM(C45:G45)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Discount factor</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C46" s="37">
-        <f>1/(1+Assumptions!$B$9)^Assumptions!B$45</f>
-        <v/>
-      </c>
-      <c r="D46" s="37">
-        <f>1/(1+Assumptions!$B$9)^Assumptions!C$45</f>
-        <v/>
-      </c>
-      <c r="E46" s="37">
-        <f>1/(1+Assumptions!$B$9)^Assumptions!D$45</f>
-        <v/>
-      </c>
-      <c r="F46" s="37">
-        <f>1/(1+Assumptions!$B$9)^Assumptions!E$45</f>
-        <v/>
-      </c>
-      <c r="G46" s="37">
-        <f>1/(1+Assumptions!$B$9)^Assumptions!F$45</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Present value</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C47" s="79">
-        <f>C45*C46</f>
-        <v/>
-      </c>
-      <c r="D47" s="79">
-        <f>D45*D46</f>
-        <v/>
-      </c>
-      <c r="E47" s="79">
-        <f>E45*E46</f>
-        <v/>
-      </c>
-      <c r="F47" s="79">
-        <f>F45*F46</f>
-        <v/>
-      </c>
-      <c r="G47" s="79">
-        <f>G45*G46</f>
-        <v/>
-      </c>
-      <c r="H47" s="79">
-        <f>SUM(C47:G47)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Cumulative net cash flow</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C48" s="76">
-        <f>SUM($C45:C45)</f>
-        <v/>
-      </c>
-      <c r="D48" s="76">
-        <f>SUM($C45:D45)</f>
-        <v/>
-      </c>
-      <c r="E48" s="76">
-        <f>SUM($C45:E45)</f>
-        <v/>
-      </c>
-      <c r="F48" s="76">
-        <f>SUM($C45:F45)</f>
-        <v/>
-      </c>
-      <c r="G48" s="76">
-        <f>SUM($C45:G45)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="16" t="inlineStr">
-        <is>
-          <t>Outputs</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>NPV @ discount rate</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C51" s="79">
-        <f>SUM(C47:G47)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>IRR</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C52" s="21">
-        <f>IFERROR(IRR(C45:G45),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Payback year (cumulative net turns positive)</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="C53" s="3">
-        <f>IF(G48&lt;0,"Beyond 2030",2026+COUNTIF(C48:G48,"&lt;0"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Full run-rate savings (2025 prices)</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Rp B/yr</t>
-        </is>
-      </c>
-      <c r="C54" s="79">
-        <f>Assumptions!$B$8*(Assumptions!$B$22*Assumptions!C32+Assumptions!$B$20*Assumptions!C33+Assumptions!$B$18*Assumptions!$B$14*Assumptions!C34*Assumptions!$B$28+Assumptions!$B$19*Assumptions!C35)+Assumptions!$B$26*Assumptions!$B$27*Assumptions!C36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Run-rate savings as % of conversion cost</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C55" s="21">
-        <f>C54/Assumptions!$B$8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Implied conversion cost index</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>index</t>
-        </is>
-      </c>
-      <c r="C56" s="53">
-        <f>Assumptions!$B$12*(1-C55)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Share of gap to benchmark closed</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C57" s="21">
-        <f>(Assumptions!$B$12-C56)/(Assumptions!$B$12-Assumptions!$B$13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>NPV incl. remaining equipment value at end-2030 (book)</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C58" s="79">
-        <f>C51+SUMPRODUCT(C42:G42,(Assumptions!$B$45:$F$45-0.5)/Assumptions!$B$11)/(1+Assumptions!$B$9)^Assumptions!$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="35" t="inlineStr">
-        <is>
-          <t>Scenario: Optimistic</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="C61" s="8" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D61" s="8" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="E61" s="8" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="F61" s="8" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="G61" s="8" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="H61" s="8" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Adoption ramp-up</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C62" s="36">
-        <f>Assumptions!B$43</f>
-        <v/>
-      </c>
-      <c r="D62" s="36">
-        <f>Assumptions!C$43</f>
-        <v/>
-      </c>
-      <c r="E62" s="36">
-        <f>Assumptions!D$43</f>
-        <v/>
-      </c>
-      <c r="F62" s="36">
-        <f>Assumptions!E$43</f>
-        <v/>
-      </c>
-      <c r="G62" s="36">
-        <f>Assumptions!F$43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Escalation factor</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C63" s="37">
-        <f>(1+Assumptions!$B$10)^(Assumptions!B$45-1)</f>
-        <v/>
-      </c>
-      <c r="D63" s="37">
-        <f>(1+Assumptions!$B$10)^(Assumptions!C$45-1)</f>
-        <v/>
-      </c>
-      <c r="E63" s="37">
-        <f>(1+Assumptions!$B$10)^(Assumptions!D$45-1)</f>
-        <v/>
-      </c>
-      <c r="F63" s="37">
-        <f>(1+Assumptions!$B$10)^(Assumptions!E$45-1)</f>
-        <v/>
-      </c>
-      <c r="G63" s="37">
-        <f>(1+Assumptions!$B$10)^(Assumptions!F$45-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Saving: scrap</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C64" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$D$32*C62*C63</f>
-        <v/>
-      </c>
-      <c r="D64" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$D$32*D62*D63</f>
-        <v/>
-      </c>
-      <c r="E64" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$D$32*E62*E63</f>
-        <v/>
-      </c>
-      <c r="F64" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$D$32*F62*F63</f>
-        <v/>
-      </c>
-      <c r="G64" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$22*Assumptions!$D$32*G62*G63</f>
-        <v/>
-      </c>
-      <c r="H64" s="76">
-        <f>SUM(C64:G64)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Saving: maintenance / downtime</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C65" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$D$33*C62*C63</f>
-        <v/>
-      </c>
-      <c r="D65" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$D$33*D62*D63</f>
-        <v/>
-      </c>
-      <c r="E65" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$D$33*E62*E63</f>
-        <v/>
-      </c>
-      <c r="F65" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$D$33*F62*F63</f>
-        <v/>
-      </c>
-      <c r="G65" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$20*Assumptions!$D$33*G62*G63</f>
-        <v/>
-      </c>
-      <c r="H65" s="76">
-        <f>SUM(C65:G65)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Saving: operator NVA time</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C66" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$D$34*Assumptions!$B$28*C62*C63</f>
-        <v/>
-      </c>
-      <c r="D66" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$D$34*Assumptions!$B$28*D62*D63</f>
-        <v/>
-      </c>
-      <c r="E66" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$D$34*Assumptions!$B$28*E62*E63</f>
-        <v/>
-      </c>
-      <c r="F66" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$D$34*Assumptions!$B$28*F62*F63</f>
-        <v/>
-      </c>
-      <c r="G66" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$18*Assumptions!$B$14*Assumptions!$D$34*Assumptions!$B$28*G62*G63</f>
-        <v/>
-      </c>
-      <c r="H66" s="76">
-        <f>SUM(C66:G66)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Saving: energy</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C67" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$D$35*C62*C63</f>
-        <v/>
-      </c>
-      <c r="D67" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$D$35*D62*D63</f>
-        <v/>
-      </c>
-      <c r="E67" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$D$35*E62*E63</f>
-        <v/>
-      </c>
-      <c r="F67" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$D$35*F62*F63</f>
-        <v/>
-      </c>
-      <c r="G67" s="76">
-        <f>Assumptions!$B$8*Assumptions!$B$19*Assumptions!$D$35*G62*G63</f>
-        <v/>
-      </c>
-      <c r="H67" s="76">
-        <f>SUM(C67:G67)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Saving: variant modification</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C68" s="76">
-        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$D$36*C62*C63</f>
-        <v/>
-      </c>
-      <c r="D68" s="76">
-        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$D$36*D62*D63</f>
-        <v/>
-      </c>
-      <c r="E68" s="76">
-        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$D$36*E62*E63</f>
-        <v/>
-      </c>
-      <c r="F68" s="76">
-        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$D$36*F62*F63</f>
-        <v/>
-      </c>
-      <c r="G68" s="76">
-        <f>Assumptions!$B$26*Assumptions!$B$27*Assumptions!$D$36*G62*G63</f>
-        <v/>
-      </c>
-      <c r="H68" s="76">
-        <f>SUM(C68:G68)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>Total gross savings</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C69" s="79">
-        <f>SUM(C64:C68)</f>
-        <v/>
-      </c>
-      <c r="D69" s="79">
-        <f>SUM(D64:D68)</f>
-        <v/>
-      </c>
-      <c r="E69" s="79">
-        <f>SUM(E64:E68)</f>
-        <v/>
-      </c>
-      <c r="F69" s="79">
-        <f>SUM(F64:F68)</f>
-        <v/>
-      </c>
-      <c r="G69" s="79">
-        <f>SUM(G64:G68)</f>
-        <v/>
-      </c>
-      <c r="H69" s="79">
-        <f>SUM(C69:G69)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Investment (capex)</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C70" s="76">
-        <f>Assumptions!$D$37*Assumptions!B$44</f>
-        <v/>
-      </c>
-      <c r="D70" s="76">
-        <f>Assumptions!$D$37*Assumptions!C$44</f>
-        <v/>
-      </c>
-      <c r="E70" s="76">
-        <f>Assumptions!$D$37*Assumptions!D$44</f>
-        <v/>
-      </c>
-      <c r="F70" s="76">
-        <f>Assumptions!$D$37*Assumptions!E$44</f>
-        <v/>
-      </c>
-      <c r="G70" s="76">
-        <f>Assumptions!$D$37*Assumptions!F$44</f>
-        <v/>
-      </c>
-      <c r="H70" s="76">
-        <f>SUM(C70:G70)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>Cumulative investment</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C71" s="76">
-        <f>SUM($C70:C70)</f>
-        <v/>
-      </c>
-      <c r="D71" s="76">
-        <f>SUM($C70:D70)</f>
-        <v/>
-      </c>
-      <c r="E71" s="76">
-        <f>SUM($C70:E70)</f>
-        <v/>
-      </c>
-      <c r="F71" s="76">
-        <f>SUM($C70:F70)</f>
-        <v/>
-      </c>
-      <c r="G71" s="76">
-        <f>SUM($C70:G70)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Running + training cost</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C72" s="76">
-        <f>C71*Assumptions!$D$38+Assumptions!$D$39</f>
-        <v/>
-      </c>
-      <c r="D72" s="76">
-        <f>D71*Assumptions!$D$38+Assumptions!$D$39</f>
-        <v/>
-      </c>
-      <c r="E72" s="76">
-        <f>E71*Assumptions!$D$38+Assumptions!$D$39</f>
-        <v/>
-      </c>
-      <c r="F72" s="76">
-        <f>F71*Assumptions!$D$38+Assumptions!$D$39</f>
-        <v/>
-      </c>
-      <c r="G72" s="76">
-        <f>G71*Assumptions!$D$38+Assumptions!$D$39</f>
-        <v/>
-      </c>
-      <c r="H72" s="76">
-        <f>SUM(C72:G72)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>Net cash flow</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C73" s="79">
-        <f>C69-C70-C72</f>
-        <v/>
-      </c>
-      <c r="D73" s="79">
-        <f>D69-D70-D72</f>
-        <v/>
-      </c>
-      <c r="E73" s="79">
-        <f>E69-E70-E72</f>
-        <v/>
-      </c>
-      <c r="F73" s="79">
-        <f>F69-F70-F72</f>
-        <v/>
-      </c>
-      <c r="G73" s="79">
-        <f>G69-G70-G72</f>
-        <v/>
-      </c>
-      <c r="H73" s="79">
-        <f>SUM(C73:G73)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>Discount factor</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C74" s="37">
-        <f>1/(1+Assumptions!$B$9)^Assumptions!B$45</f>
-        <v/>
-      </c>
-      <c r="D74" s="37">
-        <f>1/(1+Assumptions!$B$9)^Assumptions!C$45</f>
-        <v/>
-      </c>
-      <c r="E74" s="37">
-        <f>1/(1+Assumptions!$B$9)^Assumptions!D$45</f>
-        <v/>
-      </c>
-      <c r="F74" s="37">
-        <f>1/(1+Assumptions!$B$9)^Assumptions!E$45</f>
-        <v/>
-      </c>
-      <c r="G74" s="37">
-        <f>1/(1+Assumptions!$B$9)^Assumptions!F$45</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>Present value</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C75" s="79">
-        <f>C73*C74</f>
-        <v/>
-      </c>
-      <c r="D75" s="79">
-        <f>D73*D74</f>
-        <v/>
-      </c>
-      <c r="E75" s="79">
-        <f>E73*E74</f>
-        <v/>
-      </c>
-      <c r="F75" s="79">
-        <f>F73*F74</f>
-        <v/>
-      </c>
-      <c r="G75" s="79">
-        <f>G73*G74</f>
-        <v/>
-      </c>
-      <c r="H75" s="79">
-        <f>SUM(C75:G75)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Cumulative net cash flow</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C76" s="76">
-        <f>SUM($C73:C73)</f>
-        <v/>
-      </c>
-      <c r="D76" s="76">
-        <f>SUM($C73:D73)</f>
-        <v/>
-      </c>
-      <c r="E76" s="76">
-        <f>SUM($C73:E73)</f>
-        <v/>
-      </c>
-      <c r="F76" s="76">
-        <f>SUM($C73:F73)</f>
-        <v/>
-      </c>
-      <c r="G76" s="76">
-        <f>SUM($C73:G73)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="16" t="inlineStr">
-        <is>
-          <t>Outputs</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>NPV @ discount rate</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C79" s="79">
-        <f>SUM(C75:G75)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>IRR</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C80" s="21">
-        <f>IFERROR(IRR(C73:G73),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>Payback year (cumulative net turns positive)</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="C81" s="3">
-        <f>IF(G76&lt;0,"Beyond 2030",2026+COUNTIF(C76:G76,"&lt;0"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Full run-rate savings (2025 prices)</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Rp B/yr</t>
-        </is>
-      </c>
-      <c r="C82" s="79">
-        <f>Assumptions!$B$8*(Assumptions!$B$22*Assumptions!D32+Assumptions!$B$20*Assumptions!D33+Assumptions!$B$18*Assumptions!$B$14*Assumptions!D34*Assumptions!$B$28+Assumptions!$B$19*Assumptions!D35)+Assumptions!$B$26*Assumptions!$B$27*Assumptions!D36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>Run-rate savings as % of conversion cost</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C83" s="21">
-        <f>C82/Assumptions!$B$8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Implied conversion cost index</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>index</t>
-        </is>
-      </c>
-      <c r="C84" s="53">
-        <f>Assumptions!$B$12*(1-C83)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Share of gap to benchmark closed</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C85" s="21">
-        <f>(Assumptions!$B$12-C84)/(Assumptions!$B$12-Assumptions!$B$13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>NPV incl. remaining equipment value at end-2030 (book)</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Rp B</t>
-        </is>
-      </c>
-      <c r="C86" s="79">
-        <f>C79+SUMPRODUCT(C70:G70,(Assumptions!$B$45:$F$45-0.5)/Assumptions!$B$11)/(1+Assumptions!$B$9)^Assumptions!$B$11</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Financial summary for the deck (Rp billion)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Conservative</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>Optimistic</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>NPV (10%)</t>
-        </is>
-      </c>
-      <c r="B4" s="80">
-        <f>Model!C23</f>
-        <v/>
-      </c>
-      <c r="C4" s="80">
-        <f>Model!C51</f>
-        <v/>
-      </c>
-      <c r="D4" s="80">
-        <f>Model!C79</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>IRR</t>
-        </is>
-      </c>
-      <c r="B5" s="36">
-        <f>Model!C24</f>
-        <v/>
-      </c>
-      <c r="C5" s="36">
-        <f>Model!C52</f>
-        <v/>
-      </c>
-      <c r="D5" s="36">
-        <f>Model!C80</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Payback year</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>Model!C25</f>
-        <v/>
-      </c>
-      <c r="C6" s="5">
-        <f>Model!C53</f>
-        <v/>
-      </c>
-      <c r="D6" s="5">
-        <f>Model!C81</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Gross savings in 2030</t>
-        </is>
-      </c>
-      <c r="B7" s="80">
-        <f>Model!G13</f>
-        <v/>
-      </c>
-      <c r="C7" s="80">
-        <f>Model!G41</f>
-        <v/>
-      </c>
-      <c r="D7" s="80">
-        <f>Model!G69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Full run-rate savings / yr</t>
-        </is>
-      </c>
-      <c r="B8" s="80">
-        <f>Model!C26</f>
-        <v/>
-      </c>
-      <c r="C8" s="80">
-        <f>Model!C54</f>
-        <v/>
-      </c>
-      <c r="D8" s="80">
-        <f>Model!C82</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Run-rate as % of conversion cost</t>
-        </is>
-      </c>
-      <c r="B9" s="36">
-        <f>Model!C27</f>
-        <v/>
-      </c>
-      <c r="C9" s="36">
-        <f>Model!C55</f>
-        <v/>
-      </c>
-      <c r="D9" s="36">
-        <f>Model!C83</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Implied cost index (today 106)</t>
-        </is>
-      </c>
-      <c r="B10" s="81">
-        <f>Model!C28</f>
-        <v/>
-      </c>
-      <c r="C10" s="81">
-        <f>Model!C56</f>
-        <v/>
-      </c>
-      <c r="D10" s="81">
-        <f>Model!C84</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Gap to new-player benchmark closed</t>
-        </is>
-      </c>
-      <c r="B11" s="36">
-        <f>Model!C29</f>
-        <v/>
-      </c>
-      <c r="C11" s="36">
-        <f>Model!C57</f>
-        <v/>
-      </c>
-      <c r="D11" s="36">
-        <f>Model!C85</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>NPV incl. remaining equipment value</t>
-        </is>
-      </c>
-      <c r="B12" s="80">
-        <f>Model!C30</f>
-        <v/>
-      </c>
-      <c r="C12" s="80">
-        <f>Model!C58</f>
-        <v/>
-      </c>
-      <c r="D12" s="80">
-        <f>Model!C86</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Investment (Rp B)</t>
-        </is>
-      </c>
-      <c r="B13" s="80">
-        <f>Assumptions!B37</f>
-        <v/>
-      </c>
-      <c r="C13" s="80">
-        <f>Assumptions!C37</f>
-        <v/>
-      </c>
-      <c r="D13" s="80">
-        <f>Assumptions!D37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Variant modification time (months, today 9)</t>
-        </is>
-      </c>
-      <c r="B14" s="81">
-        <f>Assumptions!B40</f>
-        <v/>
-      </c>
-      <c r="C14" s="81">
-        <f>Assumptions!C40</f>
-        <v/>
-      </c>
-      <c r="D14" s="81">
-        <f>Assumptions!D40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Note: with pilot-light phasing the 2026 outflow is small, so IRR looks extreme. Lead with NPV and P(NPV&gt;0) from the Simulation tab, not IRR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Base case savings by lever</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Scrap</t>
-        </is>
-      </c>
-      <c r="B17" s="80">
-        <f>Model!C36</f>
-        <v/>
-      </c>
-      <c r="C17" s="80">
-        <f>Model!D36</f>
-        <v/>
-      </c>
-      <c r="D17" s="80">
-        <f>Model!E36</f>
-        <v/>
-      </c>
-      <c r="E17" s="80">
-        <f>Model!F36</f>
-        <v/>
-      </c>
-      <c r="F17" s="80">
-        <f>Model!G36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B18" s="80">
-        <f>Model!C37</f>
-        <v/>
-      </c>
-      <c r="C18" s="80">
-        <f>Model!D37</f>
-        <v/>
-      </c>
-      <c r="D18" s="80">
-        <f>Model!E37</f>
-        <v/>
-      </c>
-      <c r="E18" s="80">
-        <f>Model!F37</f>
-        <v/>
-      </c>
-      <c r="F18" s="80">
-        <f>Model!G37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Operator NVA</t>
-        </is>
-      </c>
-      <c r="B19" s="80">
-        <f>Model!C38</f>
-        <v/>
-      </c>
-      <c r="C19" s="80">
-        <f>Model!D38</f>
-        <v/>
-      </c>
-      <c r="D19" s="80">
-        <f>Model!E38</f>
-        <v/>
-      </c>
-      <c r="E19" s="80">
-        <f>Model!F38</f>
-        <v/>
-      </c>
-      <c r="F19" s="80">
-        <f>Model!G38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="B20" s="80">
-        <f>Model!C39</f>
-        <v/>
-      </c>
-      <c r="C20" s="80">
-        <f>Model!D39</f>
-        <v/>
-      </c>
-      <c r="D20" s="80">
-        <f>Model!E39</f>
-        <v/>
-      </c>
-      <c r="E20" s="80">
-        <f>Model!F39</f>
-        <v/>
-      </c>
-      <c r="F20" s="80">
-        <f>Model!G39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Variant modification</t>
-        </is>
-      </c>
-      <c r="B21" s="80">
-        <f>Model!C40</f>
-        <v/>
-      </c>
-      <c r="C21" s="80">
-        <f>Model!D40</f>
-        <v/>
-      </c>
-      <c r="D21" s="80">
-        <f>Model!E40</f>
-        <v/>
-      </c>
-      <c r="E21" s="80">
-        <f>Model!F40</f>
-        <v/>
-      </c>
-      <c r="F21" s="80">
-        <f>Model!G40</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
 </file>
--- a/cases/bcc-tmmin/model/TMMIN_Case_Model.xlsx
+++ b/cases/bcc-tmmin/model/TMMIN_Case_Model.xlsx
@@ -11,19 +11,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer_Guide" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ideation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulation2" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulation1" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulation" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exhibits" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Breakeven" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capability" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPIs" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA_Bank" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulation4" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulation3" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulation2" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulation1" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulation" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exhibits" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Breakeven" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capability" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPIs" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA_Bank" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -435,12 +437,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Simulation2'!$A$42:$A$46</f>
+              <f>'Simulation4'!$A$42:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Simulation2'!$B$42:$B$46</f>
+              <f>'Simulation4'!$B$42:$B$46</f>
             </numRef>
           </val>
         </ser>
@@ -478,305 +480,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>NPV across 10,000 runs (Rp B)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Simulation2'!$A$75:$A$90</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Simulation2'!$B$75:$B$90</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="10"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Scrap reduction falls as alerts are dismissed</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Simulation1'!$A$42:$A$46</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Simulation1'!$B$42:$B$46</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <numFmt formatCode="0%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>NPV across 10,000 runs (Rp B)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Simulation1'!$A$75:$A$90</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Simulation1'!$B$75:$B$90</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="10"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Scrap reduction falls as alerts are dismissed</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Simulation'!$A$42:$A$46</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Simulation'!$B$42:$B$46</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <numFmt formatCode="0%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -850,7 +554,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -924,7 +628,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -1103,6 +807,602 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>NPV across 10,000 runs (Rp B)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Simulation4'!$A$75:$A$90</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Simulation4'!$B$75:$B$90</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="10"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Scrap reduction falls as alerts are dismissed</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Simulation3'!$A$42:$A$46</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Simulation3'!$B$42:$B$46</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>NPV across 10,000 runs (Rp B)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Simulation3'!$A$75:$A$90</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Simulation3'!$B$75:$B$90</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="10"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Scrap reduction falls as alerts are dismissed</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Simulation2'!$A$42:$A$46</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Simulation2'!$B$42:$B$46</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>NPV across 10,000 runs (Rp B)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Simulation2'!$A$75:$A$90</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Simulation2'!$B$75:$B$90</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="10"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Scrap reduction falls as alerts are dismissed</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Simulation1'!$A$42:$A$46</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Simulation1'!$B$42:$B$46</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>NPV across 10,000 runs (Rp B)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Simulation1'!$A$75:$A$90</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Simulation1'!$B$75:$B$90</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="10"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Scrap reduction falls as alerts are dismissed</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Simulation'!$A$42:$A$46</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Simulation'!$B$42:$B$46</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -1251,6 +1551,104 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>40</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="2160000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>73</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2520000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>40</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="2160000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>73</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2520000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1904,6 +2302,2010 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Case exhibits, re-typed (verify red cells against the PDF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Exhibit 1. National car sales (units)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Wholesales</t>
+        </is>
+      </c>
+      <c r="B5" s="73" t="n">
+        <v>865723</v>
+      </c>
+      <c r="C5" s="73" t="n">
+        <v>803687</v>
+      </c>
+      <c r="D5" s="28">
+        <f>C5/B5-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Retail sales</t>
+        </is>
+      </c>
+      <c r="B6" s="73" t="n">
+        <v>889680</v>
+      </c>
+      <c r="C6" s="73" t="n">
+        <v>833692</v>
+      </c>
+      <c r="D6" s="28">
+        <f>C6/B6-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Exhibit 3. Conversion cost index, Karawang (TMMIN 2023 = 100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>TMMIN</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>New-player benchmark</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>TMMIN vs benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="D10" s="28">
+        <f>B10/C10-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="D11" s="28">
+        <f>B11/C11-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="D12" s="28">
+        <f>B12/C12-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Exhibit 4. Quality &amp; productivity baseline (index 2023 = 100 unless stated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Scrap (index)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Verified from casebook PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Unplanned downtime (index)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>111</v>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Verified from casebook PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Defects escaping to downstream (index)</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Verified from casebook PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Operator non-value-added time (% hours)</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C19" s="20" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Verified from casebook PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Equipment modification time, new variant (months)</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Verified from casebook PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Exhibit 5. Automation maturity (1 manual, 2 semi-auto, 3 auto+integrated, 4 autonomous)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Gap to L4</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Key condition</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Press shop</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="2">
+        <f>4-B24</f>
+        <v/>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Die changes and panel quality checks rely on operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Casting</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" s="2">
+        <f>4-B25</f>
+        <v/>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Finishing, handling, inspection partly manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Machining &amp; engine assembly</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="2">
+        <f>4-B26</f>
+        <v/>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Assembly and inspection partly manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Body welding: spot welding</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" s="2">
+        <f>4-B27</f>
+        <v/>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Programmed robots integrated in line</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Body welding: sealer application</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" s="2">
+        <f>4-B28</f>
+        <v/>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Manual/semi-auto; no automatic quality feedback</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Painting</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" s="2">
+        <f>4-B29</f>
+        <v/>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Quality check and defect repair manual visual</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Final assembly</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" s="2">
+        <f>4-B30</f>
+        <v/>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Manual with tools; high variant mix handled by operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Quality inspection</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="2">
+        <f>4-B31</f>
+        <v/>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Manual visual; in-house AI camera (from CCTV) in validation to Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Intralogistics</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" s="2">
+        <f>4-B32</f>
+        <v/>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Manual forklifts/dollies; AGV/AMR pilots</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" s="2">
+        <f>4-B33</f>
+        <v/>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Periodic preventive, not predictive</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Equipment &amp; system integration</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" s="2">
+        <f>4-B34</f>
+        <v/>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Point-to-point; no common interface standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Data integration</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="2">
+        <f>4-B35</f>
+        <v/>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Data scattered; equipment, quality, logistics not connected</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Exhibit 6A. Engineering time, knowledge &amp; improvement (production engineering)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>Engineer time on routine support &amp; troubleshooting (%)</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="C39" s="20" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>Verified; the remaining ~10% is other work</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>Engineer time on improvement &amp; new development (%)</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C40" s="20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>Critical know-how documented in shared form (%)</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C41" s="20" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>Critical processes whose know-how rests with 1-2 seniors (%)</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C42" s="20" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>Months for new engineer to work independently</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>Improvement ideas per engineer per year</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>Ideas implemented (% of submitted)</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C45" s="20" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D45" s="11" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Exhibit 6B. Operator &amp; team-leader perception, pilot area (2025, N = 120)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Indicator</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr"/>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>So what</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>Say new tech helps rather than replaces their work</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>46% are not convinced: change management is a real risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>Have received training on data-driven tools</t>
+        </is>
+      </c>
+      <c r="B50" s="20" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>Training gap is the biggest adoption blocker</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>Frequently override or ignore automated alerts</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>Tech without trust = no value; design alerts with operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>Know-how shared mainly via informal on-the-job coaching</t>
+        </is>
+      </c>
+      <c r="B52" s="20" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>Supports knowledge-capture idea</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>Would contribute ideas if an easy channel existed</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>Latent kaizen energy: biggest people opportunity</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Exhibit 7. Engineering competence (members per level, N = 30 per field)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>L1 basic</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>L2 intermediate</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>L3 proficient</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>L4 expert</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>% at L3+</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F57" s="2">
+        <f>SUM(B57:E57)</f>
+        <v/>
+      </c>
+      <c r="G57" s="28">
+        <f>(D57+E57)/F57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F58" s="2">
+        <f>SUM(B58:E58)</f>
+        <v/>
+      </c>
+      <c r="G58" s="28">
+        <f>(D58+E58)/F58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>PLC</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" s="2">
+        <f>SUM(B59:E59)</f>
+        <v/>
+      </c>
+      <c r="G59" s="28">
+        <f>(D59+E59)/F59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="2">
+        <f>SUM(B60:E60)</f>
+        <v/>
+      </c>
+      <c r="G60" s="28">
+        <f>(D60+E60)/F60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Software &amp; AI</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="2">
+        <f>SUM(B61:E61)</f>
+        <v/>
+      </c>
+      <c r="G61" s="28">
+        <f>(D61+E61)/F61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Verified from casebook PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Exhibit 8. Volume share by pathway (indicative)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>Pathway</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>2030 moderate</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>2030 aggressive</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Conventional (ICE)</t>
+        </is>
+      </c>
+      <c r="B66" s="20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C66" s="20" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D66" s="20" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>HEV</t>
+        </is>
+      </c>
+      <c r="B67" s="20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C67" s="20" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D67" s="20" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>PHEV</t>
+        </is>
+      </c>
+      <c r="B68" s="20" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C68" s="20" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D68" s="20" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="B69" s="20" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C69" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D69" s="20" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Electrified share (HEV+PHEV+BEV)</t>
+        </is>
+      </c>
+      <c r="B70" s="28">
+        <f>SUM(B67:B69)</f>
+        <v/>
+      </c>
+      <c r="C70" s="28">
+        <f>SUM(C67:C69)</f>
+        <v/>
+      </c>
+      <c r="D70" s="28">
+        <f>SUM(D67:D69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Exhibit 9 parameters are in the Assumptions tab (rows 4-15).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Case parameter (Exhibit 9 / text)</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Source / note</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installed capacity, Karawang I + II</t>
+        </is>
+      </c>
+      <c r="B4" s="73" t="n">
+        <v>250000</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>units/yr</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Exhibit 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Capacity utilization 2025</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Exhibit 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Production volume</t>
+        </is>
+      </c>
+      <c r="B6" s="74">
+        <f>B4*B5</f>
+        <v/>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>units/yr</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Formula (case: ~175,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Conversion cost per unit 2025</t>
+        </is>
+      </c>
+      <c r="B7" s="75" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Rp million</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Exhibit 9 (labor, energy, maintenance, depreciation, scrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Total annual conversion cost</t>
+        </is>
+      </c>
+      <c r="B8" s="76">
+        <f>B6*B7/1000</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Rp billion</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Formula (case: ~Rp560B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Discount rate</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>%/yr</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Exhibit 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Labor &amp; energy cost escalation</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>%/yr</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Exhibit 9, applied to savings</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Technology economic life</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Exhibit 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TMMIN conversion cost index 2025</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Exhibit 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>New-player benchmark index 2025</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Exhibit 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Operator non-value-added time</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>% hours</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Exhibit 4 / text</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Equipment modification time per new variant</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Exhibit 4 / text</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Conversion cost split (TEAM ASSUMPTION, case gives components only)</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Rp billion</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Justify with</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Labor</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C18" s="76">
+        <f>B18*$B$8</f>
+        <v/>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>No public source splits conversion cost. Stated team assumption; Monte Carlo tests labor share 35-45% (Simulation tab). Ask organizers in clarification if allowed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C19" s="76">
+        <f>B19*$B$8</f>
+        <v/>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>No public source splits conversion cost. Stated team assumption; Monte Carlo tests labor share 35-45% (Simulation tab). Ask organizers in clarification if allowed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="C20" s="76">
+        <f>B20*$B$8</f>
+        <v/>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>No public source splits conversion cost. Stated team assumption; Monte Carlo tests labor share 35-45% (Simulation tab). Ask organizers in clarification if allowed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C21" s="76">
+        <f>B21*$B$8</f>
+        <v/>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>No public source splits conversion cost. Stated team assumption; Monte Carlo tests labor share 35-45% (Simulation tab). Ask organizers in clarification if allowed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Scrap</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C22" s="76">
+        <f>B22*$B$8</f>
+        <v/>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>No public source splits conversion cost. Stated team assumption; Monte Carlo tests labor share 35-45% (Simulation tab). Ask organizers in clarification if allowed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Check (must be 100%)</t>
+        </is>
+      </c>
+      <c r="B23" s="28">
+        <f>SUM(B18:B22)</f>
+        <v/>
+      </c>
+      <c r="C23" s="76">
+        <f>SUM(C18:C22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Other team assumptions</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>New variant / model-change projects per year</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>projects/yr</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Rises with multi-pathway mix (Exhibit 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Average cost per equipment modification project</t>
+        </is>
+      </c>
+      <c r="B27" s="77" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Rp billion</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Team assumption, no public source. Tornado shows its NPV swing (Simulation Test 3); state it openly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Share of freed operator time converted to cash</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Rest is redeployed to kaizen / absorbs volume (no layoffs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Lever assumptions by scenario</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Optimistic</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>What drives it / how to defend</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr"/>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>Benchmark evidence (cite in appendix)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Scrap cost reduction</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D32" s="24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>Closed-loop feedback catches sealer/inspection lapses upstream (Exhibit 4/5)</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>Own simulation (Simulation tab): closed loop cuts in-scope scrap ~85%; x 40% scope share = ~34% plant-wide. Base 35% sits on that result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="54" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>Maintenance cost reduction</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C33" s="24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D33" s="24" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>Predictive maintenance + fewer unplanned stops</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>McKinsey (2020, via IIoT World): maintenance cost -18 to 25%, unplanned downtime up to -50%. Our range is deliberately below. https://www.iiot-world.com/predictive-analytics/predictive-maintenance/predictive-maintenance-cost-savings/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="54" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>Operator NVA time eliminated (% of the 22%)</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C34" s="24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D34" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>Intralogistics sync, digital standard work, less searching/waiting</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>Toyota AI Platform: &gt;10,000 man-hours/yr saved by worker-built tools (Google Cloud 2024). Omron/MPA AMR case: up to 15 km/day of operator walking and all manual crate runs eliminated (no % published). Validate with a time study in the pilot. https://robotics.omron.com/case-studies/amr-automation-intralogistics-mpa-omron/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="54" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>Energy cost reduction</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C35" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D35" s="24" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>Data-driven idle/standby control</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>Nissan US plants, energy management system (ISO 50001 / SEP): 13.8% energy performance gain over 3 years, 8-21% by site. Our 2-8% is deliberately below. https://www.cleanenergyministerial.org/content/uploads/2022/03/cem-em-casestudy-nissan-usa.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="54" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>Variant modification cost reduction</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C36" s="24" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D36" s="24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>Common interface standard + in-house equipment + virtual verification</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>Siemens / Wipro PARI: virtual commissioning cut on-site commissioning 70% on a 17-variant engine line. Kalypso: up to 40%. Toyota BEV plan targets halving prep lead time. https://resources.sw.siemens.com/en-US/case-study-wipro-pari/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="54" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>Total program investment</t>
+        </is>
+      </c>
+      <c r="B37" s="77" t="n">
+        <v>110</v>
+      </c>
+      <c r="C37" s="77" t="n">
+        <v>80</v>
+      </c>
+      <c r="D37" s="77" t="n">
+        <v>60</v>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>Must sit inside case range Rp40-120B</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>Case Exhibit 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="54" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>Annual running cost (% of cumulative investment)</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C38" s="24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D38" s="24" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>Licences, cloud/compute, upkeep</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>Team assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="54" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>Training &amp; change management opex</t>
+        </is>
+      </c>
+      <c r="B39" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="C39" s="77" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D39" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>Rp billion/yr: academy, coaches, kaizen time</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>Team assumption; cross-check with Capability tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Implied variant modification time (months)</t>
+        </is>
+      </c>
+      <c r="B40" s="78">
+        <f>$B$15*(1-B36)</f>
+        <v/>
+      </c>
+      <c r="C40" s="78">
+        <f>$B$15*(1-C36)</f>
+        <v/>
+      </c>
+      <c r="D40" s="78">
+        <f>$B$15*(1-D36)</f>
+        <v/>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>Show this on the flexibility slide (vs 9 months today)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Timing</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>Sum / note</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Adoption ramp-up (% of full run-rate)</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C43" s="24" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D43" s="24" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E43" s="24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F43" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Pilot -&gt; standardize -&gt; rollout</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Investment phasing (% of total): PILOT-LIGHT</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C44" s="24" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D44" s="24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E44" s="24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F44" s="24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G44" s="28">
+        <f>SUM(B44:F44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Year index (t)</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>End-of-year discounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Reference only: original front-loaded phasing</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C46" s="20" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D46" s="20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E46" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F46" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Why pilot-light: Simulation tab Test 2b. Spending little before the end-2027 gate raised P(NPV&gt;0) from ~49% to ~85% across 10,000 runs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4048,7 +6450,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4483,7 +6885,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4866,7 +7268,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5739,7 +8141,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6310,7 +8712,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6700,7 +9102,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7152,7 +9554,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17027,1082 +19429,1362 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Case exhibits, re-typed (verify red cells against the PDF)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Exhibit 1. National car sales (units)</t>
+          <t>Idea tests: simulation results (values produced by run_tests.py, not formulas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="54" t="inlineStr">
+        <is>
+          <t>Re-run run_tests.py after changing assumptions. Process parameters below are illustrative assumptions, not TMMIN data: present them as a mechanism test, and show the sensitivity.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Change</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>TEST 1. Does closing the quality loop beat adding technology alone? (sealer drift -&gt; inspection -&gt; feedback, 1 year, 175,000 units, 300 runs)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Wholesales</t>
-        </is>
-      </c>
-      <c r="B5" s="73" t="n">
-        <v>865723</v>
-      </c>
-      <c r="C5" s="73" t="n">
-        <v>803687</v>
-      </c>
-      <c r="D5" s="28">
-        <f>C5/B5-1</f>
-        <v/>
+      <c r="A5" s="55" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>Defective units / yr</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>Scrapped units / yr</t>
+        </is>
+      </c>
+      <c r="D5" s="55" t="inlineStr">
+        <is>
+          <t>Escaped defects / yr</t>
+        </is>
+      </c>
+      <c r="E5" s="55" t="inlineStr">
+        <is>
+          <t>Units built while drifting</t>
+        </is>
+      </c>
+      <c r="F5" s="55" t="inlineStr">
+        <is>
+          <t>Scrap vs today</t>
+        </is>
+      </c>
+      <c r="G5" s="55" t="inlineStr">
+        <is>
+          <t>Escapes vs today</t>
+        </is>
+      </c>
+      <c r="H5" s="55" t="inlineStr">
+        <is>
+          <t>Scrap P5-P95</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Retail sales</t>
-        </is>
-      </c>
-      <c r="B6" s="73" t="n">
-        <v>889680</v>
-      </c>
-      <c r="C6" s="73" t="n">
-        <v>833692</v>
-      </c>
-      <c r="D6" s="28">
-        <f>C6/B6-1</f>
-        <v/>
+      <c r="A6" s="56" t="inlineStr">
+        <is>
+          <t>1. Today: visual at final inspection, manual feedback</t>
+        </is>
+      </c>
+      <c r="B6" s="57" t="n">
+        <v>4266.68</v>
+      </c>
+      <c r="C6" s="57" t="n">
+        <v>1088.524</v>
+      </c>
+      <c r="D6" s="57" t="n">
+        <v>638.2666666666667</v>
+      </c>
+      <c r="E6" s="57" t="n">
+        <v>15796.09333333333</v>
+      </c>
+      <c r="F6" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="57" t="inlineStr">
+        <is>
+          <t>835 - 1,365</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="56" t="inlineStr">
+        <is>
+          <t>2. Better camera at end-of-line only (tech, no loop)</t>
+        </is>
+      </c>
+      <c r="B7" s="57" t="n">
+        <v>4265.323333333334</v>
+      </c>
+      <c r="C7" s="57" t="n">
+        <v>1215.776</v>
+      </c>
+      <c r="D7" s="57" t="n">
+        <v>212.7366666666667</v>
+      </c>
+      <c r="E7" s="57" t="n">
+        <v>15793.25666666667</v>
+      </c>
+      <c r="F7" s="58" t="n">
+        <v>0.1169032561523677</v>
+      </c>
+      <c r="G7" s="58" t="n">
+        <v>-0.6666962607060789</v>
+      </c>
+      <c r="H7" s="57" t="inlineStr">
+        <is>
+          <t>910 - 1,492</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Exhibit 3. Conversion cost index, Karawang (TMMIN 2023 = 100)</t>
+      <c r="A8" s="56" t="inlineStr">
+        <is>
+          <t>3. Closed loop at sealer, 31% of alerts dismissed (as today)</t>
+        </is>
+      </c>
+      <c r="B8" s="57" t="n">
+        <v>1652.95</v>
+      </c>
+      <c r="C8" s="57" t="n">
+        <v>362.1536666666667</v>
+      </c>
+      <c r="D8" s="57" t="n">
+        <v>203.26</v>
+      </c>
+      <c r="E8" s="57" t="n">
+        <v>5247.72</v>
+      </c>
+      <c r="F8" s="58" t="n">
+        <v>-0.6672984089770491</v>
+      </c>
+      <c r="G8" s="58" t="n">
+        <v>-0.6815437643618132</v>
+      </c>
+      <c r="H8" s="57" t="inlineStr">
+        <is>
+          <t>216 - 543</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>TMMIN</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>New-player benchmark</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>TMMIN vs benchmark</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>94</v>
-      </c>
-      <c r="D10" s="28">
-        <f>B10/C10-1</f>
-        <v/>
+      <c r="A9" s="59" t="inlineStr">
+        <is>
+          <t>4. Closed loop with people-centred design (10% dismissed)</t>
+        </is>
+      </c>
+      <c r="B9" s="60" t="n">
+        <v>908.3233333333334</v>
+      </c>
+      <c r="C9" s="60" t="n">
+        <v>166.8633333333333</v>
+      </c>
+      <c r="D9" s="60" t="n">
+        <v>88.00666666666666</v>
+      </c>
+      <c r="E9" s="60" t="n">
+        <v>2257.006666666667</v>
+      </c>
+      <c r="F9" s="61" t="n">
+        <v>-0.8467067943992661</v>
+      </c>
+      <c r="G9" s="61" t="n">
+        <v>-0.862116147900564</v>
+      </c>
+      <c r="H9" s="60" t="inlineStr">
+        <is>
+          <t>83 - 270</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>103</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>91</v>
-      </c>
-      <c r="D11" s="28">
-        <f>B11/C11-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>106</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>89</v>
-      </c>
-      <c r="D12" s="28">
-        <f>B12/C12-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Exhibit 4. Quality &amp; productivity baseline (index 2023 = 100 unless stated)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Scrap (index)</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>108</v>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>Verified from casebook PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Unplanned downtime (index)</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>111</v>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>Verified from casebook PDF</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>What this shows</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="62" t="inlineStr">
+        <is>
+          <t>- A better camera at end-of-line alone changes scrap by +12% while escapes fall 67%: it catches more bad units, but too late, so escapes turn into scrap. It does not prevent defects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="62" t="inlineStr">
+        <is>
+          <t>- Closing the loop right after the sealer cuts scrap 85% and escapes 86%, because a drift is stopped within a few units instead of hundreds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="62" t="inlineStr">
+        <is>
+          <t>- If operators dismiss alerts in 31% of drift episodes (today's override rate), scrap reduction falls to 67%. Trust, training and alert design are part of the value, not an add-on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="62" t="inlineStr">
+        <is>
+          <t>- Plant-wide: if the pilot scope causes 40% of plant scrap (team assumption), the plant-wide scrap cut is about 34%. Compare with the 20% / 35% / 50% lever in Assumptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="62" t="inlineStr">
+        <is>
+          <t>- Deck message: value comes from redesigning the system (where the check sits, how fast the signal travels, who acts on it), not from buying the device. That is exactly the case ask.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Defects escaping to downstream (index)</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>103</v>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>Verified from casebook PDF</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Process assumptions used (illustrative, change and re-run)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Operator non-value-added time (% hours)</t>
+      <c r="A19" s="54" t="inlineStr">
+        <is>
+          <t>Defect probability per unit, stable sealer</t>
         </is>
       </c>
       <c r="B19" s="20" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C19" s="20" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>Verified from casebook PDF</t>
-        </is>
+        <v>0.002</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Equipment modification time, new variant (months)</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>Verified from casebook PDF</t>
-        </is>
+      <c r="A20" s="54" t="inlineStr">
+        <is>
+          <t>Average units between drift events</t>
+        </is>
+      </c>
+      <c r="B20" s="63" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="54" t="inlineStr">
+        <is>
+          <t>Defect probability per unit while drifting</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Exhibit 5. Automation maturity (1 manual, 2 semi-auto, 3 auto+integrated, 4 autonomous)</t>
-        </is>
+      <c r="A22" s="54" t="inlineStr">
+        <is>
+          <t>Manual visual detection rate at final inspection</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="n">
+        <v>0.85</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Level</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Gap to L4</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Key condition</t>
-        </is>
+      <c r="A23" s="54" t="inlineStr">
+        <is>
+          <t>Share of sealer defect modes the in-line AI camera can see</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Press shop</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C24" s="2">
-        <f>4-B24</f>
-        <v/>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>Die changes and panel quality checks rely on operators</t>
-        </is>
+      <c r="A24" s="54" t="inlineStr">
+        <is>
+          <t>Units between sealer and today's final inspection</t>
+        </is>
+      </c>
+      <c r="B24" s="63" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Casting</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C25" s="2">
-        <f>4-B25</f>
-        <v/>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>Finishing, handling, inspection partly manual</t>
-        </is>
+      <c r="A25" s="54" t="inlineStr">
+        <is>
+          <t>Units built before manual feedback reaches the sealer</t>
+        </is>
+      </c>
+      <c r="B25" s="63" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Machining &amp; engine assembly</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C26" s="2">
-        <f>4-B26</f>
-        <v/>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>Assembly and inspection partly manual</t>
-        </is>
+      <c r="A26" s="54" t="inlineStr">
+        <is>
+          <t>Share of late-found defects scrapped</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Body welding: spot welding</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C27" s="2">
-        <f>4-B27</f>
-        <v/>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>Programmed robots integrated in line</t>
-        </is>
+      <c r="A27" s="54" t="inlineStr">
+        <is>
+          <t>Share of early-found defects scrapped</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Body welding: sealer application</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C28" s="2">
-        <f>4-B28</f>
-        <v/>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>Manual/semi-auto; no automatic quality feedback</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Painting</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C29" s="2">
-        <f>4-B29</f>
-        <v/>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>Quality check and defect repair manual visual</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Final assembly</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C30" s="2">
-        <f>4-B30</f>
-        <v/>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>Manual with tools; high variant mix handled by operators</t>
+      <c r="A28" s="54" t="inlineStr">
+        <is>
+          <t>Share of plant scrap from the pilot scope (team assumption)</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="62" t="inlineStr">
+        <is>
+          <t>In-line check: 5 units after sealer, automatic feedback within 10 units, 90% detection on visible defect modes (case: AI camera in validation to Oct 2026).</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Quality inspection</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="2">
-        <f>4-B31</f>
-        <v/>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>Manual visual; in-house AI camera (from CCTV) in validation to Oct 2026</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Robustness: closed-loop (scenario 4) scrap reduction vs today when each assumption changes</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Intralogistics</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C32" s="2">
-        <f>4-B32</f>
-        <v/>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>Manual forklifts/dollies; AGV/AMR pilots</t>
+      <c r="A32" s="55" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="B32" s="55" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C32" s="55" t="inlineStr">
+        <is>
+          <t>Reduction</t>
+        </is>
+      </c>
+      <c r="D32" s="55" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E32" s="55" t="inlineStr">
+        <is>
+          <t>Reduction</t>
+        </is>
+      </c>
+      <c r="F32" s="55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G32" s="55" t="inlineStr">
+        <is>
+          <t>Reduction</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C33" s="2">
-        <f>4-B33</f>
-        <v/>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>Periodic preventive, not predictive</t>
-        </is>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>AI camera coverage of defect modes</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C33" s="64" t="n">
+        <v>0.8247043005741556</v>
+      </c>
+      <c r="D33" s="20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E33" s="64" t="n">
+        <v>0.8468422609923756</v>
+      </c>
+      <c r="F33" s="20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G33" s="64" t="n">
+        <v>0.8667088181512177</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Equipment &amp; system integration</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C34" s="2">
-        <f>4-B34</f>
-        <v/>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>Point-to-point; no common interface standard</t>
-        </is>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Drift defect rate</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C34" s="64" t="n">
+        <v>0.8026017993273447</v>
+      </c>
+      <c r="D34" s="20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E34" s="64" t="n">
+        <v>0.8479906256107048</v>
+      </c>
+      <c r="F34" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G34" s="64" t="n">
+        <v>0.8649243431242232</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Data integration</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="2">
-        <f>4-B35</f>
-        <v/>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>Data scattered; equipment, quality, logistics not connected</t>
-        </is>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Units between drift events</t>
+        </is>
+      </c>
+      <c r="B35" s="63" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C35" s="64" t="n">
+        <v>0.8634074536698797</v>
+      </c>
+      <c r="D35" s="63" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E35" s="64" t="n">
+        <v>0.8582510378017658</v>
+      </c>
+      <c r="F35" s="63" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G35" s="64" t="n">
+        <v>0.8336816505910225</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Late-found scrap share</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C36" s="64" t="n">
+        <v>0.8314626883200975</v>
+      </c>
+      <c r="D36" s="20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E36" s="64" t="n">
+        <v>0.8538779573335564</v>
+      </c>
+      <c r="F36" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G36" s="64" t="n">
+        <v>0.8501771115300518</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Exhibit 6A. Engineering time, knowledge &amp; improvement (production engineering)</t>
-        </is>
+          <t>Units from sealer to today's inspection</t>
+        </is>
+      </c>
+      <c r="B37" s="63" t="n">
+        <v>100</v>
+      </c>
+      <c r="C37" s="64" t="n">
+        <v>0.8111230466252334</v>
+      </c>
+      <c r="D37" s="63" t="n">
+        <v>300</v>
+      </c>
+      <c r="E37" s="64" t="n">
+        <v>0.8492533988756621</v>
+      </c>
+      <c r="F37" s="63" t="n">
+        <v>600</v>
+      </c>
+      <c r="G37" s="64" t="n">
+        <v>0.8737976071910339</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Lowest scrap reduction across all tested cases: 80%. The mechanism holds even with pessimistic process assumptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>People test: how much value is lost when operators dismiss alerts?</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="55" t="inlineStr">
+        <is>
+          <t>Share of drift episodes where alerts are dismissed</t>
+        </is>
+      </c>
+      <c r="B41" s="55" t="inlineStr">
+        <is>
+          <t>Scrap reduction vs today</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="B42" s="64" t="n">
+        <v>0.9392930243154951</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B43" s="64" t="n">
+        <v>0.8445760803926541</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B44" s="64" t="n">
+        <v>0.7497194978398884</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="B45" s="64" t="n">
+        <v>0.6431060163426193</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B46" s="64" t="n">
+        <v>0.4964125733562145</v>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="62" t="inlineStr">
+        <is>
+          <t>Exhibit 6B says 31% of operators frequently override alerts today. This chart is the quantified case for the people part of the idea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>TEST 2. Is the business case robust? Financial Monte Carlo (10,000 runs, mirrors the Model tab incl. pilot-light phasing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="55" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="B50" s="55" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C50" s="55" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>Engineer time on routine support &amp; troubleshooting (%)</t>
-        </is>
-      </c>
-      <c r="B39" s="20" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="C39" s="20" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>Verified; the remaining ~10% is other work</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>Engineer time on improvement &amp; new development (%)</t>
-        </is>
-      </c>
-      <c r="B40" s="20" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="C40" s="20" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D40" s="11" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>Critical know-how documented in shared form (%)</t>
-        </is>
-      </c>
-      <c r="B41" s="20" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="C41" s="20" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="D41" s="11" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>Critical processes whose know-how rests with 1-2 seniors (%)</t>
-        </is>
-      </c>
-      <c r="B42" s="20" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="C42" s="20" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="D42" s="11" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>Months for new engineer to work independently</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D43" s="11" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>Improvement ideas per engineer per year</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="D44" s="11" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>Ideas implemented (% of submitted)</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="C45" s="20" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="D45" s="11" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Exhibit 6B. Operator &amp; team-leader perception, pilot area (2025, N = 120)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>Indicator</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Share</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr"/>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>So what</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>Say new tech helps rather than replaces their work</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="D49" s="11" t="inlineStr">
-        <is>
-          <t>46% are not convinced: change management is a real risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>Have received training on data-driven tools</t>
-        </is>
-      </c>
-      <c r="B50" s="20" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D50" s="11" t="inlineStr">
-        <is>
-          <t>Training gap is the biggest adoption blocker</t>
-        </is>
-      </c>
-    </row>
     <row r="51">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>Frequently override or ignore automated alerts</t>
-        </is>
-      </c>
-      <c r="B51" s="20" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="D51" s="11" t="inlineStr">
-        <is>
-          <t>Tech without trust = no value; design alerts with operators</t>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Deterministic base NPV (check vs Model tab)</t>
+        </is>
+      </c>
+      <c r="B51" s="65" t="n">
+        <v>27.01403870465879</v>
+      </c>
+      <c r="C51" s="54" t="inlineStr">
+        <is>
+          <t>Should match Dashboard base NPV</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>Know-how shared mainly via informal on-the-job coaching</t>
-        </is>
-      </c>
-      <c r="B52" s="20" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>Supports knowledge-capture idea</t>
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Mean NPV</t>
+        </is>
+      </c>
+      <c r="B52" s="65" t="n">
+        <v>11.82360761131173</v>
+      </c>
+      <c r="C52" s="54" t="inlineStr">
+        <is>
+          <t>Rp billion</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>Would contribute ideas if an easy channel existed</t>
-        </is>
-      </c>
-      <c r="B53" s="20" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>Latent kaizen energy: biggest people opportunity</t>
-        </is>
-      </c>
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>P5 NPV (bad case)</t>
+        </is>
+      </c>
+      <c r="B53" s="65" t="n">
+        <v>-19.41291040060244</v>
+      </c>
+      <c r="C53" s="54" t="inlineStr">
+        <is>
+          <t>1-in-20 downside</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Median NPV</t>
+        </is>
+      </c>
+      <c r="B54" s="65" t="n">
+        <v>11.7084469092985</v>
+      </c>
+      <c r="C54" s="54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Exhibit 7. Engineering competence (members per level, N = 30 per field)</t>
-        </is>
-      </c>
+          <t>P95 NPV (good case)</t>
+        </is>
+      </c>
+      <c r="B55" s="65" t="n">
+        <v>43.10332192077205</v>
+      </c>
+      <c r="C55" s="54" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>L1 basic</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="inlineStr">
-        <is>
-          <t>L2 intermediate</t>
-        </is>
-      </c>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>L3 proficient</t>
-        </is>
-      </c>
-      <c r="E56" s="8" t="inlineStr">
-        <is>
-          <t>L4 expert</t>
-        </is>
-      </c>
-      <c r="F56" s="8" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="G56" s="8" t="inlineStr">
-        <is>
-          <t>% at L3+</t>
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Probability NPV &gt; 0</t>
+        </is>
+      </c>
+      <c r="B56" s="64" t="n">
+        <v>0.7311</v>
+      </c>
+      <c r="C56" s="54" t="inlineStr">
+        <is>
+          <t>Headline for the financial slide</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Mechanical</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D57" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="E57" s="4" t="n">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Median full run-rate savings (Rp B/yr)</t>
+        </is>
+      </c>
+      <c r="B57" s="65" t="n">
+        <v>49.0844126012166</v>
+      </c>
+      <c r="C57" s="54" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Median run-rate as % of conversion cost</t>
+        </is>
+      </c>
+      <c r="B58" s="64" t="n">
+        <v>0.08765073678788678</v>
+      </c>
+      <c r="C58" s="54" t="inlineStr">
+        <is>
+          <t>vs 16% gap to benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>TEST 2b. How should the roadmap spend the money? Same 10,000 runs, five strategies (gate = stop scaling if 2027 pilot adoption &lt; 80%; happens in 25% of runs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="55" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="B61" s="55" t="inlineStr">
+        <is>
+          <t>Mean NPV</t>
+        </is>
+      </c>
+      <c r="C61" s="55" t="inlineStr">
+        <is>
+          <t>P5 NPV</t>
+        </is>
+      </c>
+      <c r="D61" s="55" t="inlineStr">
+        <is>
+          <t>Median NPV</t>
+        </is>
+      </c>
+      <c r="E61" s="55" t="inlineStr">
+        <is>
+          <t>P95 NPV</t>
+        </is>
+      </c>
+      <c r="F61" s="55" t="inlineStr">
+        <is>
+          <t>P(NPV &gt; 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="66" t="inlineStr">
+        <is>
+          <t>A. Front-loaded phasing, no gate</t>
+        </is>
+      </c>
+      <c r="B62" s="67" t="n">
+        <v>-0.191332294676973</v>
+      </c>
+      <c r="C62" s="67" t="n">
+        <v>-32.83255089311962</v>
+      </c>
+      <c r="D62" s="67" t="n">
+        <v>-0.3737217276611755</v>
+      </c>
+      <c r="E62" s="67" t="n">
+        <v>32.5044161216826</v>
+      </c>
+      <c r="F62" s="58" t="n">
+        <v>0.4925</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="66" t="inlineStr">
+        <is>
+          <t>B. Front-loaded phasing + gate (65% already spent)</t>
+        </is>
+      </c>
+      <c r="B63" s="67" t="n">
+        <v>-3.79967892697686</v>
+      </c>
+      <c r="C63" s="67" t="n">
+        <v>-39.74590657971964</v>
+      </c>
+      <c r="D63" s="67" t="n">
+        <v>-2.962350007986172</v>
+      </c>
+      <c r="E63" s="67" t="n">
+        <v>32.40194504032392</v>
+      </c>
+      <c r="F63" s="58" t="n">
+        <v>0.4518</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="66" t="inlineStr">
+        <is>
+          <t>C. Pilot-light phasing, no gate (as in Model tab)</t>
+        </is>
+      </c>
+      <c r="B64" s="67" t="n">
+        <v>11.82360761131173</v>
+      </c>
+      <c r="C64" s="67" t="n">
+        <v>-19.41291040060244</v>
+      </c>
+      <c r="D64" s="67" t="n">
+        <v>11.7084469092985</v>
+      </c>
+      <c r="E64" s="67" t="n">
+        <v>43.10332192077205</v>
+      </c>
+      <c r="F64" s="58" t="n">
+        <v>0.7311</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="68" t="inlineStr">
+        <is>
+          <t>D. Pilot-light phasing + gate</t>
+        </is>
+      </c>
+      <c r="B65" s="69" t="n">
+        <v>15.05090030021514</v>
+      </c>
+      <c r="C65" s="69" t="n">
+        <v>-8.411626796801812</v>
+      </c>
+      <c r="D65" s="69" t="n">
+        <v>13.32040175184729</v>
+      </c>
+      <c r="E65" s="69" t="n">
+        <v>43.06772269056702</v>
+      </c>
+      <c r="F65" s="61" t="n">
+        <v>0.8595</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="66" t="inlineStr">
+        <is>
+          <t>E. D + remaining equipment life valued at book</t>
+        </is>
+      </c>
+      <c r="B66" s="67" t="n">
+        <v>36.01053481960803</v>
+      </c>
+      <c r="C66" s="67" t="n">
+        <v>6.476777490438207</v>
+      </c>
+      <c r="D66" s="67" t="n">
+        <v>36.96085240343595</v>
+      </c>
+      <c r="E66" s="67" t="n">
+        <v>67.48368978517901</v>
+      </c>
+      <c r="F66" s="58" t="n">
+        <v>0.9938</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="66" t="inlineStr">
+        <is>
+          <t>F. D but savings ramp one year slower (stress test)</t>
+        </is>
+      </c>
+      <c r="B67" s="67" t="n">
+        <v>-7.534233621168762</v>
+      </c>
+      <c r="C67" s="67" t="n">
+        <v>-31.89940806088983</v>
+      </c>
+      <c r="D67" s="67" t="n">
+        <v>-5.542507323532465</v>
+      </c>
+      <c r="E67" s="67" t="n">
+        <v>12.32550108470081</v>
+      </c>
+      <c r="F67" s="58" t="n">
+        <v>0.3242</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="66" t="inlineStr">
+        <is>
+          <t>G. F + remaining equipment life valued at book</t>
+        </is>
+      </c>
+      <c r="B68" s="67" t="n">
+        <v>13.42540089822414</v>
+      </c>
+      <c r="C68" s="67" t="n">
+        <v>-3.778779125254701</v>
+      </c>
+      <c r="D68" s="67" t="n">
+        <v>11.92716410770895</v>
+      </c>
+      <c r="E68" s="67" t="n">
+        <v>35.1241416528562</v>
+      </c>
+      <c r="F68" s="58" t="n">
+        <v>0.879</v>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="62" t="inlineStr">
+        <is>
+          <t>Pilot-light phasing: 10% / 15% / 40% / 25% / 10% of capex in 2026-2030. Ramp-up kept the same to isolate the effect of phasing; if scaling later also delays savings, the gain is smaller.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="58" customHeight="1">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>Reading: a gate only protects value if little money is spent before it. Gate after heavy spending (B) destroys value; pilot-light + gate (D) is the design to defend in SQ3. Valuing equipment life beyond 2030 (E) is legitimate but state it openly. Stress test (F): if savings arrive a year late, P(NPV&gt;0) falls to 32% (88% if remaining equipment life is valued, G). Speed of the pilot is the make-or-break factor: quick wins in 2026-27 belong in the roadmap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="45" customHeight="1">
+      <c r="A71" s="62" t="inlineStr">
+        <is>
+          <t>Ranges used (triangular low / mode / high): scrap 20/35/50%, maintenance 5/10/15%, NVA 15/30/45%, energy 2/5/8%, variant cost 20/35/50%, investment 60/80/110, running 8/9/12%, training 2/2.5/3, variant projects 2/3/5, cost per project 5/10/15, cash realization 30/50/70%, adoption 60/100/100%, labor share 35/40/45%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>NPV distribution (histogram)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="55" t="inlineStr">
+        <is>
+          <t>NPV bin from (Rp B)</t>
+        </is>
+      </c>
+      <c r="B74" s="55" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="65" t="n">
+        <v>-51.6</v>
+      </c>
+      <c r="B75" s="70" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="65" t="n">
+        <v>-41.6</v>
+      </c>
+      <c r="B76" s="70" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="65" t="n">
+        <v>-31.5</v>
+      </c>
+      <c r="B77" s="70" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="65" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="B78" s="70" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="65" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="B79" s="70" t="n">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="65" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="B80" s="70" t="n">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="65" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="B81" s="70" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="65" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="B82" s="70" t="n">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="65" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="B83" s="70" t="n">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="65" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="B84" s="70" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="65" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="B85" s="70" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="65" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="B86" s="70" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="65" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="B87" s="70" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="65" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="B88" s="70" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="65" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="B89" s="70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="65" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="B90" s="70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>TEST 3. Which assumption matters most? Tornado (base case, one at a time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="55" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="B93" s="55" t="inlineStr">
+        <is>
+          <t>Low input</t>
+        </is>
+      </c>
+      <c r="C93" s="55" t="inlineStr">
+        <is>
+          <t>High input</t>
+        </is>
+      </c>
+      <c r="D93" s="55" t="inlineStr">
+        <is>
+          <t>NPV at low</t>
+        </is>
+      </c>
+      <c r="E93" s="55" t="inlineStr">
+        <is>
+          <t>NPV at high</t>
+        </is>
+      </c>
+      <c r="F93" s="55" t="inlineStr">
+        <is>
+          <t>Swing</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="71" t="inlineStr">
+        <is>
+          <t>Investment (Rp B)</t>
+        </is>
+      </c>
+      <c r="B94" s="72" t="n">
+        <v>110</v>
+      </c>
+      <c r="C94" s="72" t="n">
+        <v>60</v>
+      </c>
+      <c r="D94" s="67" t="n">
+        <v>-1.497910926203485</v>
+      </c>
+      <c r="E94" s="67" t="n">
+        <v>46.02200512523363</v>
+      </c>
+      <c r="F94" s="67" t="n">
+        <v>47.51991605143711</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="71" t="inlineStr">
+        <is>
+          <t>Adoption achieved</t>
+        </is>
+      </c>
+      <c r="B95" s="58" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C95" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" s="67" t="n">
+        <v>-17.99510981953292</v>
+      </c>
+      <c r="E95" s="67" t="n">
+        <v>27.01403870465879</v>
+      </c>
+      <c r="F95" s="67" t="n">
+        <v>45.00914852419172</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="71" t="inlineStr">
+        <is>
+          <t>Scrap reduction</t>
+        </is>
+      </c>
+      <c r="B96" s="58" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C96" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D96" s="67" t="n">
+        <v>7.376539348554191</v>
+      </c>
+      <c r="E96" s="67" t="n">
+        <v>46.65153806076337</v>
+      </c>
+      <c r="F96" s="67" t="n">
+        <v>39.27499871220918</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="71" t="inlineStr">
+        <is>
+          <t>Variant projects / yr</t>
+        </is>
+      </c>
+      <c r="B97" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="C97" s="72" t="n">
         <v>5</v>
       </c>
-      <c r="F57" s="2">
-        <f>SUM(B57:E57)</f>
-        <v/>
-      </c>
-      <c r="G57" s="28">
-        <f>(D57+E57)/F57</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Electrical</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="n">
+      <c r="D97" s="67" t="n">
+        <v>18.83174730628188</v>
+      </c>
+      <c r="E97" s="67" t="n">
+        <v>43.37862150141261</v>
+      </c>
+      <c r="F97" s="67" t="n">
+        <v>24.54687419513073</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="71" t="inlineStr">
+        <is>
+          <t>Cost per variant project</t>
+        </is>
+      </c>
+      <c r="B98" s="72" t="n">
         <v>5</v>
       </c>
-      <c r="C58" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D58" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F58" s="2">
-        <f>SUM(B58:E58)</f>
-        <v/>
-      </c>
-      <c r="G58" s="28">
-        <f>(D58+E58)/F58</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>PLC</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="D59" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E59" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F59" s="2">
-        <f>SUM(B59:E59)</f>
-        <v/>
-      </c>
-      <c r="G59" s="28">
-        <f>(D59+E59)/F59</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Programming</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="C60" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="2">
-        <f>SUM(B60:E60)</f>
-        <v/>
-      </c>
-      <c r="G60" s="28">
-        <f>(D60+E60)/F60</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Software &amp; AI</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="C61" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D61" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="2">
-        <f>SUM(B61:E61)</f>
-        <v/>
-      </c>
-      <c r="G61" s="28">
-        <f>(D61+E61)/F61</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Verified from casebook PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>Exhibit 8. Volume share by pathway (indicative)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>Pathway</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C65" s="8" t="inlineStr">
-        <is>
-          <t>2030 moderate</t>
-        </is>
-      </c>
-      <c r="D65" s="8" t="inlineStr">
-        <is>
-          <t>2030 aggressive</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Conventional (ICE)</t>
-        </is>
-      </c>
-      <c r="B66" s="20" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C66" s="20" t="n">
+      <c r="C98" s="72" t="n">
+        <v>15</v>
+      </c>
+      <c r="D98" s="67" t="n">
+        <v>14.74060160709343</v>
+      </c>
+      <c r="E98" s="67" t="n">
+        <v>39.28747580222415</v>
+      </c>
+      <c r="F98" s="67" t="n">
+        <v>24.54687419513073</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="71" t="inlineStr">
+        <is>
+          <t>Variant cost reduction</t>
+        </is>
+      </c>
+      <c r="B99" s="58" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C99" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D99" s="67" t="n">
+        <v>16.49394976388848</v>
+      </c>
+      <c r="E99" s="67" t="n">
+        <v>37.5341276454291</v>
+      </c>
+      <c r="F99" s="67" t="n">
+        <v>21.04017788154063</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="71" t="inlineStr">
+        <is>
+          <t>Operator NVA eliminated</t>
+        </is>
+      </c>
+      <c r="B100" s="58" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C100" s="58" t="n">
         <v>0.45</v>
       </c>
-      <c r="D66" s="20" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>HEV</t>
-        </is>
-      </c>
-      <c r="B67" s="20" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C67" s="20" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="D67" s="20" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>PHEV</t>
-        </is>
-      </c>
-      <c r="B68" s="20" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C68" s="20" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D68" s="20" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>BEV</t>
-        </is>
-      </c>
-      <c r="B69" s="20" t="n">
+      <c r="D100" s="67" t="n">
+        <v>18.37353898797276</v>
+      </c>
+      <c r="E100" s="67" t="n">
+        <v>35.6545384213448</v>
+      </c>
+      <c r="F100" s="67" t="n">
+        <v>17.28099943337204</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="71" t="inlineStr">
+        <is>
+          <t>Maintenance reduction</t>
+        </is>
+      </c>
+      <c r="B101" s="58" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C101" s="58" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D101" s="67" t="n">
+        <v>18.50445565034678</v>
+      </c>
+      <c r="E101" s="67" t="n">
+        <v>35.52362175897076</v>
+      </c>
+      <c r="F101" s="67" t="n">
+        <v>17.01916610862397</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="71" t="inlineStr">
+        <is>
+          <t>Energy reduction</t>
+        </is>
+      </c>
+      <c r="B102" s="58" t="n">
         <v>0.02</v>
       </c>
-      <c r="C69" s="20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D69" s="20" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>Electrified share (HEV+PHEV+BEV)</t>
-        </is>
-      </c>
-      <c r="B70" s="28">
-        <f>SUM(B67:B69)</f>
-        <v/>
-      </c>
-      <c r="C70" s="28">
-        <f>SUM(C67:C69)</f>
-        <v/>
-      </c>
-      <c r="D70" s="28">
-        <f>SUM(D67:D69)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>Exhibit 9 parameters are in the Assumptions tab (rows 4-15).</t>
+      <c r="C102" s="58" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D102" s="67" t="n">
+        <v>22.30103885919367</v>
+      </c>
+      <c r="E102" s="67" t="n">
+        <v>31.72703855012389</v>
+      </c>
+      <c r="F102" s="67" t="n">
+        <v>9.425999690930212</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="71" t="inlineStr">
+        <is>
+          <t>Running cost %</t>
+        </is>
+      </c>
+      <c r="B103" s="58" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C103" s="58" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D103" s="67" t="n">
+        <v>23.77962476124955</v>
+      </c>
+      <c r="E103" s="67" t="n">
+        <v>30.24845264806801</v>
+      </c>
+      <c r="F103" s="67" t="n">
+        <v>6.468827886818463</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>Use the top 2-3 drivers as the assumptions you defend hardest in Q&amp;A, and as the KPIs you track first in the pilot.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -18112,915 +20794,1361 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Model inputs</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>Case parameter (Exhibit 9 / text)</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
+          <t>Idea tests: simulation results (values produced by run_tests.py, not formulas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="54" t="inlineStr">
+        <is>
+          <t>Re-run run_tests.py after changing assumptions. Process parameters below are illustrative assumptions, not TMMIN data: present them as a mechanism test, and show the sensitivity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>TEST 1. Does closing the quality loop beat adding technology alone? (sealer drift -&gt; inspection -&gt; feedback, 1 year, 175,000 units, 300 runs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="55" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>Defective units / yr</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>Scrapped units / yr</t>
+        </is>
+      </c>
+      <c r="D5" s="55" t="inlineStr">
+        <is>
+          <t>Escaped defects / yr</t>
+        </is>
+      </c>
+      <c r="E5" s="55" t="inlineStr">
+        <is>
+          <t>Units built while drifting</t>
+        </is>
+      </c>
+      <c r="F5" s="55" t="inlineStr">
+        <is>
+          <t>Scrap vs today</t>
+        </is>
+      </c>
+      <c r="G5" s="55" t="inlineStr">
+        <is>
+          <t>Escapes vs today</t>
+        </is>
+      </c>
+      <c r="H5" s="55" t="inlineStr">
+        <is>
+          <t>Scrap P5-P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="56" t="inlineStr">
+        <is>
+          <t>1. Today: visual at final inspection, manual feedback</t>
+        </is>
+      </c>
+      <c r="B6" s="57" t="n">
+        <v>4266.68</v>
+      </c>
+      <c r="C6" s="57" t="n">
+        <v>1088.524</v>
+      </c>
+      <c r="D6" s="57" t="n">
+        <v>638.2666666666667</v>
+      </c>
+      <c r="E6" s="57" t="n">
+        <v>15796.09333333333</v>
+      </c>
+      <c r="F6" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="57" t="inlineStr">
+        <is>
+          <t>835 - 1,365</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="56" t="inlineStr">
+        <is>
+          <t>2. Better camera at end-of-line only (tech, no loop)</t>
+        </is>
+      </c>
+      <c r="B7" s="57" t="n">
+        <v>4265.323333333334</v>
+      </c>
+      <c r="C7" s="57" t="n">
+        <v>1215.776</v>
+      </c>
+      <c r="D7" s="57" t="n">
+        <v>212.7366666666667</v>
+      </c>
+      <c r="E7" s="57" t="n">
+        <v>15793.25666666667</v>
+      </c>
+      <c r="F7" s="58" t="n">
+        <v>0.1169032561523677</v>
+      </c>
+      <c r="G7" s="58" t="n">
+        <v>-0.6666962607060789</v>
+      </c>
+      <c r="H7" s="57" t="inlineStr">
+        <is>
+          <t>910 - 1,492</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="56" t="inlineStr">
+        <is>
+          <t>3. Closed loop at sealer, 31% of alerts dismissed (as today)</t>
+        </is>
+      </c>
+      <c r="B8" s="57" t="n">
+        <v>1652.95</v>
+      </c>
+      <c r="C8" s="57" t="n">
+        <v>362.1536666666667</v>
+      </c>
+      <c r="D8" s="57" t="n">
+        <v>203.26</v>
+      </c>
+      <c r="E8" s="57" t="n">
+        <v>5247.72</v>
+      </c>
+      <c r="F8" s="58" t="n">
+        <v>-0.6672984089770491</v>
+      </c>
+      <c r="G8" s="58" t="n">
+        <v>-0.6815437643618132</v>
+      </c>
+      <c r="H8" s="57" t="inlineStr">
+        <is>
+          <t>216 - 543</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="59" t="inlineStr">
+        <is>
+          <t>4. Closed loop with people-centred design (10% dismissed)</t>
+        </is>
+      </c>
+      <c r="B9" s="60" t="n">
+        <v>908.3233333333334</v>
+      </c>
+      <c r="C9" s="60" t="n">
+        <v>166.8633333333333</v>
+      </c>
+      <c r="D9" s="60" t="n">
+        <v>88.00666666666666</v>
+      </c>
+      <c r="E9" s="60" t="n">
+        <v>2257.006666666667</v>
+      </c>
+      <c r="F9" s="61" t="n">
+        <v>-0.8467067943992661</v>
+      </c>
+      <c r="G9" s="61" t="n">
+        <v>-0.862116147900564</v>
+      </c>
+      <c r="H9" s="60" t="inlineStr">
+        <is>
+          <t>83 - 270</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>What this shows</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="62" t="inlineStr">
+        <is>
+          <t>- A better camera at end-of-line alone changes scrap by +12% while escapes fall 67%: it catches more bad units, but too late, so escapes turn into scrap. It does not prevent defects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="62" t="inlineStr">
+        <is>
+          <t>- Closing the loop right after the sealer cuts scrap 85% and escapes 86%, because a drift is stopped within a few units instead of hundreds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="62" t="inlineStr">
+        <is>
+          <t>- If operators dismiss alerts in 31% of drift episodes (today's override rate), scrap reduction falls to 67%. Trust, training and alert design are part of the value, not an add-on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="62" t="inlineStr">
+        <is>
+          <t>- Plant-wide: if the pilot scope causes 40% of plant scrap (team assumption), the plant-wide scrap cut is about 34%. Compare with the 20% / 35% / 50% lever in Assumptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="62" t="inlineStr">
+        <is>
+          <t>- Deck message: value comes from redesigning the system (where the check sits, how fast the signal travels, who acts on it), not from buying the device. That is exactly the case ask.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Process assumptions used (illustrative, change and re-run)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="54" t="inlineStr">
+        <is>
+          <t>Defect probability per unit, stable sealer</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="54" t="inlineStr">
+        <is>
+          <t>Average units between drift events</t>
+        </is>
+      </c>
+      <c r="B20" s="63" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="54" t="inlineStr">
+        <is>
+          <t>Defect probability per unit while drifting</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="54" t="inlineStr">
+        <is>
+          <t>Manual visual detection rate at final inspection</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="54" t="inlineStr">
+        <is>
+          <t>Share of sealer defect modes the in-line AI camera can see</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="54" t="inlineStr">
+        <is>
+          <t>Units between sealer and today's final inspection</t>
+        </is>
+      </c>
+      <c r="B24" s="63" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="54" t="inlineStr">
+        <is>
+          <t>Units built before manual feedback reaches the sealer</t>
+        </is>
+      </c>
+      <c r="B25" s="63" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="54" t="inlineStr">
+        <is>
+          <t>Share of late-found defects scrapped</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="54" t="inlineStr">
+        <is>
+          <t>Share of early-found defects scrapped</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="54" t="inlineStr">
+        <is>
+          <t>Share of plant scrap from the pilot scope (team assumption)</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="62" t="inlineStr">
+        <is>
+          <t>In-line check: 5 units after sealer, automatic feedback within 10 units, 90% detection on visible defect modes (case: AI camera in validation to Oct 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Robustness: closed-loop (scenario 4) scrap reduction vs today when each assumption changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="55" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="B32" s="55" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C32" s="55" t="inlineStr">
+        <is>
+          <t>Reduction</t>
+        </is>
+      </c>
+      <c r="D32" s="55" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E32" s="55" t="inlineStr">
+        <is>
+          <t>Reduction</t>
+        </is>
+      </c>
+      <c r="F32" s="55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G32" s="55" t="inlineStr">
+        <is>
+          <t>Reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>AI camera coverage of defect modes</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C33" s="64" t="n">
+        <v>0.8247043005741556</v>
+      </c>
+      <c r="D33" s="20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E33" s="64" t="n">
+        <v>0.8468422609923756</v>
+      </c>
+      <c r="F33" s="20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G33" s="64" t="n">
+        <v>0.8667088181512177</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Drift defect rate</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C34" s="64" t="n">
+        <v>0.8026017993273447</v>
+      </c>
+      <c r="D34" s="20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E34" s="64" t="n">
+        <v>0.8479906256107048</v>
+      </c>
+      <c r="F34" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G34" s="64" t="n">
+        <v>0.8649243431242232</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Units between drift events</t>
+        </is>
+      </c>
+      <c r="B35" s="63" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C35" s="64" t="n">
+        <v>0.8634074536698797</v>
+      </c>
+      <c r="D35" s="63" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E35" s="64" t="n">
+        <v>0.8582510378017658</v>
+      </c>
+      <c r="F35" s="63" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G35" s="64" t="n">
+        <v>0.8336816505910225</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Late-found scrap share</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C36" s="64" t="n">
+        <v>0.8314626883200975</v>
+      </c>
+      <c r="D36" s="20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E36" s="64" t="n">
+        <v>0.8538779573335564</v>
+      </c>
+      <c r="F36" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G36" s="64" t="n">
+        <v>0.8501771115300518</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Units from sealer to today's inspection</t>
+        </is>
+      </c>
+      <c r="B37" s="63" t="n">
+        <v>100</v>
+      </c>
+      <c r="C37" s="64" t="n">
+        <v>0.8111230466252334</v>
+      </c>
+      <c r="D37" s="63" t="n">
+        <v>300</v>
+      </c>
+      <c r="E37" s="64" t="n">
+        <v>0.8492533988756621</v>
+      </c>
+      <c r="F37" s="63" t="n">
+        <v>600</v>
+      </c>
+      <c r="G37" s="64" t="n">
+        <v>0.8737976071910339</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Lowest scrap reduction across all tested cases: 80%. The mechanism holds even with pessimistic process assumptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>People test: how much value is lost when operators dismiss alerts?</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="55" t="inlineStr">
+        <is>
+          <t>Share of drift episodes where alerts are dismissed</t>
+        </is>
+      </c>
+      <c r="B41" s="55" t="inlineStr">
+        <is>
+          <t>Scrap reduction vs today</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="B42" s="64" t="n">
+        <v>0.9392930243154951</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B43" s="64" t="n">
+        <v>0.8445760803926541</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B44" s="64" t="n">
+        <v>0.7497194978398884</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="B45" s="64" t="n">
+        <v>0.6431060163426193</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B46" s="64" t="n">
+        <v>0.4964125733562145</v>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="62" t="inlineStr">
+        <is>
+          <t>Exhibit 6B says 31% of operators frequently override alerts today. This chart is the quantified case for the people part of the idea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>TEST 2. Is the business case robust? Financial Monte Carlo (10,000 runs, mirrors the Model tab incl. pilot-light phasing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="55" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B50" s="55" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>Source / note</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Installed capacity, Karawang I + II</t>
-        </is>
-      </c>
-      <c r="B4" s="73" t="n">
-        <v>250000</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>units/yr</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>Exhibit 9</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Capacity utilization 2025</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Exhibit 9</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Production volume</t>
-        </is>
-      </c>
-      <c r="B6" s="74">
-        <f>B4*B5</f>
-        <v/>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>units/yr</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>Formula (case: ~175,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Conversion cost per unit 2025</t>
-        </is>
-      </c>
-      <c r="B7" s="75" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Rp million</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Exhibit 9 (labor, energy, maintenance, depreciation, scrap)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Total annual conversion cost</t>
-        </is>
-      </c>
-      <c r="B8" s="76">
-        <f>B6*B7/1000</f>
-        <v/>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C50" s="55" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Deterministic base NPV (check vs Model tab)</t>
+        </is>
+      </c>
+      <c r="B51" s="65" t="n">
+        <v>27.01403870465879</v>
+      </c>
+      <c r="C51" s="54" t="inlineStr">
+        <is>
+          <t>Should match Dashboard base NPV</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Mean NPV</t>
+        </is>
+      </c>
+      <c r="B52" s="65" t="n">
+        <v>11.82360761131173</v>
+      </c>
+      <c r="C52" s="54" t="inlineStr">
         <is>
           <t>Rp billion</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>Formula (case: ~Rp560B)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Discount rate</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>%/yr</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Exhibit 9</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Labor &amp; energy cost escalation</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>%/yr</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>Exhibit 9, applied to savings</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Technology economic life</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>P5 NPV (bad case)</t>
+        </is>
+      </c>
+      <c r="B53" s="65" t="n">
+        <v>-19.41291040060244</v>
+      </c>
+      <c r="C53" s="54" t="inlineStr">
+        <is>
+          <t>1-in-20 downside</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Median NPV</t>
+        </is>
+      </c>
+      <c r="B54" s="65" t="n">
+        <v>11.7084469092985</v>
+      </c>
+      <c r="C54" s="54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>P95 NPV (good case)</t>
+        </is>
+      </c>
+      <c r="B55" s="65" t="n">
+        <v>43.10332192077205</v>
+      </c>
+      <c r="C55" s="54" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Probability NPV &gt; 0</t>
+        </is>
+      </c>
+      <c r="B56" s="64" t="n">
+        <v>0.7311</v>
+      </c>
+      <c r="C56" s="54" t="inlineStr">
+        <is>
+          <t>Headline for the financial slide</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Median full run-rate savings (Rp B/yr)</t>
+        </is>
+      </c>
+      <c r="B57" s="65" t="n">
+        <v>49.0844126012166</v>
+      </c>
+      <c r="C57" s="54" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Median run-rate as % of conversion cost</t>
+        </is>
+      </c>
+      <c r="B58" s="64" t="n">
+        <v>0.08765073678788678</v>
+      </c>
+      <c r="C58" s="54" t="inlineStr">
+        <is>
+          <t>vs 16% gap to benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>TEST 2b. How should the roadmap spend the money? Same 10,000 runs, five strategies (gate = stop scaling if 2027 pilot adoption &lt; 80%; happens in 25% of runs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="55" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="B61" s="55" t="inlineStr">
+        <is>
+          <t>Mean NPV</t>
+        </is>
+      </c>
+      <c r="C61" s="55" t="inlineStr">
+        <is>
+          <t>P5 NPV</t>
+        </is>
+      </c>
+      <c r="D61" s="55" t="inlineStr">
+        <is>
+          <t>Median NPV</t>
+        </is>
+      </c>
+      <c r="E61" s="55" t="inlineStr">
+        <is>
+          <t>P95 NPV</t>
+        </is>
+      </c>
+      <c r="F61" s="55" t="inlineStr">
+        <is>
+          <t>P(NPV &gt; 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="66" t="inlineStr">
+        <is>
+          <t>A. Front-loaded phasing, no gate</t>
+        </is>
+      </c>
+      <c r="B62" s="67" t="n">
+        <v>-0.191332294676973</v>
+      </c>
+      <c r="C62" s="67" t="n">
+        <v>-32.83255089311962</v>
+      </c>
+      <c r="D62" s="67" t="n">
+        <v>-0.3737217276611755</v>
+      </c>
+      <c r="E62" s="67" t="n">
+        <v>32.5044161216826</v>
+      </c>
+      <c r="F62" s="58" t="n">
+        <v>0.4925</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="66" t="inlineStr">
+        <is>
+          <t>B. Front-loaded phasing + gate (65% already spent)</t>
+        </is>
+      </c>
+      <c r="B63" s="67" t="n">
+        <v>-3.79967892697686</v>
+      </c>
+      <c r="C63" s="67" t="n">
+        <v>-39.74590657971964</v>
+      </c>
+      <c r="D63" s="67" t="n">
+        <v>-2.962350007986172</v>
+      </c>
+      <c r="E63" s="67" t="n">
+        <v>32.40194504032392</v>
+      </c>
+      <c r="F63" s="58" t="n">
+        <v>0.4518</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="66" t="inlineStr">
+        <is>
+          <t>C. Pilot-light phasing, no gate (as in Model tab)</t>
+        </is>
+      </c>
+      <c r="B64" s="67" t="n">
+        <v>11.82360761131173</v>
+      </c>
+      <c r="C64" s="67" t="n">
+        <v>-19.41291040060244</v>
+      </c>
+      <c r="D64" s="67" t="n">
+        <v>11.7084469092985</v>
+      </c>
+      <c r="E64" s="67" t="n">
+        <v>43.10332192077205</v>
+      </c>
+      <c r="F64" s="58" t="n">
+        <v>0.7311</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="68" t="inlineStr">
+        <is>
+          <t>D. Pilot-light phasing + gate</t>
+        </is>
+      </c>
+      <c r="B65" s="69" t="n">
+        <v>15.05090030021514</v>
+      </c>
+      <c r="C65" s="69" t="n">
+        <v>-8.411626796801812</v>
+      </c>
+      <c r="D65" s="69" t="n">
+        <v>13.32040175184729</v>
+      </c>
+      <c r="E65" s="69" t="n">
+        <v>43.06772269056702</v>
+      </c>
+      <c r="F65" s="61" t="n">
+        <v>0.8595</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="66" t="inlineStr">
+        <is>
+          <t>E. D + remaining equipment life valued at book</t>
+        </is>
+      </c>
+      <c r="B66" s="67" t="n">
+        <v>36.01053481960803</v>
+      </c>
+      <c r="C66" s="67" t="n">
+        <v>6.476777490438207</v>
+      </c>
+      <c r="D66" s="67" t="n">
+        <v>36.96085240343595</v>
+      </c>
+      <c r="E66" s="67" t="n">
+        <v>67.48368978517901</v>
+      </c>
+      <c r="F66" s="58" t="n">
+        <v>0.9938</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="66" t="inlineStr">
+        <is>
+          <t>F. D but savings ramp one year slower (stress test)</t>
+        </is>
+      </c>
+      <c r="B67" s="67" t="n">
+        <v>-7.534233621168762</v>
+      </c>
+      <c r="C67" s="67" t="n">
+        <v>-31.89940806088983</v>
+      </c>
+      <c r="D67" s="67" t="n">
+        <v>-5.542507323532465</v>
+      </c>
+      <c r="E67" s="67" t="n">
+        <v>12.32550108470081</v>
+      </c>
+      <c r="F67" s="58" t="n">
+        <v>0.3242</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="66" t="inlineStr">
+        <is>
+          <t>G. F + remaining equipment life valued at book</t>
+        </is>
+      </c>
+      <c r="B68" s="67" t="n">
+        <v>13.42540089822414</v>
+      </c>
+      <c r="C68" s="67" t="n">
+        <v>-3.778779125254701</v>
+      </c>
+      <c r="D68" s="67" t="n">
+        <v>11.92716410770895</v>
+      </c>
+      <c r="E68" s="67" t="n">
+        <v>35.1241416528562</v>
+      </c>
+      <c r="F68" s="58" t="n">
+        <v>0.879</v>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="62" t="inlineStr">
+        <is>
+          <t>Pilot-light phasing: 10% / 15% / 40% / 25% / 10% of capex in 2026-2030. Ramp-up kept the same to isolate the effect of phasing; if scaling later also delays savings, the gain is smaller.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="58" customHeight="1">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>Reading: a gate only protects value if little money is spent before it. Gate after heavy spending (B) destroys value; pilot-light + gate (D) is the design to defend in SQ3. Valuing equipment life beyond 2030 (E) is legitimate but state it openly. Stress test (F): if savings arrive a year late, P(NPV&gt;0) falls to 32% (88% if remaining equipment life is valued, G). Speed of the pilot is the make-or-break factor: quick wins in 2026-27 belong in the roadmap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="45" customHeight="1">
+      <c r="A71" s="62" t="inlineStr">
+        <is>
+          <t>Ranges used (triangular low / mode / high): scrap 20/35/50%, maintenance 5/10/15%, NVA 15/30/45%, energy 2/5/8%, variant cost 20/35/50%, investment 60/80/110, running 8/9/12%, training 2/2.5/3, variant projects 2/3/5, cost per project 5/10/15, cash realization 30/50/70%, adoption 60/100/100%, labor share 35/40/45%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>NPV distribution (histogram)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="55" t="inlineStr">
+        <is>
+          <t>NPV bin from (Rp B)</t>
+        </is>
+      </c>
+      <c r="B74" s="55" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="65" t="n">
+        <v>-51.6</v>
+      </c>
+      <c r="B75" s="70" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="65" t="n">
+        <v>-41.6</v>
+      </c>
+      <c r="B76" s="70" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="65" t="n">
+        <v>-31.5</v>
+      </c>
+      <c r="B77" s="70" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="65" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="B78" s="70" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="65" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="B79" s="70" t="n">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="65" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="B80" s="70" t="n">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="65" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="B81" s="70" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="65" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="B82" s="70" t="n">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="65" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="B83" s="70" t="n">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="65" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="B84" s="70" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="65" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="B85" s="70" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="65" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="B86" s="70" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="65" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="B87" s="70" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="65" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="B88" s="70" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="65" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="B89" s="70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="65" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="B90" s="70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>TEST 3. Which assumption matters most? Tornado (base case, one at a time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="55" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="B93" s="55" t="inlineStr">
+        <is>
+          <t>Low input</t>
+        </is>
+      </c>
+      <c r="C93" s="55" t="inlineStr">
+        <is>
+          <t>High input</t>
+        </is>
+      </c>
+      <c r="D93" s="55" t="inlineStr">
+        <is>
+          <t>NPV at low</t>
+        </is>
+      </c>
+      <c r="E93" s="55" t="inlineStr">
+        <is>
+          <t>NPV at high</t>
+        </is>
+      </c>
+      <c r="F93" s="55" t="inlineStr">
+        <is>
+          <t>Swing</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="71" t="inlineStr">
+        <is>
+          <t>Investment (Rp B)</t>
+        </is>
+      </c>
+      <c r="B94" s="72" t="n">
+        <v>110</v>
+      </c>
+      <c r="C94" s="72" t="n">
+        <v>60</v>
+      </c>
+      <c r="D94" s="67" t="n">
+        <v>-1.497910926203485</v>
+      </c>
+      <c r="E94" s="67" t="n">
+        <v>46.02200512523363</v>
+      </c>
+      <c r="F94" s="67" t="n">
+        <v>47.51991605143711</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="71" t="inlineStr">
+        <is>
+          <t>Adoption achieved</t>
+        </is>
+      </c>
+      <c r="B95" s="58" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C95" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" s="67" t="n">
+        <v>-17.99510981953292</v>
+      </c>
+      <c r="E95" s="67" t="n">
+        <v>27.01403870465879</v>
+      </c>
+      <c r="F95" s="67" t="n">
+        <v>45.00914852419172</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="71" t="inlineStr">
+        <is>
+          <t>Scrap reduction</t>
+        </is>
+      </c>
+      <c r="B96" s="58" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C96" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D96" s="67" t="n">
+        <v>7.376539348554191</v>
+      </c>
+      <c r="E96" s="67" t="n">
+        <v>46.65153806076337</v>
+      </c>
+      <c r="F96" s="67" t="n">
+        <v>39.27499871220918</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="71" t="inlineStr">
+        <is>
+          <t>Variant projects / yr</t>
+        </is>
+      </c>
+      <c r="B97" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="C97" s="72" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>Exhibit 9</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TMMIN conversion cost index 2025</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>106</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>index</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>Exhibit 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>New-player benchmark index 2025</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>89</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>index</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>Exhibit 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Operator non-value-added time</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>% hours</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>Exhibit 4 / text</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Equipment modification time per new variant</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>months</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>Exhibit 4 / text</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Conversion cost split (TEAM ASSUMPTION, case gives components only)</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Share</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Rp billion</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Justify with</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Labor</t>
-        </is>
-      </c>
-      <c r="B18" s="24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C18" s="76">
-        <f>B18*$B$8</f>
-        <v/>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>No public source splits conversion cost. Stated team assumption; Monte Carlo tests labor share 35-45% (Simulation tab). Ask organizers in clarification if allowed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="B19" s="24" t="n">
+      <c r="D97" s="67" t="n">
+        <v>18.83174730628188</v>
+      </c>
+      <c r="E97" s="67" t="n">
+        <v>43.37862150141261</v>
+      </c>
+      <c r="F97" s="67" t="n">
+        <v>24.54687419513073</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="71" t="inlineStr">
+        <is>
+          <t>Cost per variant project</t>
+        </is>
+      </c>
+      <c r="B98" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="C98" s="72" t="n">
+        <v>15</v>
+      </c>
+      <c r="D98" s="67" t="n">
+        <v>14.74060160709343</v>
+      </c>
+      <c r="E98" s="67" t="n">
+        <v>39.28747580222415</v>
+      </c>
+      <c r="F98" s="67" t="n">
+        <v>24.54687419513073</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="71" t="inlineStr">
+        <is>
+          <t>Variant cost reduction</t>
+        </is>
+      </c>
+      <c r="B99" s="58" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C99" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D99" s="67" t="n">
+        <v>16.49394976388848</v>
+      </c>
+      <c r="E99" s="67" t="n">
+        <v>37.5341276454291</v>
+      </c>
+      <c r="F99" s="67" t="n">
+        <v>21.04017788154063</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="71" t="inlineStr">
+        <is>
+          <t>Operator NVA eliminated</t>
+        </is>
+      </c>
+      <c r="B100" s="58" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C100" s="58" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D100" s="67" t="n">
+        <v>18.37353898797276</v>
+      </c>
+      <c r="E100" s="67" t="n">
+        <v>35.6545384213448</v>
+      </c>
+      <c r="F100" s="67" t="n">
+        <v>17.28099943337204</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="71" t="inlineStr">
+        <is>
+          <t>Maintenance reduction</t>
+        </is>
+      </c>
+      <c r="B101" s="58" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C101" s="58" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D101" s="67" t="n">
+        <v>18.50445565034678</v>
+      </c>
+      <c r="E101" s="67" t="n">
+        <v>35.52362175897076</v>
+      </c>
+      <c r="F101" s="67" t="n">
+        <v>17.01916610862397</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="71" t="inlineStr">
+        <is>
+          <t>Energy reduction</t>
+        </is>
+      </c>
+      <c r="B102" s="58" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C102" s="58" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D102" s="67" t="n">
+        <v>22.30103885919367</v>
+      </c>
+      <c r="E102" s="67" t="n">
+        <v>31.72703855012389</v>
+      </c>
+      <c r="F102" s="67" t="n">
+        <v>9.425999690930212</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="71" t="inlineStr">
+        <is>
+          <t>Running cost %</t>
+        </is>
+      </c>
+      <c r="B103" s="58" t="n">
         <v>0.12</v>
       </c>
-      <c r="C19" s="76">
-        <f>B19*$B$8</f>
-        <v/>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>No public source splits conversion cost. Stated team assumption; Monte Carlo tests labor share 35-45% (Simulation tab). Ask organizers in clarification if allowed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B20" s="24" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="C20" s="76">
-        <f>B20*$B$8</f>
-        <v/>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>No public source splits conversion cost. Stated team assumption; Monte Carlo tests labor share 35-45% (Simulation tab). Ask organizers in clarification if allowed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="B21" s="24" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C21" s="76">
-        <f>B21*$B$8</f>
-        <v/>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>No public source splits conversion cost. Stated team assumption; Monte Carlo tests labor share 35-45% (Simulation tab). Ask organizers in clarification if allowed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Scrap</t>
-        </is>
-      </c>
-      <c r="B22" s="24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C22" s="76">
-        <f>B22*$B$8</f>
-        <v/>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>No public source splits conversion cost. Stated team assumption; Monte Carlo tests labor share 35-45% (Simulation tab). Ask organizers in clarification if allowed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Check (must be 100%)</t>
-        </is>
-      </c>
-      <c r="B23" s="28">
-        <f>SUM(B18:B22)</f>
-        <v/>
-      </c>
-      <c r="C23" s="76">
-        <f>SUM(C18:C22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Other team assumptions</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>New variant / model-change projects per year</t>
-        </is>
-      </c>
-      <c r="B26" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>projects/yr</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>Rises with multi-pathway mix (Exhibit 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Average cost per equipment modification project</t>
-        </is>
-      </c>
-      <c r="B27" s="77" t="n">
-        <v>10</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Rp billion</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>Team assumption, no public source. Tornado shows its NPV swing (Simulation Test 3); state it openly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Share of freed operator time converted to cash</t>
-        </is>
-      </c>
-      <c r="B28" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>Rest is redeployed to kaizen / absorbs volume (no layoffs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Lever assumptions by scenario</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Conservative</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Optimistic</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>What drives it / how to defend</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr"/>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>Benchmark evidence (cite in appendix)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="54" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>Scrap cost reduction</t>
-        </is>
-      </c>
-      <c r="B32" s="24" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C32" s="24" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D32" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>Closed-loop feedback catches sealer/inspection lapses upstream (Exhibit 4/5)</t>
-        </is>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>Own simulation (Simulation tab): closed loop cuts in-scope scrap ~85%; x 40% scope share = ~34% plant-wide. Base 35% sits on that result.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="54" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>Maintenance cost reduction</t>
-        </is>
-      </c>
-      <c r="B33" s="24" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C33" s="24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D33" s="24" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E33" s="11" t="inlineStr">
-        <is>
-          <t>Predictive maintenance + fewer unplanned stops</t>
-        </is>
-      </c>
-      <c r="G33" s="11" t="inlineStr">
-        <is>
-          <t>McKinsey (2020, via IIoT World): maintenance cost -18 to 25%, unplanned downtime up to -50%. Our range is deliberately below. https://www.iiot-world.com/predictive-analytics/predictive-maintenance/predictive-maintenance-cost-savings/</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="54" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>Operator NVA time eliminated (% of the 22%)</t>
-        </is>
-      </c>
-      <c r="B34" s="24" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C34" s="24" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D34" s="24" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E34" s="11" t="inlineStr">
-        <is>
-          <t>Intralogistics sync, digital standard work, less searching/waiting</t>
-        </is>
-      </c>
-      <c r="G34" s="11" t="inlineStr">
-        <is>
-          <t>Toyota AI Platform: &gt;10,000 man-hours/yr saved by worker-built tools (Google Cloud 2024). Omron/MPA AMR case: up to 15 km/day of operator walking and all manual crate runs eliminated (no % published). Validate with a time study in the pilot. https://robotics.omron.com/case-studies/amr-automation-intralogistics-mpa-omron/</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="54" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>Energy cost reduction</t>
-        </is>
-      </c>
-      <c r="B35" s="24" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C35" s="24" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D35" s="24" t="n">
+      <c r="C103" s="58" t="n">
         <v>0.08</v>
       </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>Data-driven idle/standby control</t>
-        </is>
-      </c>
-      <c r="G35" s="11" t="inlineStr">
-        <is>
-          <t>Nissan US plants, energy management system (ISO 50001 / SEP): 13.8% energy performance gain over 3 years, 8-21% by site. Our 2-8% is deliberately below. https://www.cleanenergyministerial.org/content/uploads/2022/03/cem-em-casestudy-nissan-usa.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="54" customHeight="1">
-      <c r="A36" s="11" t="inlineStr">
-        <is>
-          <t>Variant modification cost reduction</t>
-        </is>
-      </c>
-      <c r="B36" s="24" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C36" s="24" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D36" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E36" s="11" t="inlineStr">
-        <is>
-          <t>Common interface standard + in-house equipment + virtual verification</t>
-        </is>
-      </c>
-      <c r="G36" s="11" t="inlineStr">
-        <is>
-          <t>Siemens / Wipro PARI: virtual commissioning cut on-site commissioning 70% on a 17-variant engine line. Kalypso: up to 40%. Toyota BEV plan targets halving prep lead time. https://resources.sw.siemens.com/en-US/case-study-wipro-pari/</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="54" customHeight="1">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>Total program investment</t>
-        </is>
-      </c>
-      <c r="B37" s="77" t="n">
-        <v>110</v>
-      </c>
-      <c r="C37" s="77" t="n">
-        <v>80</v>
-      </c>
-      <c r="D37" s="77" t="n">
-        <v>60</v>
-      </c>
-      <c r="E37" s="11" t="inlineStr">
-        <is>
-          <t>Must sit inside case range Rp40-120B</t>
-        </is>
-      </c>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t>Case Exhibit 9</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="54" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>Annual running cost (% of cumulative investment)</t>
-        </is>
-      </c>
-      <c r="B38" s="24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C38" s="24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D38" s="24" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E38" s="11" t="inlineStr">
-        <is>
-          <t>Licences, cloud/compute, upkeep</t>
-        </is>
-      </c>
-      <c r="G38" s="11" t="inlineStr">
-        <is>
-          <t>Team assumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="54" customHeight="1">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>Training &amp; change management opex</t>
-        </is>
-      </c>
-      <c r="B39" s="77" t="n">
-        <v>3</v>
-      </c>
-      <c r="C39" s="77" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D39" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="E39" s="11" t="inlineStr">
-        <is>
-          <t>Rp billion/yr: academy, coaches, kaizen time</t>
-        </is>
-      </c>
-      <c r="G39" s="11" t="inlineStr">
-        <is>
-          <t>Team assumption; cross-check with Capability tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Implied variant modification time (months)</t>
-        </is>
-      </c>
-      <c r="B40" s="78">
-        <f>$B$15*(1-B36)</f>
-        <v/>
-      </c>
-      <c r="C40" s="78">
-        <f>$B$15*(1-C36)</f>
-        <v/>
-      </c>
-      <c r="D40" s="78">
-        <f>$B$15*(1-D36)</f>
-        <v/>
-      </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>Show this on the flexibility slide (vs 9 months today)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>Timing</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>Sum / note</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Adoption ramp-up (% of full run-rate)</t>
-        </is>
-      </c>
-      <c r="B43" s="24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C43" s="24" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D43" s="24" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E43" s="24" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F43" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Pilot -&gt; standardize -&gt; rollout</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Investment phasing (% of total): PILOT-LIGHT</t>
-        </is>
-      </c>
-      <c r="B44" s="24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C44" s="24" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D44" s="24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E44" s="24" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F44" s="24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G44" s="28">
-        <f>SUM(B44:F44)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Year index (t)</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>End-of-year discounting</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Reference only: original front-loaded phasing</t>
-        </is>
-      </c>
-      <c r="B46" s="20" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C46" s="20" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D46" s="20" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E46" s="20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F46" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Why pilot-light: Simulation tab Test 2b. Spending little before the end-2027 gate raised P(NPV&gt;0) from ~49% to ~85% across 10,000 runs.</t>
+      <c r="D103" s="67" t="n">
+        <v>23.77962476124955</v>
+      </c>
+      <c r="E103" s="67" t="n">
+        <v>30.24845264806801</v>
+      </c>
+      <c r="F103" s="67" t="n">
+        <v>6.468827886818463</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>Use the top 2-3 drivers as the assumptions you defend hardest in Q&amp;A, and as the KPIs you track first in the pilot.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>